--- a/research/traditional_assets/database/data/ghana/ghana_household_products.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_household_products.xlsx
@@ -588,118 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0137</v>
+        <v>0.00373</v>
+      </c>
+      <c r="E2">
+        <v>-0.287</v>
       </c>
       <c r="G2">
-        <v>-0.01420996818663839</v>
+        <v>-0.05938069216757741</v>
       </c>
       <c r="H2">
-        <v>-0.01420996818663839</v>
+        <v>-0.05938069216757741</v>
       </c>
       <c r="I2">
-        <v>-0.02046659597030753</v>
+        <v>-0.009836065573770493</v>
       </c>
       <c r="J2">
-        <v>-0.02046659597030753</v>
+        <v>-0.009836065573770493</v>
       </c>
       <c r="K2">
-        <v>-6.87</v>
+        <v>0.878</v>
       </c>
       <c r="L2">
-        <v>-0.0728525980911983</v>
+        <v>0.01599271402550091</v>
       </c>
       <c r="M2">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.03207236842105263</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.2838427947598253</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.03207236842105263</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.2838427947598253</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="V2">
-        <v>0.03108552631578947</v>
+        <v>0.1236947791164659</v>
       </c>
       <c r="W2">
-        <v>-0.5822033898305085</v>
+        <v>0.1825363825363825</v>
       </c>
       <c r="X2">
-        <v>0.1235930971042961</v>
+        <v>0.3466837043904417</v>
       </c>
       <c r="Y2">
-        <v>-0.7057964869348046</v>
+        <v>-0.1641473218540592</v>
       </c>
       <c r="Z2">
-        <v>5.842627013630731</v>
+        <v>8.632075471698112</v>
       </c>
       <c r="AA2">
-        <v>-0.1195786864931846</v>
+        <v>-0.08490566037735849</v>
       </c>
       <c r="AB2">
-        <v>0.1204429910751101</v>
+        <v>0.3056370430666834</v>
       </c>
       <c r="AC2">
-        <v>-0.2400216775682947</v>
+        <v>-0.3905427034440419</v>
       </c>
       <c r="AD2">
-        <v>3.44</v>
+        <v>6.75</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.44</v>
+        <v>6.75</v>
       </c>
       <c r="AG2">
-        <v>1.55</v>
+        <v>3.67</v>
       </c>
       <c r="AH2">
-        <v>0.05354919053549191</v>
+        <v>0.2132701421800948</v>
       </c>
       <c r="AI2">
-        <v>0.416969696969697</v>
+        <v>0.7368995633187773</v>
       </c>
       <c r="AJ2">
-        <v>0.02485966319165999</v>
+        <v>0.1284564228211411</v>
       </c>
       <c r="AK2">
-        <v>0.2437106918238994</v>
+        <v>0.6036184210526315</v>
       </c>
       <c r="AL2">
-        <v>0.414</v>
+        <v>1.24</v>
       </c>
       <c r="AM2">
-        <v>0.389</v>
+        <v>1.108</v>
       </c>
       <c r="AN2">
-        <v>13.07984790874525</v>
+        <v>9.684361549497849</v>
       </c>
       <c r="AO2">
-        <v>-4.661835748792271</v>
+        <v>-0.435483870967742</v>
       </c>
       <c r="AP2">
-        <v>5.893536121673003</v>
+        <v>5.265423242467719</v>
       </c>
       <c r="AQ2">
-        <v>-4.961439588688946</v>
+        <v>-0.4873646209386281</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0137</v>
+        <v>0.00373</v>
+      </c>
+      <c r="E3">
+        <v>-0.287</v>
       </c>
       <c r="G3">
-        <v>-0.01420996818663839</v>
+        <v>-0.05938069216757741</v>
       </c>
       <c r="H3">
-        <v>-0.01420996818663839</v>
+        <v>-0.05938069216757741</v>
       </c>
       <c r="I3">
-        <v>-0.02046659597030753</v>
+        <v>-0.009836065573770493</v>
       </c>
       <c r="J3">
-        <v>-0.02046659597030753</v>
+        <v>-0.009836065573770493</v>
       </c>
       <c r="K3">
-        <v>-6.87</v>
+        <v>0.878</v>
       </c>
       <c r="L3">
-        <v>-0.0728525980911983</v>
+        <v>0.01599271402550091</v>
       </c>
       <c r="M3">
-        <v>1.95</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03207236842105263</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.2838427947598253</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>1.95</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03207236842105263</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.2838427947598253</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="V3">
-        <v>0.03108552631578947</v>
+        <v>0.1236947791164659</v>
       </c>
       <c r="W3">
-        <v>-0.5822033898305085</v>
+        <v>0.1825363825363825</v>
       </c>
       <c r="X3">
-        <v>0.1235930971042961</v>
+        <v>0.3466837043904417</v>
       </c>
       <c r="Y3">
-        <v>-0.7057964869348046</v>
+        <v>-0.1641473218540592</v>
       </c>
       <c r="Z3">
-        <v>5.842627013630731</v>
+        <v>8.632075471698112</v>
       </c>
       <c r="AA3">
-        <v>-0.1195786864931846</v>
+        <v>-0.08490566037735849</v>
       </c>
       <c r="AB3">
-        <v>0.1204429910751101</v>
+        <v>0.3056370430666834</v>
       </c>
       <c r="AC3">
-        <v>-0.2400216775682947</v>
+        <v>-0.3905427034440419</v>
       </c>
       <c r="AD3">
-        <v>3.44</v>
+        <v>6.75</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.44</v>
+        <v>6.75</v>
       </c>
       <c r="AG3">
-        <v>1.55</v>
+        <v>3.67</v>
       </c>
       <c r="AH3">
-        <v>0.05354919053549191</v>
+        <v>0.2132701421800948</v>
       </c>
       <c r="AI3">
-        <v>0.416969696969697</v>
+        <v>0.7368995633187773</v>
       </c>
       <c r="AJ3">
-        <v>0.02485966319165999</v>
+        <v>0.1284564228211411</v>
       </c>
       <c r="AK3">
-        <v>0.2437106918238994</v>
+        <v>0.6036184210526315</v>
       </c>
       <c r="AL3">
-        <v>0.414</v>
+        <v>1.24</v>
       </c>
       <c r="AM3">
-        <v>0.389</v>
+        <v>1.108</v>
       </c>
       <c r="AN3">
-        <v>13.07984790874525</v>
+        <v>9.684361549497849</v>
       </c>
       <c r="AO3">
-        <v>-4.661835748792271</v>
+        <v>-0.435483870967742</v>
       </c>
       <c r="AP3">
-        <v>5.893536121673003</v>
+        <v>5.265423242467719</v>
       </c>
       <c r="AQ3">
-        <v>-4.961439588688946</v>
+        <v>-0.4873646209386281</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ghana/ghana_household_products.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_household_products.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ghse_unil" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,28 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00373</v>
+        <v>0.0767</v>
       </c>
       <c r="E2">
-        <v>-0.287</v>
+        <v>0.00263</v>
       </c>
       <c r="G2">
-        <v>-0.05938069216757741</v>
+        <v>0.07906040268456375</v>
       </c>
       <c r="H2">
-        <v>-0.05938069216757741</v>
+        <v>0.07906040268456375</v>
       </c>
       <c r="I2">
-        <v>-0.009836065573770493</v>
+        <v>0.1785234899328859</v>
       </c>
       <c r="J2">
-        <v>-0.009836065573770493</v>
+        <v>0.1600501896702655</v>
       </c>
       <c r="K2">
-        <v>0.878</v>
+        <v>10.3</v>
       </c>
       <c r="L2">
-        <v>0.01599271402550091</v>
+        <v>0.138255033557047</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.08</v>
+        <v>7.82</v>
       </c>
       <c r="V2">
-        <v>0.1236947791164659</v>
+        <v>0.1848699763593381</v>
       </c>
       <c r="W2">
-        <v>0.1825363825363825</v>
+        <v>4.273858921161826</v>
       </c>
       <c r="X2">
-        <v>0.3466837043904417</v>
+        <v>0.1732367967469674</v>
       </c>
       <c r="Y2">
-        <v>-0.1641473218540592</v>
+        <v>4.100622124414858</v>
       </c>
       <c r="Z2">
-        <v>8.632075471698112</v>
+        <v>12.25328947368421</v>
       </c>
       <c r="AA2">
-        <v>-0.08490566037735849</v>
+        <v>1.961141304347826</v>
       </c>
       <c r="AB2">
-        <v>0.3056370430666834</v>
+        <v>0.1709656889115508</v>
       </c>
       <c r="AC2">
-        <v>-0.3905427034440419</v>
+        <v>1.790175615436275</v>
       </c>
       <c r="AD2">
-        <v>6.75</v>
+        <v>1.88</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.75</v>
+        <v>1.88</v>
       </c>
       <c r="AG2">
-        <v>3.67</v>
+        <v>-5.94</v>
       </c>
       <c r="AH2">
-        <v>0.2132701421800948</v>
+        <v>0.0425531914893617</v>
       </c>
       <c r="AI2">
-        <v>0.7368995633187773</v>
+        <v>0.1307371349095967</v>
       </c>
       <c r="AJ2">
-        <v>0.1284564228211411</v>
+        <v>-0.1633663366336634</v>
       </c>
       <c r="AK2">
-        <v>0.6036184210526315</v>
+        <v>-0.9054878048780489</v>
       </c>
       <c r="AL2">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AM2">
-        <v>1.108</v>
+        <v>1.305</v>
       </c>
       <c r="AN2">
-        <v>9.684361549497849</v>
+        <v>0.1296551724137931</v>
       </c>
       <c r="AO2">
-        <v>-0.435483870967742</v>
+        <v>9.432624113475178</v>
       </c>
       <c r="AP2">
-        <v>5.265423242467719</v>
+        <v>-0.4096551724137931</v>
       </c>
       <c r="AQ2">
-        <v>-0.4873646209386281</v>
+        <v>10.19157088122605</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00373</v>
+        <v>0.0767</v>
       </c>
       <c r="E3">
-        <v>-0.287</v>
+        <v>0.00263</v>
       </c>
       <c r="G3">
-        <v>-0.05938069216757741</v>
+        <v>0.07906040268456375</v>
       </c>
       <c r="H3">
-        <v>-0.05938069216757741</v>
+        <v>0.07906040268456375</v>
       </c>
       <c r="I3">
-        <v>-0.009836065573770493</v>
+        <v>0.1785234899328859</v>
       </c>
       <c r="J3">
-        <v>-0.009836065573770493</v>
+        <v>0.1600501896702655</v>
       </c>
       <c r="K3">
-        <v>0.878</v>
+        <v>10.3</v>
       </c>
       <c r="L3">
-        <v>0.01599271402550091</v>
+        <v>0.138255033557047</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,73 +766,8845 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.08</v>
+        <v>7.82</v>
       </c>
       <c r="V3">
-        <v>0.1236947791164659</v>
+        <v>0.1848699763593381</v>
       </c>
       <c r="W3">
-        <v>0.1825363825363825</v>
+        <v>4.273858921161826</v>
       </c>
       <c r="X3">
-        <v>0.3466837043904417</v>
+        <v>0.1732367967469674</v>
       </c>
       <c r="Y3">
-        <v>-0.1641473218540592</v>
+        <v>4.100622124414858</v>
       </c>
       <c r="Z3">
-        <v>8.632075471698112</v>
+        <v>12.25328947368421</v>
       </c>
       <c r="AA3">
-        <v>-0.08490566037735849</v>
+        <v>1.961141304347826</v>
       </c>
       <c r="AB3">
-        <v>0.3056370430666834</v>
+        <v>0.1709656889115508</v>
       </c>
       <c r="AC3">
-        <v>-0.3905427034440419</v>
+        <v>1.790175615436275</v>
       </c>
       <c r="AD3">
-        <v>6.75</v>
+        <v>1.88</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.75</v>
+        <v>1.88</v>
       </c>
       <c r="AG3">
-        <v>3.67</v>
+        <v>-5.94</v>
       </c>
       <c r="AH3">
-        <v>0.2132701421800948</v>
+        <v>0.0425531914893617</v>
       </c>
       <c r="AI3">
-        <v>0.7368995633187773</v>
+        <v>0.1307371349095967</v>
       </c>
       <c r="AJ3">
-        <v>0.1284564228211411</v>
+        <v>-0.1633663366336634</v>
       </c>
       <c r="AK3">
-        <v>0.6036184210526315</v>
+        <v>-0.9054878048780489</v>
       </c>
       <c r="AL3">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AM3">
-        <v>1.108</v>
+        <v>1.305</v>
       </c>
       <c r="AN3">
-        <v>9.684361549497849</v>
+        <v>0.1296551724137931</v>
       </c>
       <c r="AO3">
-        <v>-0.435483870967742</v>
+        <v>9.432624113475178</v>
       </c>
       <c r="AP3">
-        <v>5.265423242467719</v>
+        <v>-0.4096551724137931</v>
       </c>
       <c r="AQ3">
-        <v>-0.4873646209386281</v>
+        <v>10.19157088122605</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unilever Ghana PLC (GHSE:UNIL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GHSE:UNIL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Household Products</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>9.43262411347518</v>
+      </c>
+      <c r="F2">
+        <v>6.20575541354174</v>
+      </c>
+      <c r="G2">
+        <v>0.129655172413793</v>
+      </c>
+      <c r="H2">
+        <v>2.98595862068965</v>
+      </c>
+      <c r="I2">
+        <v>0.0425531914893617</v>
+      </c>
+      <c r="J2">
+        <v>0.98</v>
+      </c>
+      <c r="K2">
+        <v>42.3</v>
+      </c>
+      <c r="L2">
+        <v>8.1663841475269</v>
+      </c>
+      <c r="M2">
+        <v>36.36</v>
+      </c>
+      <c r="N2">
+        <v>43.6427841475269</v>
+      </c>
+      <c r="O2">
+        <v>1.88</v>
+      </c>
+      <c r="P2">
+        <v>43.2964</v>
+      </c>
+      <c r="Q2">
+        <v>0.170965688911551</v>
+      </c>
+      <c r="R2">
+        <v>0.135384095042542</v>
+      </c>
+      <c r="S2">
+        <v>0.119865762614679</v>
+      </c>
+      <c r="T2">
+        <v>0.037125</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.173236796746967</v>
+      </c>
+      <c r="X2">
+        <v>4.95007975212711</v>
+      </c>
+      <c r="Y2">
+        <v>0.699170952607045</v>
+      </c>
+      <c r="Z2">
+        <v>25.5422936718541</v>
+      </c>
+      <c r="AA2">
+        <v>1.88</v>
+      </c>
+      <c r="AB2">
+        <v>0.1598210168195719</v>
+      </c>
+      <c r="AC2">
+        <v>9.432624113475178</v>
+      </c>
+      <c r="AD2">
+        <v>1.88</v>
+      </c>
+      <c r="AE2">
+        <v>1.41</v>
+      </c>
+      <c r="AF2">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="AG2">
+        <v>14.5</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>42.3</v>
+      </c>
+      <c r="AK2">
+        <v>0.1922802946056096</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>3.079999999999998</v>
+      </c>
+      <c r="AR2">
+        <v>1.41</v>
+      </c>
+      <c r="AS2">
+        <v>1.88</v>
+      </c>
+      <c r="AT2">
+        <v>7.82</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.168900125884162</v>
+      </c>
+      <c r="C2">
+        <v>44.53567187383592</v>
+      </c>
+      <c r="D2">
+        <v>36.71567187383592</v>
+      </c>
+      <c r="E2">
+        <v>-1.88</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>7.82</v>
+      </c>
+      <c r="H2">
+        <v>42.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>14.5</v>
+      </c>
+      <c r="K2">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L2">
+        <v>13.3</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>13.3</v>
+      </c>
+      <c r="O2">
+        <v>3.325</v>
+      </c>
+      <c r="P2">
+        <v>9.975000000000001</v>
+      </c>
+      <c r="Q2">
+        <v>11.175</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.168900125884162</v>
+      </c>
+      <c r="T2">
+        <v>0.6766170509100436</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.033525</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1685221255694516</v>
+      </c>
+      <c r="C3">
+        <v>44.15971477665532</v>
+      </c>
+      <c r="D3">
+        <v>36.78151477665532</v>
+      </c>
+      <c r="E3">
+        <v>-1.4382</v>
+      </c>
+      <c r="F3">
+        <v>0.4418</v>
+      </c>
+      <c r="G3">
+        <v>7.82</v>
+      </c>
+      <c r="H3">
+        <v>42.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>14.5</v>
+      </c>
+      <c r="K3">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L3">
+        <v>13.3</v>
+      </c>
+      <c r="M3">
+        <v>0.01974846</v>
+      </c>
+      <c r="N3">
+        <v>13.28025154</v>
+      </c>
+      <c r="O3">
+        <v>3.320062885</v>
+      </c>
+      <c r="P3">
+        <v>9.960188655</v>
+      </c>
+      <c r="Q3">
+        <v>11.160188655</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1698857328984359</v>
+      </c>
+      <c r="T3">
+        <v>0.6817429376593621</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.033525</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>673.4702351474494</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1681441252547412</v>
+      </c>
+      <c r="C4">
+        <v>43.78399425836054</v>
+      </c>
+      <c r="D4">
+        <v>36.84759425836054</v>
+      </c>
+      <c r="E4">
+        <v>-0.9963999999999998</v>
+      </c>
+      <c r="F4">
+        <v>0.8836000000000001</v>
+      </c>
+      <c r="G4">
+        <v>7.82</v>
+      </c>
+      <c r="H4">
+        <v>42.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>14.5</v>
+      </c>
+      <c r="K4">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L4">
+        <v>13.3</v>
+      </c>
+      <c r="M4">
+        <v>0.03949692</v>
+      </c>
+      <c r="N4">
+        <v>13.26050308</v>
+      </c>
+      <c r="O4">
+        <v>3.31512577</v>
+      </c>
+      <c r="P4">
+        <v>9.945377310000001</v>
+      </c>
+      <c r="Q4">
+        <v>11.14537731</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1708914543415726</v>
+      </c>
+      <c r="T4">
+        <v>0.6869734343423403</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.033525</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>336.7351175737247</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1677661249400307</v>
+      </c>
+      <c r="C5">
+        <v>43.40851159631708</v>
+      </c>
+      <c r="D5">
+        <v>36.91391159631709</v>
+      </c>
+      <c r="E5">
+        <v>-0.5546</v>
+      </c>
+      <c r="F5">
+        <v>1.3254</v>
+      </c>
+      <c r="G5">
+        <v>7.82</v>
+      </c>
+      <c r="H5">
+        <v>42.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>14.5</v>
+      </c>
+      <c r="K5">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L5">
+        <v>13.3</v>
+      </c>
+      <c r="M5">
+        <v>0.05924538</v>
+      </c>
+      <c r="N5">
+        <v>13.24075462</v>
+      </c>
+      <c r="O5">
+        <v>3.310188655</v>
+      </c>
+      <c r="P5">
+        <v>9.930565965</v>
+      </c>
+      <c r="Q5">
+        <v>11.130565965</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.17191791230931</v>
+      </c>
+      <c r="T5">
+        <v>0.6923117763177508</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.033525</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>224.4900783824832</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1673881246253204</v>
+      </c>
+      <c r="C6">
+        <v>43.0332680771029</v>
+      </c>
+      <c r="D6">
+        <v>36.9804680771029</v>
+      </c>
+      <c r="E6">
+        <v>-0.1127999999999998</v>
+      </c>
+      <c r="F6">
+        <v>1.7672</v>
+      </c>
+      <c r="G6">
+        <v>7.82</v>
+      </c>
+      <c r="H6">
+        <v>42.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>14.5</v>
+      </c>
+      <c r="K6">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L6">
+        <v>13.3</v>
+      </c>
+      <c r="M6">
+        <v>0.07899384000000001</v>
+      </c>
+      <c r="N6">
+        <v>13.22100616</v>
+      </c>
+      <c r="O6">
+        <v>3.30525154</v>
+      </c>
+      <c r="P6">
+        <v>9.91575462</v>
+      </c>
+      <c r="Q6">
+        <v>11.11575462</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.172965754818042</v>
+      </c>
+      <c r="T6">
+        <v>0.6977613337509825</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.033525</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>168.3675587868624</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1670101243106099</v>
+      </c>
+      <c r="C7">
+        <v>42.65826499659162</v>
+      </c>
+      <c r="D7">
+        <v>37.04726499659162</v>
+      </c>
+      <c r="E7">
+        <v>0.3290000000000002</v>
+      </c>
+      <c r="F7">
+        <v>2.209</v>
+      </c>
+      <c r="G7">
+        <v>7.82</v>
+      </c>
+      <c r="H7">
+        <v>42.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>14.5</v>
+      </c>
+      <c r="K7">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L7">
+        <v>13.3</v>
+      </c>
+      <c r="M7">
+        <v>0.09874230000000001</v>
+      </c>
+      <c r="N7">
+        <v>13.2012577</v>
+      </c>
+      <c r="O7">
+        <v>3.300314425</v>
+      </c>
+      <c r="P7">
+        <v>9.900943275000001</v>
+      </c>
+      <c r="Q7">
+        <v>11.100943275</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1740356571690631</v>
+      </c>
+      <c r="T7">
+        <v>0.7033256187091244</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.033525</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>134.6940470294899</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1666321239958995</v>
+      </c>
+      <c r="C8">
+        <v>42.28350366003662</v>
+      </c>
+      <c r="D8">
+        <v>37.11430366003661</v>
+      </c>
+      <c r="E8">
+        <v>0.7707999999999999</v>
+      </c>
+      <c r="F8">
+        <v>2.6508</v>
+      </c>
+      <c r="G8">
+        <v>7.82</v>
+      </c>
+      <c r="H8">
+        <v>42.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>14.5</v>
+      </c>
+      <c r="K8">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L8">
+        <v>13.3</v>
+      </c>
+      <c r="M8">
+        <v>0.11849076</v>
+      </c>
+      <c r="N8">
+        <v>13.18150924</v>
+      </c>
+      <c r="O8">
+        <v>3.29537731</v>
+      </c>
+      <c r="P8">
+        <v>9.886131930000001</v>
+      </c>
+      <c r="Q8">
+        <v>11.08613193</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1751283233998931</v>
+      </c>
+      <c r="T8">
+        <v>0.7090082927089287</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.033525</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>112.2450391912416</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1662541236811891</v>
+      </c>
+      <c r="C9">
+        <v>41.90898538215605</v>
+      </c>
+      <c r="D9">
+        <v>37.18158538215604</v>
+      </c>
+      <c r="E9">
+        <v>1.212600000000001</v>
+      </c>
+      <c r="F9">
+        <v>3.0926</v>
+      </c>
+      <c r="G9">
+        <v>7.82</v>
+      </c>
+      <c r="H9">
+        <v>42.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>14.5</v>
+      </c>
+      <c r="K9">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L9">
+        <v>13.3</v>
+      </c>
+      <c r="M9">
+        <v>0.13823922</v>
+      </c>
+      <c r="N9">
+        <v>13.16176078</v>
+      </c>
+      <c r="O9">
+        <v>3.290440195</v>
+      </c>
+      <c r="P9">
+        <v>9.871320584999999</v>
+      </c>
+      <c r="Q9">
+        <v>11.071320585</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1762444878292356</v>
+      </c>
+      <c r="T9">
+        <v>0.7148131747517397</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.033525</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>96.21003359249276</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1658761233664787</v>
+      </c>
+      <c r="C10">
+        <v>41.53471148721881</v>
+      </c>
+      <c r="D10">
+        <v>37.24911148721881</v>
+      </c>
+      <c r="E10">
+        <v>1.6544</v>
+      </c>
+      <c r="F10">
+        <v>3.5344</v>
+      </c>
+      <c r="G10">
+        <v>7.82</v>
+      </c>
+      <c r="H10">
+        <v>42.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>14.5</v>
+      </c>
+      <c r="K10">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L10">
+        <v>13.3</v>
+      </c>
+      <c r="M10">
+        <v>0.15798768</v>
+      </c>
+      <c r="N10">
+        <v>13.14201232</v>
+      </c>
+      <c r="O10">
+        <v>3.28550308</v>
+      </c>
+      <c r="P10">
+        <v>9.856509240000001</v>
+      </c>
+      <c r="Q10">
+        <v>11.05650924</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1773849167026943</v>
+      </c>
+      <c r="T10">
+        <v>0.7207442498824378</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.033525</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>84.18377939343118</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1654981230517683</v>
+      </c>
+      <c r="C11">
+        <v>41.1606833091314</v>
+      </c>
+      <c r="D11">
+        <v>37.3168833091314</v>
+      </c>
+      <c r="E11">
+        <v>2.0962</v>
+      </c>
+      <c r="F11">
+        <v>3.9762</v>
+      </c>
+      <c r="G11">
+        <v>7.82</v>
+      </c>
+      <c r="H11">
+        <v>42.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>14.5</v>
+      </c>
+      <c r="K11">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L11">
+        <v>13.3</v>
+      </c>
+      <c r="M11">
+        <v>0.17773614</v>
+      </c>
+      <c r="N11">
+        <v>13.12226386</v>
+      </c>
+      <c r="O11">
+        <v>3.280565965</v>
+      </c>
+      <c r="P11">
+        <v>9.841697894999999</v>
+      </c>
+      <c r="Q11">
+        <v>11.041697895</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1785504099469981</v>
+      </c>
+      <c r="T11">
+        <v>0.7268056783127117</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.033525</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>74.83002612749438</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1651201227370579</v>
+      </c>
+      <c r="C12">
+        <v>40.78690219152575</v>
+      </c>
+      <c r="D12">
+        <v>37.38490219152575</v>
+      </c>
+      <c r="E12">
+        <v>2.538</v>
+      </c>
+      <c r="F12">
+        <v>4.418</v>
+      </c>
+      <c r="G12">
+        <v>7.82</v>
+      </c>
+      <c r="H12">
+        <v>42.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>14.5</v>
+      </c>
+      <c r="K12">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L12">
+        <v>13.3</v>
+      </c>
+      <c r="M12">
+        <v>0.1974846</v>
+      </c>
+      <c r="N12">
+        <v>13.1025154</v>
+      </c>
+      <c r="O12">
+        <v>3.27562885</v>
+      </c>
+      <c r="P12">
+        <v>9.826886550000001</v>
+      </c>
+      <c r="Q12">
+        <v>11.02688655</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1797418030411755</v>
+      </c>
+      <c r="T12">
+        <v>0.7330018051525472</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.033525</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>67.34702351474495</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1647421224223475</v>
+      </c>
+      <c r="C13">
+        <v>40.41336948784809</v>
+      </c>
+      <c r="D13">
+        <v>37.45316948784809</v>
+      </c>
+      <c r="E13">
+        <v>2.9798</v>
+      </c>
+      <c r="F13">
+        <v>4.8598</v>
+      </c>
+      <c r="G13">
+        <v>7.82</v>
+      </c>
+      <c r="H13">
+        <v>42.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>14.5</v>
+      </c>
+      <c r="K13">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L13">
+        <v>13.3</v>
+      </c>
+      <c r="M13">
+        <v>0.21723306</v>
+      </c>
+      <c r="N13">
+        <v>13.08276694</v>
+      </c>
+      <c r="O13">
+        <v>3.270691735</v>
+      </c>
+      <c r="P13">
+        <v>9.812075205000001</v>
+      </c>
+      <c r="Q13">
+        <v>11.012075205</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1809599690138736</v>
+      </c>
+      <c r="T13">
+        <v>0.7393371707977725</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.033525</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>61.22456683158632</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1643641221076371</v>
+      </c>
+      <c r="C14">
+        <v>40.04008656144858</v>
+      </c>
+      <c r="D14">
+        <v>37.52168656144858</v>
+      </c>
+      <c r="E14">
+        <v>3.4216</v>
+      </c>
+      <c r="F14">
+        <v>5.3016</v>
+      </c>
+      <c r="G14">
+        <v>7.82</v>
+      </c>
+      <c r="H14">
+        <v>42.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>14.5</v>
+      </c>
+      <c r="K14">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L14">
+        <v>13.3</v>
+      </c>
+      <c r="M14">
+        <v>0.23698152</v>
+      </c>
+      <c r="N14">
+        <v>13.06301848</v>
+      </c>
+      <c r="O14">
+        <v>3.26575462</v>
+      </c>
+      <c r="P14">
+        <v>9.797263860000001</v>
+      </c>
+      <c r="Q14">
+        <v>10.99726386</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1822058205768604</v>
+      </c>
+      <c r="T14">
+        <v>0.7458165220258436</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.033525</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>56.12251959562079</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1639861217929267</v>
+      </c>
+      <c r="C15">
+        <v>39.66705478567219</v>
+      </c>
+      <c r="D15">
+        <v>37.59045478567219</v>
+      </c>
+      <c r="E15">
+        <v>3.8634</v>
+      </c>
+      <c r="F15">
+        <v>5.7434</v>
+      </c>
+      <c r="G15">
+        <v>7.82</v>
+      </c>
+      <c r="H15">
+        <v>42.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>14.5</v>
+      </c>
+      <c r="K15">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L15">
+        <v>13.3</v>
+      </c>
+      <c r="M15">
+        <v>0.25672998</v>
+      </c>
+      <c r="N15">
+        <v>13.04327002</v>
+      </c>
+      <c r="O15">
+        <v>3.260817505</v>
+      </c>
+      <c r="P15">
+        <v>9.782452515000001</v>
+      </c>
+      <c r="Q15">
+        <v>10.982452515</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1834803124056629</v>
+      </c>
+      <c r="T15">
+        <v>0.7524448238568588</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.033525</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>51.80540270364996</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1636081214782163</v>
+      </c>
+      <c r="C16">
+        <v>39.29427554395046</v>
+      </c>
+      <c r="D16">
+        <v>37.65947554395046</v>
+      </c>
+      <c r="E16">
+        <v>4.305200000000001</v>
+      </c>
+      <c r="F16">
+        <v>6.185200000000001</v>
+      </c>
+      <c r="G16">
+        <v>7.82</v>
+      </c>
+      <c r="H16">
+        <v>42.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>14.5</v>
+      </c>
+      <c r="K16">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L16">
+        <v>13.3</v>
+      </c>
+      <c r="M16">
+        <v>0.27647844</v>
+      </c>
+      <c r="N16">
+        <v>13.02352156</v>
+      </c>
+      <c r="O16">
+        <v>3.25588039</v>
+      </c>
+      <c r="P16">
+        <v>9.767641170000001</v>
+      </c>
+      <c r="Q16">
+        <v>10.96764117</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1847844435793213</v>
+      </c>
+      <c r="T16">
+        <v>0.7592272722420839</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.033525</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>48.10501679624639</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1632301211635059</v>
+      </c>
+      <c r="C17">
+        <v>38.92175022989416</v>
+      </c>
+      <c r="D17">
+        <v>37.72875022989416</v>
+      </c>
+      <c r="E17">
+        <v>4.747</v>
+      </c>
+      <c r="F17">
+        <v>6.627</v>
+      </c>
+      <c r="G17">
+        <v>7.82</v>
+      </c>
+      <c r="H17">
+        <v>42.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>14.5</v>
+      </c>
+      <c r="K17">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L17">
+        <v>13.3</v>
+      </c>
+      <c r="M17">
+        <v>0.2962269</v>
+      </c>
+      <c r="N17">
+        <v>13.0037731</v>
+      </c>
+      <c r="O17">
+        <v>3.250943275</v>
+      </c>
+      <c r="P17">
+        <v>9.752829824999999</v>
+      </c>
+      <c r="Q17">
+        <v>10.952829825</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1861192601923599</v>
+      </c>
+      <c r="T17">
+        <v>0.7661693076481376</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.033525</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>44.89801567649663</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1628521208487955</v>
+      </c>
+      <c r="C18">
+        <v>38.54948024738721</v>
+      </c>
+      <c r="D18">
+        <v>37.79828024738721</v>
+      </c>
+      <c r="E18">
+        <v>5.188800000000001</v>
+      </c>
+      <c r="F18">
+        <v>7.0688</v>
+      </c>
+      <c r="G18">
+        <v>7.82</v>
+      </c>
+      <c r="H18">
+        <v>42.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>14.5</v>
+      </c>
+      <c r="K18">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L18">
+        <v>13.3</v>
+      </c>
+      <c r="M18">
+        <v>0.31597536</v>
+      </c>
+      <c r="N18">
+        <v>12.98402464</v>
+      </c>
+      <c r="O18">
+        <v>3.24600616</v>
+      </c>
+      <c r="P18">
+        <v>9.738018480000001</v>
+      </c>
+      <c r="Q18">
+        <v>10.93801848</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1874858581533279</v>
+      </c>
+      <c r="T18">
+        <v>0.7732766296114784</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.033525</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>42.09188969671559</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1624741205340851</v>
+      </c>
+      <c r="C19">
+        <v>38.17746701068144</v>
+      </c>
+      <c r="D19">
+        <v>37.86806701068144</v>
+      </c>
+      <c r="E19">
+        <v>5.6306</v>
+      </c>
+      <c r="F19">
+        <v>7.5106</v>
+      </c>
+      <c r="G19">
+        <v>7.82</v>
+      </c>
+      <c r="H19">
+        <v>42.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>14.5</v>
+      </c>
+      <c r="K19">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L19">
+        <v>13.3</v>
+      </c>
+      <c r="M19">
+        <v>0.3357238200000001</v>
+      </c>
+      <c r="N19">
+        <v>12.96427618</v>
+      </c>
+      <c r="O19">
+        <v>3.241069045</v>
+      </c>
+      <c r="P19">
+        <v>9.723207135000001</v>
+      </c>
+      <c r="Q19">
+        <v>10.923207135</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1888853861856447</v>
+      </c>
+      <c r="T19">
+        <v>0.7805552123450203</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.033525</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>39.61589618514408</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1620961202193747</v>
+      </c>
+      <c r="C20">
+        <v>37.80571194449249</v>
+      </c>
+      <c r="D20">
+        <v>37.93811194449248</v>
+      </c>
+      <c r="E20">
+        <v>6.0724</v>
+      </c>
+      <c r="F20">
+        <v>7.9524</v>
+      </c>
+      <c r="G20">
+        <v>7.82</v>
+      </c>
+      <c r="H20">
+        <v>42.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>14.5</v>
+      </c>
+      <c r="K20">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L20">
+        <v>13.3</v>
+      </c>
+      <c r="M20">
+        <v>0.35547228</v>
+      </c>
+      <c r="N20">
+        <v>12.94452772</v>
+      </c>
+      <c r="O20">
+        <v>3.23613193</v>
+      </c>
+      <c r="P20">
+        <v>9.708395790000001</v>
+      </c>
+      <c r="Q20">
+        <v>10.90839579</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1903190490480179</v>
+      </c>
+      <c r="T20">
+        <v>0.7880113214866972</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.033525</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>37.41501306374719</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1617181199046643</v>
+      </c>
+      <c r="C21">
+        <v>37.43421648409682</v>
+      </c>
+      <c r="D21">
+        <v>38.00841648409681</v>
+      </c>
+      <c r="E21">
+        <v>6.5142</v>
+      </c>
+      <c r="F21">
+        <v>8.3942</v>
+      </c>
+      <c r="G21">
+        <v>7.82</v>
+      </c>
+      <c r="H21">
+        <v>42.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>14.5</v>
+      </c>
+      <c r="K21">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L21">
+        <v>13.3</v>
+      </c>
+      <c r="M21">
+        <v>0.37522074</v>
+      </c>
+      <c r="N21">
+        <v>12.92477926</v>
+      </c>
+      <c r="O21">
+        <v>3.231194815</v>
+      </c>
+      <c r="P21">
+        <v>9.693584445000001</v>
+      </c>
+      <c r="Q21">
+        <v>10.893584445</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1917881109934127</v>
+      </c>
+      <c r="T21">
+        <v>0.7956515320886626</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.033525</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>35.44580184986577</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1613401195899539</v>
+      </c>
+      <c r="C22">
+        <v>37.06298207542965</v>
+      </c>
+      <c r="D22">
+        <v>38.07898207542965</v>
+      </c>
+      <c r="E22">
+        <v>6.956</v>
+      </c>
+      <c r="F22">
+        <v>8.836</v>
+      </c>
+      <c r="G22">
+        <v>7.82</v>
+      </c>
+      <c r="H22">
+        <v>42.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>14.5</v>
+      </c>
+      <c r="K22">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L22">
+        <v>13.3</v>
+      </c>
+      <c r="M22">
+        <v>0.3949692</v>
+      </c>
+      <c r="N22">
+        <v>12.9050308</v>
+      </c>
+      <c r="O22">
+        <v>3.2262577</v>
+      </c>
+      <c r="P22">
+        <v>9.678773100000001</v>
+      </c>
+      <c r="Q22">
+        <v>10.8787731</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1932938994874424</v>
+      </c>
+      <c r="T22">
+        <v>0.8034827479556769</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.033525</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>33.67351175737247</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1609621192752435</v>
+      </c>
+      <c r="C23">
+        <v>36.69201017518419</v>
+      </c>
+      <c r="D23">
+        <v>38.14981017518419</v>
+      </c>
+      <c r="E23">
+        <v>7.397799999999999</v>
+      </c>
+      <c r="F23">
+        <v>9.277799999999999</v>
+      </c>
+      <c r="G23">
+        <v>7.82</v>
+      </c>
+      <c r="H23">
+        <v>42.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>14.5</v>
+      </c>
+      <c r="K23">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L23">
+        <v>13.3</v>
+      </c>
+      <c r="M23">
+        <v>0.41471766</v>
+      </c>
+      <c r="N23">
+        <v>12.88528234</v>
+      </c>
+      <c r="O23">
+        <v>3.221320585</v>
+      </c>
+      <c r="P23">
+        <v>9.663961754999999</v>
+      </c>
+      <c r="Q23">
+        <v>10.863961755</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1948378092091689</v>
+      </c>
+      <c r="T23">
+        <v>0.8115122224522359</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.033525</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>32.07001119749759</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1605841189605331</v>
+      </c>
+      <c r="C24">
+        <v>36.32130225091176</v>
+      </c>
+      <c r="D24">
+        <v>38.22090225091176</v>
+      </c>
+      <c r="E24">
+        <v>7.8396</v>
+      </c>
+      <c r="F24">
+        <v>9.7196</v>
+      </c>
+      <c r="G24">
+        <v>7.82</v>
+      </c>
+      <c r="H24">
+        <v>42.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>14.5</v>
+      </c>
+      <c r="K24">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L24">
+        <v>13.3</v>
+      </c>
+      <c r="M24">
+        <v>0.43446612</v>
+      </c>
+      <c r="N24">
+        <v>12.86553388</v>
+      </c>
+      <c r="O24">
+        <v>3.21638347</v>
+      </c>
+      <c r="P24">
+        <v>9.649150410000001</v>
+      </c>
+      <c r="Q24">
+        <v>10.84915041</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1964213063596578</v>
+      </c>
+      <c r="T24">
+        <v>0.8197475809102451</v>
+      </c>
+      <c r="U24">
+        <v>0.0447</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.033525</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>30.61228341579316</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1602061186458227</v>
+      </c>
+      <c r="C25">
+        <v>35.9508597811233</v>
+      </c>
+      <c r="D25">
+        <v>38.2922597811233</v>
+      </c>
+      <c r="E25">
+        <v>8.281400000000001</v>
+      </c>
+      <c r="F25">
+        <v>10.1614</v>
+      </c>
+      <c r="G25">
+        <v>7.82</v>
+      </c>
+      <c r="H25">
+        <v>42.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>14.5</v>
+      </c>
+      <c r="K25">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L25">
+        <v>13.3</v>
+      </c>
+      <c r="M25">
+        <v>0.45421458</v>
+      </c>
+      <c r="N25">
+        <v>12.84578542</v>
+      </c>
+      <c r="O25">
+        <v>3.211446355</v>
+      </c>
+      <c r="P25">
+        <v>9.634339065000001</v>
+      </c>
+      <c r="Q25">
+        <v>10.834339065</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1980459333062632</v>
+      </c>
+      <c r="T25">
+        <v>0.8281968447827482</v>
+      </c>
+      <c r="U25">
+        <v>0.0447</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.033525</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>29.28131457162824</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1598281183311122</v>
+      </c>
+      <c r="C26">
+        <v>35.58068425539171</v>
+      </c>
+      <c r="D26">
+        <v>38.36388425539171</v>
+      </c>
+      <c r="E26">
+        <v>8.723199999999999</v>
+      </c>
+      <c r="F26">
+        <v>10.6032</v>
+      </c>
+      <c r="G26">
+        <v>7.82</v>
+      </c>
+      <c r="H26">
+        <v>42.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>14.5</v>
+      </c>
+      <c r="K26">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L26">
+        <v>13.3</v>
+      </c>
+      <c r="M26">
+        <v>0.47396304</v>
+      </c>
+      <c r="N26">
+        <v>12.82603696</v>
+      </c>
+      <c r="O26">
+        <v>3.20650924</v>
+      </c>
+      <c r="P26">
+        <v>9.619527720000001</v>
+      </c>
+      <c r="Q26">
+        <v>10.81952772</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1997133135935688</v>
+      </c>
+      <c r="T26">
+        <v>0.8368684577045277</v>
+      </c>
+      <c r="U26">
+        <v>0.0447</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.033525</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>28.0612597978104</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1594501180164019</v>
+      </c>
+      <c r="C27">
+        <v>35.21077717445561</v>
+      </c>
+      <c r="D27">
+        <v>38.43577717445561</v>
+      </c>
+      <c r="E27">
+        <v>9.164999999999999</v>
+      </c>
+      <c r="F27">
+        <v>11.045</v>
+      </c>
+      <c r="G27">
+        <v>7.82</v>
+      </c>
+      <c r="H27">
+        <v>42.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>14.5</v>
+      </c>
+      <c r="K27">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L27">
+        <v>13.3</v>
+      </c>
+      <c r="M27">
+        <v>0.4937115</v>
+      </c>
+      <c r="N27">
+        <v>12.8062885</v>
+      </c>
+      <c r="O27">
+        <v>3.201572125</v>
+      </c>
+      <c r="P27">
+        <v>9.604716375000001</v>
+      </c>
+      <c r="Q27">
+        <v>10.804716375</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2014251573552024</v>
+      </c>
+      <c r="T27">
+        <v>0.8457713136375545</v>
+      </c>
+      <c r="U27">
+        <v>0.0447</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.033525</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>26.93880940589798</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1590721177016914</v>
+      </c>
+      <c r="C28">
+        <v>34.84114005032411</v>
+      </c>
+      <c r="D28">
+        <v>38.50794005032412</v>
+      </c>
+      <c r="E28">
+        <v>9.6068</v>
+      </c>
+      <c r="F28">
+        <v>11.4868</v>
+      </c>
+      <c r="G28">
+        <v>7.82</v>
+      </c>
+      <c r="H28">
+        <v>42.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>14.5</v>
+      </c>
+      <c r="K28">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L28">
+        <v>13.3</v>
+      </c>
+      <c r="M28">
+        <v>0.51345996</v>
+      </c>
+      <c r="N28">
+        <v>12.78654004</v>
+      </c>
+      <c r="O28">
+        <v>3.19663501</v>
+      </c>
+      <c r="P28">
+        <v>9.589905030000001</v>
+      </c>
+      <c r="Q28">
+        <v>10.78990503</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2031832671644479</v>
+      </c>
+      <c r="T28">
+        <v>0.8549147872985011</v>
+      </c>
+      <c r="U28">
+        <v>0.0447</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.033525</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>25.90270135182498</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1586941173869811</v>
+      </c>
+      <c r="C29">
+        <v>34.47177440638283</v>
+      </c>
+      <c r="D29">
+        <v>38.58037440638283</v>
+      </c>
+      <c r="E29">
+        <v>10.0486</v>
+      </c>
+      <c r="F29">
+        <v>11.9286</v>
+      </c>
+      <c r="G29">
+        <v>7.82</v>
+      </c>
+      <c r="H29">
+        <v>42.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>14.5</v>
+      </c>
+      <c r="K29">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L29">
+        <v>13.3</v>
+      </c>
+      <c r="M29">
+        <v>0.5332084200000001</v>
+      </c>
+      <c r="N29">
+        <v>12.76679158</v>
+      </c>
+      <c r="O29">
+        <v>3.191697895</v>
+      </c>
+      <c r="P29">
+        <v>9.575093685000001</v>
+      </c>
+      <c r="Q29">
+        <v>10.775093685</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2049895443657275</v>
+      </c>
+      <c r="T29">
+        <v>0.8643087670871449</v>
+      </c>
+      <c r="U29">
+        <v>0.0447</v>
+      </c>
+      <c r="V29">
+        <v>0.25</v>
+      </c>
+      <c r="W29">
+        <v>0.033525</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>24.94334204249813</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1583161170722706</v>
+      </c>
+      <c r="C30">
+        <v>34.10268177750108</v>
+      </c>
+      <c r="D30">
+        <v>38.65308177750109</v>
+      </c>
+      <c r="E30">
+        <v>10.4904</v>
+      </c>
+      <c r="F30">
+        <v>12.3704</v>
+      </c>
+      <c r="G30">
+        <v>7.82</v>
+      </c>
+      <c r="H30">
+        <v>42.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>14.5</v>
+      </c>
+      <c r="K30">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L30">
+        <v>13.3</v>
+      </c>
+      <c r="M30">
+        <v>0.5529568800000001</v>
+      </c>
+      <c r="N30">
+        <v>12.74704312</v>
+      </c>
+      <c r="O30">
+        <v>3.18676078</v>
+      </c>
+      <c r="P30">
+        <v>9.560282340000001</v>
+      </c>
+      <c r="Q30">
+        <v>10.76028234</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2068459959337092</v>
+      </c>
+      <c r="T30">
+        <v>0.8739636907588064</v>
+      </c>
+      <c r="U30">
+        <v>0.0447</v>
+      </c>
+      <c r="V30">
+        <v>0.25</v>
+      </c>
+      <c r="W30">
+        <v>0.033525</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>24.05250839812319</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1579381167575602</v>
+      </c>
+      <c r="C31">
+        <v>33.73386371014031</v>
+      </c>
+      <c r="D31">
+        <v>38.72606371014031</v>
+      </c>
+      <c r="E31">
+        <v>10.9322</v>
+      </c>
+      <c r="F31">
+        <v>12.8122</v>
+      </c>
+      <c r="G31">
+        <v>7.82</v>
+      </c>
+      <c r="H31">
+        <v>42.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>14.5</v>
+      </c>
+      <c r="K31">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L31">
+        <v>13.3</v>
+      </c>
+      <c r="M31">
+        <v>0.57270534</v>
+      </c>
+      <c r="N31">
+        <v>12.72729466</v>
+      </c>
+      <c r="O31">
+        <v>3.181823665</v>
+      </c>
+      <c r="P31">
+        <v>9.545470995000001</v>
+      </c>
+      <c r="Q31">
+        <v>10.745470995</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2087547419120566</v>
+      </c>
+      <c r="T31">
+        <v>0.8838905841113598</v>
+      </c>
+      <c r="U31">
+        <v>0.0447</v>
+      </c>
+      <c r="V31">
+        <v>0.25</v>
+      </c>
+      <c r="W31">
+        <v>0.033525</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>23.2231115568086</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1575601164428498</v>
+      </c>
+      <c r="C32">
+        <v>33.36532176246367</v>
+      </c>
+      <c r="D32">
+        <v>38.79932176246367</v>
+      </c>
+      <c r="E32">
+        <v>11.374</v>
+      </c>
+      <c r="F32">
+        <v>13.254</v>
+      </c>
+      <c r="G32">
+        <v>7.82</v>
+      </c>
+      <c r="H32">
+        <v>42.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>14.5</v>
+      </c>
+      <c r="K32">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L32">
+        <v>13.3</v>
+      </c>
+      <c r="M32">
+        <v>0.5924538</v>
+      </c>
+      <c r="N32">
+        <v>12.7075462</v>
+      </c>
+      <c r="O32">
+        <v>3.17688655</v>
+      </c>
+      <c r="P32">
+        <v>9.53065965</v>
+      </c>
+      <c r="Q32">
+        <v>10.73065965</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2107180234897855</v>
+      </c>
+      <c r="T32">
+        <v>0.8941011029882719</v>
+      </c>
+      <c r="U32">
+        <v>0.0447</v>
+      </c>
+      <c r="V32">
+        <v>0.25</v>
+      </c>
+      <c r="W32">
+        <v>0.033525</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>22.44900783824832</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1571821161281394</v>
+      </c>
+      <c r="C33">
+        <v>32.99705750444701</v>
+      </c>
+      <c r="D33">
+        <v>38.872857504447</v>
+      </c>
+      <c r="E33">
+        <v>11.8158</v>
+      </c>
+      <c r="F33">
+        <v>13.6958</v>
+      </c>
+      <c r="G33">
+        <v>7.82</v>
+      </c>
+      <c r="H33">
+        <v>42.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>14.5</v>
+      </c>
+      <c r="K33">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L33">
+        <v>13.3</v>
+      </c>
+      <c r="M33">
+        <v>0.6122022600000001</v>
+      </c>
+      <c r="N33">
+        <v>12.68779774</v>
+      </c>
+      <c r="O33">
+        <v>3.171949435</v>
+      </c>
+      <c r="P33">
+        <v>9.515848305</v>
+      </c>
+      <c r="Q33">
+        <v>10.715848305</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2127382117799122</v>
+      </c>
+      <c r="T33">
+        <v>0.9046075789340801</v>
+      </c>
+      <c r="U33">
+        <v>0.0447</v>
+      </c>
+      <c r="V33">
+        <v>0.25</v>
+      </c>
+      <c r="W33">
+        <v>0.033525</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>21.72484629507901</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.156804115813429</v>
+      </c>
+      <c r="C34">
+        <v>32.62907251799098</v>
+      </c>
+      <c r="D34">
+        <v>38.94667251799098</v>
+      </c>
+      <c r="E34">
+        <v>12.2576</v>
+      </c>
+      <c r="F34">
+        <v>14.1376</v>
+      </c>
+      <c r="G34">
+        <v>7.82</v>
+      </c>
+      <c r="H34">
+        <v>42.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>14.5</v>
+      </c>
+      <c r="K34">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L34">
+        <v>13.3</v>
+      </c>
+      <c r="M34">
+        <v>0.6319507200000001</v>
+      </c>
+      <c r="N34">
+        <v>12.66804928</v>
+      </c>
+      <c r="O34">
+        <v>3.16701232</v>
+      </c>
+      <c r="P34">
+        <v>9.50103696</v>
+      </c>
+      <c r="Q34">
+        <v>10.70103696</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2148178173726897</v>
+      </c>
+      <c r="T34">
+        <v>0.9154230688782944</v>
+      </c>
+      <c r="U34">
+        <v>0.0447</v>
+      </c>
+      <c r="V34">
+        <v>0.25</v>
+      </c>
+      <c r="W34">
+        <v>0.033525</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>21.0459448483578</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1564261154987186</v>
+      </c>
+      <c r="C35">
+        <v>32.26136839703442</v>
+      </c>
+      <c r="D35">
+        <v>39.02076839703442</v>
+      </c>
+      <c r="E35">
+        <v>12.6994</v>
+      </c>
+      <c r="F35">
+        <v>14.5794</v>
+      </c>
+      <c r="G35">
+        <v>7.82</v>
+      </c>
+      <c r="H35">
+        <v>42.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>14.5</v>
+      </c>
+      <c r="K35">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L35">
+        <v>13.3</v>
+      </c>
+      <c r="M35">
+        <v>0.6516991800000002</v>
+      </c>
+      <c r="N35">
+        <v>12.64830082</v>
+      </c>
+      <c r="O35">
+        <v>3.162075205</v>
+      </c>
+      <c r="P35">
+        <v>9.486225615</v>
+      </c>
+      <c r="Q35">
+        <v>10.686225615</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2169595007443561</v>
+      </c>
+      <c r="T35">
+        <v>0.9265614092686046</v>
+      </c>
+      <c r="U35">
+        <v>0.0447</v>
+      </c>
+      <c r="V35">
+        <v>0.25</v>
+      </c>
+      <c r="W35">
+        <v>0.033525</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>20.4081889438621</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1560481151840082</v>
+      </c>
+      <c r="C36">
+        <v>31.8939467476692</v>
+      </c>
+      <c r="D36">
+        <v>39.0951467476692</v>
+      </c>
+      <c r="E36">
+        <v>13.1412</v>
+      </c>
+      <c r="F36">
+        <v>15.0212</v>
+      </c>
+      <c r="G36">
+        <v>7.82</v>
+      </c>
+      <c r="H36">
+        <v>42.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>14.5</v>
+      </c>
+      <c r="K36">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L36">
+        <v>13.3</v>
+      </c>
+      <c r="M36">
+        <v>0.6714476400000001</v>
+      </c>
+      <c r="N36">
+        <v>12.62855236</v>
+      </c>
+      <c r="O36">
+        <v>3.15713809</v>
+      </c>
+      <c r="P36">
+        <v>9.47141427</v>
+      </c>
+      <c r="Q36">
+        <v>10.67141427</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2191660836121337</v>
+      </c>
+      <c r="T36">
+        <v>0.9380372751252879</v>
+      </c>
+      <c r="U36">
+        <v>0.0447</v>
+      </c>
+      <c r="V36">
+        <v>0.25</v>
+      </c>
+      <c r="W36">
+        <v>0.033525</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>19.80794809257204</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1556701148692978</v>
+      </c>
+      <c r="C37">
+        <v>31.52680918825618</v>
+      </c>
+      <c r="D37">
+        <v>39.16980918825618</v>
+      </c>
+      <c r="E37">
+        <v>13.583</v>
+      </c>
+      <c r="F37">
+        <v>15.463</v>
+      </c>
+      <c r="G37">
+        <v>7.82</v>
+      </c>
+      <c r="H37">
+        <v>42.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>14.5</v>
+      </c>
+      <c r="K37">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L37">
+        <v>13.3</v>
+      </c>
+      <c r="M37">
+        <v>0.6911961000000001</v>
+      </c>
+      <c r="N37">
+        <v>12.6088039</v>
+      </c>
+      <c r="O37">
+        <v>3.152200975</v>
+      </c>
+      <c r="P37">
+        <v>9.456602925</v>
+      </c>
+      <c r="Q37">
+        <v>10.656602925</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2214405613373812</v>
+      </c>
+      <c r="T37">
+        <v>0.9498662445467921</v>
+      </c>
+      <c r="U37">
+        <v>0.0447</v>
+      </c>
+      <c r="V37">
+        <v>0.25</v>
+      </c>
+      <c r="W37">
+        <v>0.033525</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>19.24200671849855</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1552921145545874</v>
+      </c>
+      <c r="C38">
+        <v>31.15995734954259</v>
+      </c>
+      <c r="D38">
+        <v>39.2447573495426</v>
+      </c>
+      <c r="E38">
+        <v>14.0248</v>
+      </c>
+      <c r="F38">
+        <v>15.9048</v>
+      </c>
+      <c r="G38">
+        <v>7.82</v>
+      </c>
+      <c r="H38">
+        <v>42.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>14.5</v>
+      </c>
+      <c r="K38">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L38">
+        <v>13.3</v>
+      </c>
+      <c r="M38">
+        <v>0.7109445600000001</v>
+      </c>
+      <c r="N38">
+        <v>12.58905544</v>
+      </c>
+      <c r="O38">
+        <v>3.14726386</v>
+      </c>
+      <c r="P38">
+        <v>9.44179158</v>
+      </c>
+      <c r="Q38">
+        <v>10.64179158</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2237861164915428</v>
+      </c>
+      <c r="T38">
+        <v>0.9620648692627183</v>
+      </c>
+      <c r="U38">
+        <v>0.0447</v>
+      </c>
+      <c r="V38">
+        <v>0.25</v>
+      </c>
+      <c r="W38">
+        <v>0.033525</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>18.7075065318736</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.154914114239877</v>
+      </c>
+      <c r="C39">
+        <v>30.79339287478083</v>
+      </c>
+      <c r="D39">
+        <v>39.31999287478083</v>
+      </c>
+      <c r="E39">
+        <v>14.4666</v>
+      </c>
+      <c r="F39">
+        <v>16.3466</v>
+      </c>
+      <c r="G39">
+        <v>7.82</v>
+      </c>
+      <c r="H39">
+        <v>42.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>14.5</v>
+      </c>
+      <c r="K39">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L39">
+        <v>13.3</v>
+      </c>
+      <c r="M39">
+        <v>0.73069302</v>
+      </c>
+      <c r="N39">
+        <v>12.56930698</v>
+      </c>
+      <c r="O39">
+        <v>3.142326745</v>
+      </c>
+      <c r="P39">
+        <v>9.426980235</v>
+      </c>
+      <c r="Q39">
+        <v>10.626980235</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2262061337140905</v>
+      </c>
+      <c r="T39">
+        <v>0.9746507519061343</v>
+      </c>
+      <c r="U39">
+        <v>0.0447</v>
+      </c>
+      <c r="V39">
+        <v>0.25</v>
+      </c>
+      <c r="W39">
+        <v>0.033525</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>18.20189824722836</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1545361139251666</v>
+      </c>
+      <c r="C40">
+        <v>30.42711741984848</v>
+      </c>
+      <c r="D40">
+        <v>39.39551741984847</v>
+      </c>
+      <c r="E40">
+        <v>14.9084</v>
+      </c>
+      <c r="F40">
+        <v>16.7884</v>
+      </c>
+      <c r="G40">
+        <v>7.82</v>
+      </c>
+      <c r="H40">
+        <v>42.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>14.5</v>
+      </c>
+      <c r="K40">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L40">
+        <v>13.3</v>
+      </c>
+      <c r="M40">
+        <v>0.75044148</v>
+      </c>
+      <c r="N40">
+        <v>12.54955852</v>
+      </c>
+      <c r="O40">
+        <v>3.13738963</v>
+      </c>
+      <c r="P40">
+        <v>9.41216889</v>
+      </c>
+      <c r="Q40">
+        <v>10.61216889</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2287042160083332</v>
+      </c>
+      <c r="T40">
+        <v>0.9876426307638541</v>
+      </c>
+      <c r="U40">
+        <v>0.0447</v>
+      </c>
+      <c r="V40">
+        <v>0.25</v>
+      </c>
+      <c r="W40">
+        <v>0.033525</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>17.72290092493288</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1541581136104562</v>
+      </c>
+      <c r="C41">
+        <v>30.06113265336984</v>
+      </c>
+      <c r="D41">
+        <v>39.47133265336983</v>
+      </c>
+      <c r="E41">
+        <v>15.3502</v>
+      </c>
+      <c r="F41">
+        <v>17.2302</v>
+      </c>
+      <c r="G41">
+        <v>7.82</v>
+      </c>
+      <c r="H41">
+        <v>42.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>14.5</v>
+      </c>
+      <c r="K41">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L41">
+        <v>13.3</v>
+      </c>
+      <c r="M41">
+        <v>0.7701899400000001</v>
+      </c>
+      <c r="N41">
+        <v>12.52981006</v>
+      </c>
+      <c r="O41">
+        <v>3.132452515</v>
+      </c>
+      <c r="P41">
+        <v>9.397357545</v>
+      </c>
+      <c r="Q41">
+        <v>10.597357545</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2312842026400921</v>
+      </c>
+      <c r="T41">
+        <v>1.001060472862811</v>
+      </c>
+      <c r="U41">
+        <v>0.0447</v>
+      </c>
+      <c r="V41">
+        <v>0.25</v>
+      </c>
+      <c r="W41">
+        <v>0.033525</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>17.26846756788332</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1537801132957458</v>
+      </c>
+      <c r="C42">
+        <v>29.69544025683878</v>
+      </c>
+      <c r="D42">
+        <v>39.54744025683878</v>
+      </c>
+      <c r="E42">
+        <v>15.792</v>
+      </c>
+      <c r="F42">
+        <v>17.672</v>
+      </c>
+      <c r="G42">
+        <v>7.82</v>
+      </c>
+      <c r="H42">
+        <v>42.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>14.5</v>
+      </c>
+      <c r="K42">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L42">
+        <v>13.3</v>
+      </c>
+      <c r="M42">
+        <v>0.7899384</v>
+      </c>
+      <c r="N42">
+        <v>12.5100616</v>
+      </c>
+      <c r="O42">
+        <v>3.1275154</v>
+      </c>
+      <c r="P42">
+        <v>9.3825462</v>
+      </c>
+      <c r="Q42">
+        <v>10.5825462</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.233950188826243</v>
+      </c>
+      <c r="T42">
+        <v>1.014925576365066</v>
+      </c>
+      <c r="U42">
+        <v>0.0447</v>
+      </c>
+      <c r="V42">
+        <v>0.25</v>
+      </c>
+      <c r="W42">
+        <v>0.033525</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>16.83675587868624</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1534021129810353</v>
+      </c>
+      <c r="C43">
+        <v>29.33004192474312</v>
+      </c>
+      <c r="D43">
+        <v>39.62384192474313</v>
+      </c>
+      <c r="E43">
+        <v>16.2338</v>
+      </c>
+      <c r="F43">
+        <v>18.1138</v>
+      </c>
+      <c r="G43">
+        <v>7.82</v>
+      </c>
+      <c r="H43">
+        <v>42.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>14.5</v>
+      </c>
+      <c r="K43">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L43">
+        <v>13.3</v>
+      </c>
+      <c r="M43">
+        <v>0.8096868600000001</v>
+      </c>
+      <c r="N43">
+        <v>12.49031314</v>
+      </c>
+      <c r="O43">
+        <v>3.122578285</v>
+      </c>
+      <c r="P43">
+        <v>9.367734855000002</v>
+      </c>
+      <c r="Q43">
+        <v>10.567734855</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2367065474254837</v>
+      </c>
+      <c r="T43">
+        <v>1.029260683375872</v>
+      </c>
+      <c r="U43">
+        <v>0.0447</v>
+      </c>
+      <c r="V43">
+        <v>0.25</v>
+      </c>
+      <c r="W43">
+        <v>0.033525</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>16.42610329627925</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.153024112666325</v>
+      </c>
+      <c r="C44">
+        <v>28.96493936469033</v>
+      </c>
+      <c r="D44">
+        <v>39.70053936469033</v>
+      </c>
+      <c r="E44">
+        <v>16.6756</v>
+      </c>
+      <c r="F44">
+        <v>18.5556</v>
+      </c>
+      <c r="G44">
+        <v>7.82</v>
+      </c>
+      <c r="H44">
+        <v>42.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>14.5</v>
+      </c>
+      <c r="K44">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L44">
+        <v>13.3</v>
+      </c>
+      <c r="M44">
+        <v>0.82943532</v>
+      </c>
+      <c r="N44">
+        <v>12.47056468</v>
+      </c>
+      <c r="O44">
+        <v>3.11764117</v>
+      </c>
+      <c r="P44">
+        <v>9.35292351</v>
+      </c>
+      <c r="Q44">
+        <v>10.55292351</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2395579528729741</v>
+      </c>
+      <c r="T44">
+        <v>1.044090104421533</v>
+      </c>
+      <c r="U44">
+        <v>0.0447</v>
+      </c>
+      <c r="V44">
+        <v>0.25</v>
+      </c>
+      <c r="W44">
+        <v>0.033525</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>16.0350055987488</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1526461123516146</v>
+      </c>
+      <c r="C45">
+        <v>28.60013429753474</v>
+      </c>
+      <c r="D45">
+        <v>39.77753429753474</v>
+      </c>
+      <c r="E45">
+        <v>17.1174</v>
+      </c>
+      <c r="F45">
+        <v>18.9974</v>
+      </c>
+      <c r="G45">
+        <v>7.82</v>
+      </c>
+      <c r="H45">
+        <v>42.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>14.5</v>
+      </c>
+      <c r="K45">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L45">
+        <v>13.3</v>
+      </c>
+      <c r="M45">
+        <v>0.8491837800000001</v>
+      </c>
+      <c r="N45">
+        <v>12.45081622</v>
+      </c>
+      <c r="O45">
+        <v>3.112704055</v>
+      </c>
+      <c r="P45">
+        <v>9.338112165</v>
+      </c>
+      <c r="Q45">
+        <v>10.538112165</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2425094076344115</v>
+      </c>
+      <c r="T45">
+        <v>1.0594398560302</v>
+      </c>
+      <c r="U45">
+        <v>0.0447</v>
+      </c>
+      <c r="V45">
+        <v>0.25</v>
+      </c>
+      <c r="W45">
+        <v>0.033525</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>15.66209849180115</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1522681120369042</v>
+      </c>
+      <c r="C46">
+        <v>28.23562845750628</v>
+      </c>
+      <c r="D46">
+        <v>39.85482845750628</v>
+      </c>
+      <c r="E46">
+        <v>17.5592</v>
+      </c>
+      <c r="F46">
+        <v>19.4392</v>
+      </c>
+      <c r="G46">
+        <v>7.82</v>
+      </c>
+      <c r="H46">
+        <v>42.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>14.5</v>
+      </c>
+      <c r="K46">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L46">
+        <v>13.3</v>
+      </c>
+      <c r="M46">
+        <v>0.86893224</v>
+      </c>
+      <c r="N46">
+        <v>12.43106776</v>
+      </c>
+      <c r="O46">
+        <v>3.10776694</v>
+      </c>
+      <c r="P46">
+        <v>9.32330082</v>
+      </c>
+      <c r="Q46">
+        <v>10.52330082</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2455662714944717</v>
+      </c>
+      <c r="T46">
+        <v>1.075337813053462</v>
+      </c>
+      <c r="U46">
+        <v>0.0447</v>
+      </c>
+      <c r="V46">
+        <v>0.25</v>
+      </c>
+      <c r="W46">
+        <v>0.033525</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>15.30614170789658</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1518901117221937</v>
+      </c>
+      <c r="C47">
+        <v>27.8714235923407</v>
+      </c>
+      <c r="D47">
+        <v>39.9324235923407</v>
+      </c>
+      <c r="E47">
+        <v>18.001</v>
+      </c>
+      <c r="F47">
+        <v>19.881</v>
+      </c>
+      <c r="G47">
+        <v>7.82</v>
+      </c>
+      <c r="H47">
+        <v>42.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>14.5</v>
+      </c>
+      <c r="K47">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L47">
+        <v>13.3</v>
+      </c>
+      <c r="M47">
+        <v>0.8886807000000001</v>
+      </c>
+      <c r="N47">
+        <v>12.4113193</v>
+      </c>
+      <c r="O47">
+        <v>3.102829825</v>
+      </c>
+      <c r="P47">
+        <v>9.308489475</v>
+      </c>
+      <c r="Q47">
+        <v>10.508489475</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2487342940403523</v>
+      </c>
+      <c r="T47">
+        <v>1.091813877604843</v>
+      </c>
+      <c r="U47">
+        <v>0.0447</v>
+      </c>
+      <c r="V47">
+        <v>0.25</v>
+      </c>
+      <c r="W47">
+        <v>0.033525</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>14.96600522549888</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1515121114074833</v>
+      </c>
+      <c r="C48">
+        <v>27.50752146341125</v>
+      </c>
+      <c r="D48">
+        <v>40.01032146341125</v>
+      </c>
+      <c r="E48">
+        <v>18.4428</v>
+      </c>
+      <c r="F48">
+        <v>20.3228</v>
+      </c>
+      <c r="G48">
+        <v>7.82</v>
+      </c>
+      <c r="H48">
+        <v>42.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>14.5</v>
+      </c>
+      <c r="K48">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L48">
+        <v>13.3</v>
+      </c>
+      <c r="M48">
+        <v>0.9084291600000001</v>
+      </c>
+      <c r="N48">
+        <v>12.39157084</v>
+      </c>
+      <c r="O48">
+        <v>3.09789271</v>
+      </c>
+      <c r="P48">
+        <v>9.29367813</v>
+      </c>
+      <c r="Q48">
+        <v>10.49367813</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2520196507545988</v>
+      </c>
+      <c r="T48">
+        <v>1.108900166769238</v>
+      </c>
+      <c r="U48">
+        <v>0.0447</v>
+      </c>
+      <c r="V48">
+        <v>0.25</v>
+      </c>
+      <c r="W48">
+        <v>0.033525</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>14.64065728581412</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1511341110927729</v>
+      </c>
+      <c r="C49">
+        <v>27.14392384586201</v>
+      </c>
+      <c r="D49">
+        <v>40.08852384586201</v>
+      </c>
+      <c r="E49">
+        <v>18.8846</v>
+      </c>
+      <c r="F49">
+        <v>20.7646</v>
+      </c>
+      <c r="G49">
+        <v>7.82</v>
+      </c>
+      <c r="H49">
+        <v>42.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>14.5</v>
+      </c>
+      <c r="K49">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L49">
+        <v>13.3</v>
+      </c>
+      <c r="M49">
+        <v>0.9281776200000001</v>
+      </c>
+      <c r="N49">
+        <v>12.37182238</v>
+      </c>
+      <c r="O49">
+        <v>3.092955595</v>
+      </c>
+      <c r="P49">
+        <v>9.278866785000002</v>
+      </c>
+      <c r="Q49">
+        <v>10.478866785</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2554289831939112</v>
+      </c>
+      <c r="T49">
+        <v>1.126631221562478</v>
+      </c>
+      <c r="U49">
+        <v>0.0447</v>
+      </c>
+      <c r="V49">
+        <v>0.25</v>
+      </c>
+      <c r="W49">
+        <v>0.033525</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>14.32915393930744</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1507561107780625</v>
+      </c>
+      <c r="C50">
+        <v>26.78063252874269</v>
+      </c>
+      <c r="D50">
+        <v>40.16703252874269</v>
+      </c>
+      <c r="E50">
+        <v>19.3264</v>
+      </c>
+      <c r="F50">
+        <v>21.2064</v>
+      </c>
+      <c r="G50">
+        <v>7.82</v>
+      </c>
+      <c r="H50">
+        <v>42.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>14.5</v>
+      </c>
+      <c r="K50">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L50">
+        <v>13.3</v>
+      </c>
+      <c r="M50">
+        <v>0.94792608</v>
+      </c>
+      <c r="N50">
+        <v>12.35207392</v>
+      </c>
+      <c r="O50">
+        <v>3.08801848</v>
+      </c>
+      <c r="P50">
+        <v>9.26405544</v>
+      </c>
+      <c r="Q50">
+        <v>10.46405544</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2589694438039664</v>
+      </c>
+      <c r="T50">
+        <v>1.145044240001612</v>
+      </c>
+      <c r="U50">
+        <v>0.0447</v>
+      </c>
+      <c r="V50">
+        <v>0.25</v>
+      </c>
+      <c r="W50">
+        <v>0.033525</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>14.0306298989052</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1503781104633521</v>
+      </c>
+      <c r="C51">
+        <v>26.41764931514507</v>
+      </c>
+      <c r="D51">
+        <v>40.24584931514507</v>
+      </c>
+      <c r="E51">
+        <v>19.7682</v>
+      </c>
+      <c r="F51">
+        <v>21.6482</v>
+      </c>
+      <c r="G51">
+        <v>7.82</v>
+      </c>
+      <c r="H51">
+        <v>42.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>14.5</v>
+      </c>
+      <c r="K51">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L51">
+        <v>13.3</v>
+      </c>
+      <c r="M51">
+        <v>0.9676745400000001</v>
+      </c>
+      <c r="N51">
+        <v>12.33232546</v>
+      </c>
+      <c r="O51">
+        <v>3.083081365</v>
+      </c>
+      <c r="P51">
+        <v>9.249244095</v>
+      </c>
+      <c r="Q51">
+        <v>10.449244095</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2626487460065728</v>
+      </c>
+      <c r="T51">
+        <v>1.164179337595222</v>
+      </c>
+      <c r="U51">
+        <v>0.0447</v>
+      </c>
+      <c r="V51">
+        <v>0.25</v>
+      </c>
+      <c r="W51">
+        <v>0.033525</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>13.74429051321325</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1500001101486417</v>
+      </c>
+      <c r="C52">
+        <v>26.05497602234106</v>
+      </c>
+      <c r="D52">
+        <v>40.32497602234106</v>
+      </c>
+      <c r="E52">
+        <v>20.21</v>
+      </c>
+      <c r="F52">
+        <v>22.09</v>
+      </c>
+      <c r="G52">
+        <v>7.82</v>
+      </c>
+      <c r="H52">
+        <v>42.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>14.5</v>
+      </c>
+      <c r="K52">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L52">
+        <v>13.3</v>
+      </c>
+      <c r="M52">
+        <v>0.9874230000000001</v>
+      </c>
+      <c r="N52">
+        <v>12.312577</v>
+      </c>
+      <c r="O52">
+        <v>3.07814425</v>
+      </c>
+      <c r="P52">
+        <v>9.23443275</v>
+      </c>
+      <c r="Q52">
+        <v>10.43443275</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2664752202972834</v>
+      </c>
+      <c r="T52">
+        <v>1.184079839092576</v>
+      </c>
+      <c r="U52">
+        <v>0.0447</v>
+      </c>
+      <c r="V52">
+        <v>0.25</v>
+      </c>
+      <c r="W52">
+        <v>0.033525</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>13.46940470294899</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1496221098339313</v>
+      </c>
+      <c r="C53">
+        <v>25.69261448192237</v>
+      </c>
+      <c r="D53">
+        <v>40.40441448192237</v>
+      </c>
+      <c r="E53">
+        <v>20.6518</v>
+      </c>
+      <c r="F53">
+        <v>22.5318</v>
+      </c>
+      <c r="G53">
+        <v>7.82</v>
+      </c>
+      <c r="H53">
+        <v>42.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>14.5</v>
+      </c>
+      <c r="K53">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L53">
+        <v>13.3</v>
+      </c>
+      <c r="M53">
+        <v>1.00717146</v>
+      </c>
+      <c r="N53">
+        <v>12.29282854</v>
+      </c>
+      <c r="O53">
+        <v>3.073207135</v>
+      </c>
+      <c r="P53">
+        <v>9.219621405</v>
+      </c>
+      <c r="Q53">
+        <v>10.419621405</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2704578772121047</v>
+      </c>
+      <c r="T53">
+        <v>1.20479260595717</v>
+      </c>
+      <c r="U53">
+        <v>0.0447</v>
+      </c>
+      <c r="V53">
+        <v>0.25</v>
+      </c>
+      <c r="W53">
+        <v>0.033525</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>13.20529872838136</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1492441095192209</v>
+      </c>
+      <c r="C54">
+        <v>25.3305665399418</v>
+      </c>
+      <c r="D54">
+        <v>40.4841665399418</v>
+      </c>
+      <c r="E54">
+        <v>21.0936</v>
+      </c>
+      <c r="F54">
+        <v>22.9736</v>
+      </c>
+      <c r="G54">
+        <v>7.82</v>
+      </c>
+      <c r="H54">
+        <v>42.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>14.5</v>
+      </c>
+      <c r="K54">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L54">
+        <v>13.3</v>
+      </c>
+      <c r="M54">
+        <v>1.02691992</v>
+      </c>
+      <c r="N54">
+        <v>12.27308008</v>
+      </c>
+      <c r="O54">
+        <v>3.06827002</v>
+      </c>
+      <c r="P54">
+        <v>9.20481006</v>
+      </c>
+      <c r="Q54">
+        <v>10.40481006</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2746064781650436</v>
+      </c>
+      <c r="T54">
+        <v>1.226368404774454</v>
+      </c>
+      <c r="U54">
+        <v>0.0447</v>
+      </c>
+      <c r="V54">
+        <v>0.25</v>
+      </c>
+      <c r="W54">
+        <v>0.033525</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>12.95135067591249</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1493033592045105</v>
+      </c>
+      <c r="C55">
+        <v>24.87624499764778</v>
+      </c>
+      <c r="D55">
+        <v>40.47164499764779</v>
+      </c>
+      <c r="E55">
+        <v>21.5354</v>
+      </c>
+      <c r="F55">
+        <v>23.4154</v>
+      </c>
+      <c r="G55">
+        <v>7.82</v>
+      </c>
+      <c r="H55">
+        <v>42.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>14.5</v>
+      </c>
+      <c r="K55">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L55">
+        <v>13.3</v>
+      </c>
+      <c r="M55">
+        <v>1.07242532</v>
+      </c>
+      <c r="N55">
+        <v>12.22757468</v>
+      </c>
+      <c r="O55">
+        <v>3.05689367</v>
+      </c>
+      <c r="P55">
+        <v>9.170681009999999</v>
+      </c>
+      <c r="Q55">
+        <v>10.37068101</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2789316153287458</v>
+      </c>
+      <c r="T55">
+        <v>1.248862322690347</v>
+      </c>
+      <c r="U55">
+        <v>0.0458</v>
+      </c>
+      <c r="V55">
+        <v>0.25</v>
+      </c>
+      <c r="W55">
+        <v>0.03435</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>12.40179595908832</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1489336088898001</v>
+      </c>
+      <c r="C56">
+        <v>24.51271314514343</v>
+      </c>
+      <c r="D56">
+        <v>40.54991314514344</v>
+      </c>
+      <c r="E56">
+        <v>21.9772</v>
+      </c>
+      <c r="F56">
+        <v>23.8572</v>
+      </c>
+      <c r="G56">
+        <v>7.82</v>
+      </c>
+      <c r="H56">
+        <v>42.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>14.5</v>
+      </c>
+      <c r="K56">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L56">
+        <v>13.3</v>
+      </c>
+      <c r="M56">
+        <v>1.09265976</v>
+      </c>
+      <c r="N56">
+        <v>12.20734024</v>
+      </c>
+      <c r="O56">
+        <v>3.05183506</v>
+      </c>
+      <c r="P56">
+        <v>9.15550518</v>
+      </c>
+      <c r="Q56">
+        <v>10.35550518</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2834448019343481</v>
+      </c>
+      <c r="T56">
+        <v>1.272334237037365</v>
+      </c>
+      <c r="U56">
+        <v>0.0458</v>
+      </c>
+      <c r="V56">
+        <v>0.25</v>
+      </c>
+      <c r="W56">
+        <v>0.03435</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>12.17213307095706</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1485638585750897</v>
+      </c>
+      <c r="C57">
+        <v>24.14948460488433</v>
+      </c>
+      <c r="D57">
+        <v>40.62848460488433</v>
+      </c>
+      <c r="E57">
+        <v>22.419</v>
+      </c>
+      <c r="F57">
+        <v>24.299</v>
+      </c>
+      <c r="G57">
+        <v>7.82</v>
+      </c>
+      <c r="H57">
+        <v>42.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>14.5</v>
+      </c>
+      <c r="K57">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L57">
+        <v>13.3</v>
+      </c>
+      <c r="M57">
+        <v>1.1128942</v>
+      </c>
+      <c r="N57">
+        <v>12.1871058</v>
+      </c>
+      <c r="O57">
+        <v>3.04677645</v>
+      </c>
+      <c r="P57">
+        <v>9.140329350000002</v>
+      </c>
+      <c r="Q57">
+        <v>10.34032935</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2881585746113105</v>
+      </c>
+      <c r="T57">
+        <v>1.296849347577584</v>
+      </c>
+      <c r="U57">
+        <v>0.0458</v>
+      </c>
+      <c r="V57">
+        <v>0.25</v>
+      </c>
+      <c r="W57">
+        <v>0.03435</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>11.95082156057602</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1481941082603793</v>
+      </c>
+      <c r="C58">
+        <v>23.78656114343056</v>
+      </c>
+      <c r="D58">
+        <v>40.70736114343057</v>
+      </c>
+      <c r="E58">
+        <v>22.8608</v>
+      </c>
+      <c r="F58">
+        <v>24.7408</v>
+      </c>
+      <c r="G58">
+        <v>7.82</v>
+      </c>
+      <c r="H58">
+        <v>42.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>14.5</v>
+      </c>
+      <c r="K58">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L58">
+        <v>13.3</v>
+      </c>
+      <c r="M58">
+        <v>1.13312864</v>
+      </c>
+      <c r="N58">
+        <v>12.16687136</v>
+      </c>
+      <c r="O58">
+        <v>3.04171784</v>
+      </c>
+      <c r="P58">
+        <v>9.12515352</v>
+      </c>
+      <c r="Q58">
+        <v>10.32515352</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2930866096826802</v>
+      </c>
+      <c r="T58">
+        <v>1.322478781324176</v>
+      </c>
+      <c r="U58">
+        <v>0.0458</v>
+      </c>
+      <c r="V58">
+        <v>0.25</v>
+      </c>
+      <c r="W58">
+        <v>0.03435</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>11.73741403270859</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1478243579456689</v>
+      </c>
+      <c r="C59">
+        <v>23.42394454108738</v>
+      </c>
+      <c r="D59">
+        <v>40.78654454108739</v>
+      </c>
+      <c r="E59">
+        <v>23.30260000000001</v>
+      </c>
+      <c r="F59">
+        <v>25.1826</v>
+      </c>
+      <c r="G59">
+        <v>7.82</v>
+      </c>
+      <c r="H59">
+        <v>42.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>14.5</v>
+      </c>
+      <c r="K59">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L59">
+        <v>13.3</v>
+      </c>
+      <c r="M59">
+        <v>1.15336308</v>
+      </c>
+      <c r="N59">
+        <v>12.14663692</v>
+      </c>
+      <c r="O59">
+        <v>3.03665923</v>
+      </c>
+      <c r="P59">
+        <v>9.109977690000001</v>
+      </c>
+      <c r="Q59">
+        <v>10.30997769</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2982438556876021</v>
+      </c>
+      <c r="T59">
+        <v>1.349300281756657</v>
+      </c>
+      <c r="U59">
+        <v>0.0458</v>
+      </c>
+      <c r="V59">
+        <v>0.25</v>
+      </c>
+      <c r="W59">
+        <v>0.03435</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>11.5314944882751</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1474546076309585</v>
+      </c>
+      <c r="C60">
+        <v>23.06163659203916</v>
+      </c>
+      <c r="D60">
+        <v>40.86603659203916</v>
+      </c>
+      <c r="E60">
+        <v>23.7444</v>
+      </c>
+      <c r="F60">
+        <v>25.6244</v>
+      </c>
+      <c r="G60">
+        <v>7.82</v>
+      </c>
+      <c r="H60">
+        <v>42.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>14.5</v>
+      </c>
+      <c r="K60">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L60">
+        <v>13.3</v>
+      </c>
+      <c r="M60">
+        <v>1.17359752</v>
+      </c>
+      <c r="N60">
+        <v>12.12640248</v>
+      </c>
+      <c r="O60">
+        <v>3.03160062</v>
+      </c>
+      <c r="P60">
+        <v>9.09480186</v>
+      </c>
+      <c r="Q60">
+        <v>10.29480186</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3036466848356154</v>
+      </c>
+      <c r="T60">
+        <v>1.377398996495446</v>
+      </c>
+      <c r="U60">
+        <v>0.0458</v>
+      </c>
+      <c r="V60">
+        <v>0.25</v>
+      </c>
+      <c r="W60">
+        <v>0.03435</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>11.33267561778761</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.147084857316248</v>
+      </c>
+      <c r="C61">
+        <v>22.69963910448485</v>
+      </c>
+      <c r="D61">
+        <v>40.94583910448485</v>
+      </c>
+      <c r="E61">
+        <v>24.1862</v>
+      </c>
+      <c r="F61">
+        <v>26.0662</v>
+      </c>
+      <c r="G61">
+        <v>7.82</v>
+      </c>
+      <c r="H61">
+        <v>42.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>14.5</v>
+      </c>
+      <c r="K61">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L61">
+        <v>13.3</v>
+      </c>
+      <c r="M61">
+        <v>1.19383196</v>
+      </c>
+      <c r="N61">
+        <v>12.10616804</v>
+      </c>
+      <c r="O61">
+        <v>3.02654201</v>
+      </c>
+      <c r="P61">
+        <v>9.07962603</v>
+      </c>
+      <c r="Q61">
+        <v>10.27962603</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3093130666249952</v>
+      </c>
+      <c r="T61">
+        <v>1.406868380245883</v>
+      </c>
+      <c r="U61">
+        <v>0.0458</v>
+      </c>
+      <c r="V61">
+        <v>0.25</v>
+      </c>
+      <c r="W61">
+        <v>0.03435</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>11.14059637002849</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1467151070015377</v>
+      </c>
+      <c r="C62">
+        <v>22.33795390077513</v>
+      </c>
+      <c r="D62">
+        <v>41.02595390077513</v>
+      </c>
+      <c r="E62">
+        <v>24.628</v>
+      </c>
+      <c r="F62">
+        <v>26.508</v>
+      </c>
+      <c r="G62">
+        <v>7.82</v>
+      </c>
+      <c r="H62">
+        <v>42.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>14.5</v>
+      </c>
+      <c r="K62">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L62">
+        <v>13.3</v>
+      </c>
+      <c r="M62">
+        <v>1.2140664</v>
+      </c>
+      <c r="N62">
+        <v>12.0859336</v>
+      </c>
+      <c r="O62">
+        <v>3.0214834</v>
+      </c>
+      <c r="P62">
+        <v>9.0644502</v>
+      </c>
+      <c r="Q62">
+        <v>10.2644502</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3152627675038442</v>
+      </c>
+      <c r="T62">
+        <v>1.437811233183843</v>
+      </c>
+      <c r="U62">
+        <v>0.0458</v>
+      </c>
+      <c r="V62">
+        <v>0.25</v>
+      </c>
+      <c r="W62">
+        <v>0.03435</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>10.95491976386135</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1463453566868273</v>
+      </c>
+      <c r="C63">
+        <v>21.97658281755113</v>
+      </c>
+      <c r="D63">
+        <v>41.10638281755113</v>
+      </c>
+      <c r="E63">
+        <v>25.0698</v>
+      </c>
+      <c r="F63">
+        <v>26.9498</v>
+      </c>
+      <c r="G63">
+        <v>7.82</v>
+      </c>
+      <c r="H63">
+        <v>42.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>14.5</v>
+      </c>
+      <c r="K63">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L63">
+        <v>13.3</v>
+      </c>
+      <c r="M63">
+        <v>1.23430084</v>
+      </c>
+      <c r="N63">
+        <v>12.06569916</v>
+      </c>
+      <c r="O63">
+        <v>3.01642479</v>
+      </c>
+      <c r="P63">
+        <v>9.049274370000001</v>
+      </c>
+      <c r="Q63">
+        <v>10.24927437</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3215175812482751</v>
+      </c>
+      <c r="T63">
+        <v>1.47034089909298</v>
+      </c>
+      <c r="U63">
+        <v>0.0458</v>
+      </c>
+      <c r="V63">
+        <v>0.25</v>
+      </c>
+      <c r="W63">
+        <v>0.03435</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>10.77533091527346</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1459756063721168</v>
+      </c>
+      <c r="C64">
+        <v>21.6155277058848</v>
+      </c>
+      <c r="D64">
+        <v>41.1871277058848</v>
+      </c>
+      <c r="E64">
+        <v>25.5116</v>
+      </c>
+      <c r="F64">
+        <v>27.3916</v>
+      </c>
+      <c r="G64">
+        <v>7.82</v>
+      </c>
+      <c r="H64">
+        <v>42.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>14.5</v>
+      </c>
+      <c r="K64">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L64">
+        <v>13.3</v>
+      </c>
+      <c r="M64">
+        <v>1.25453528</v>
+      </c>
+      <c r="N64">
+        <v>12.04546472</v>
+      </c>
+      <c r="O64">
+        <v>3.01136618</v>
+      </c>
+      <c r="P64">
+        <v>9.03409854</v>
+      </c>
+      <c r="Q64">
+        <v>10.23409854</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.328101595716097</v>
+      </c>
+      <c r="T64">
+        <v>1.504582652681544</v>
+      </c>
+      <c r="U64">
+        <v>0.0458</v>
+      </c>
+      <c r="V64">
+        <v>0.25</v>
+      </c>
+      <c r="W64">
+        <v>0.03435</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>10.60153525534969</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1456058560574064</v>
+      </c>
+      <c r="C65">
+        <v>21.2547904314208</v>
+      </c>
+      <c r="D65">
+        <v>41.2681904314208</v>
+      </c>
+      <c r="E65">
+        <v>25.9534</v>
+      </c>
+      <c r="F65">
+        <v>27.8334</v>
+      </c>
+      <c r="G65">
+        <v>7.82</v>
+      </c>
+      <c r="H65">
+        <v>42.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>14.5</v>
+      </c>
+      <c r="K65">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L65">
+        <v>13.3</v>
+      </c>
+      <c r="M65">
+        <v>1.27476972</v>
+      </c>
+      <c r="N65">
+        <v>12.02523028</v>
+      </c>
+      <c r="O65">
+        <v>3.00630757</v>
+      </c>
+      <c r="P65">
+        <v>9.01892271</v>
+      </c>
+      <c r="Q65">
+        <v>10.21892271</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3350415028578553</v>
+      </c>
+      <c r="T65">
+        <v>1.540675311869491</v>
+      </c>
+      <c r="U65">
+        <v>0.0458</v>
+      </c>
+      <c r="V65">
+        <v>0.25</v>
+      </c>
+      <c r="W65">
+        <v>0.03435</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>10.43325691796319</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.145236105742696</v>
+      </c>
+      <c r="C66">
+        <v>20.89437287452035</v>
+      </c>
+      <c r="D66">
+        <v>41.34957287452036</v>
+      </c>
+      <c r="E66">
+        <v>26.3952</v>
+      </c>
+      <c r="F66">
+        <v>28.2752</v>
+      </c>
+      <c r="G66">
+        <v>7.82</v>
+      </c>
+      <c r="H66">
+        <v>42.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>14.5</v>
+      </c>
+      <c r="K66">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L66">
+        <v>13.3</v>
+      </c>
+      <c r="M66">
+        <v>1.29500416</v>
+      </c>
+      <c r="N66">
+        <v>12.00499584</v>
+      </c>
+      <c r="O66">
+        <v>3.00124896</v>
+      </c>
+      <c r="P66">
+        <v>9.003746880000001</v>
+      </c>
+      <c r="Q66">
+        <v>10.20374688</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3423669603963779</v>
+      </c>
+      <c r="T66">
+        <v>1.578773118790102</v>
+      </c>
+      <c r="U66">
+        <v>0.0458</v>
+      </c>
+      <c r="V66">
+        <v>0.25</v>
+      </c>
+      <c r="W66">
+        <v>0.03435</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>10.27023727862002</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1448663554279856</v>
+      </c>
+      <c r="C67">
+        <v>20.53427693040654</v>
+      </c>
+      <c r="D67">
+        <v>41.43127693040654</v>
+      </c>
+      <c r="E67">
+        <v>26.837</v>
+      </c>
+      <c r="F67">
+        <v>28.717</v>
+      </c>
+      <c r="G67">
+        <v>7.82</v>
+      </c>
+      <c r="H67">
+        <v>42.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>14.5</v>
+      </c>
+      <c r="K67">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L67">
+        <v>13.3</v>
+      </c>
+      <c r="M67">
+        <v>1.3152386</v>
+      </c>
+      <c r="N67">
+        <v>11.9847614</v>
+      </c>
+      <c r="O67">
+        <v>2.99619035</v>
+      </c>
+      <c r="P67">
+        <v>8.988571050000001</v>
+      </c>
+      <c r="Q67">
+        <v>10.18857105</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3501110155085305</v>
+      </c>
+      <c r="T67">
+        <v>1.619047943249033</v>
+      </c>
+      <c r="U67">
+        <v>0.0458</v>
+      </c>
+      <c r="V67">
+        <v>0.25</v>
+      </c>
+      <c r="W67">
+        <v>0.03435</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>10.11223362817971</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1444966051132752</v>
+      </c>
+      <c r="C68">
+        <v>20.17450450931145</v>
+      </c>
+      <c r="D68">
+        <v>41.51330450931145</v>
+      </c>
+      <c r="E68">
+        <v>27.2788</v>
+      </c>
+      <c r="F68">
+        <v>29.1588</v>
+      </c>
+      <c r="G68">
+        <v>7.82</v>
+      </c>
+      <c r="H68">
+        <v>42.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>14.5</v>
+      </c>
+      <c r="K68">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L68">
+        <v>13.3</v>
+      </c>
+      <c r="M68">
+        <v>1.33547304</v>
+      </c>
+      <c r="N68">
+        <v>11.96452696</v>
+      </c>
+      <c r="O68">
+        <v>2.99113174</v>
+      </c>
+      <c r="P68">
+        <v>8.97339522</v>
+      </c>
+      <c r="Q68">
+        <v>10.17339522</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3583106032743389</v>
+      </c>
+      <c r="T68">
+        <v>1.661691875029078</v>
+      </c>
+      <c r="U68">
+        <v>0.0458</v>
+      </c>
+      <c r="V68">
+        <v>0.25</v>
+      </c>
+      <c r="W68">
+        <v>0.03435</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>9.959017967146682</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1452323547985648</v>
+      </c>
+      <c r="C69">
+        <v>19.5698001060074</v>
+      </c>
+      <c r="D69">
+        <v>41.3504001060074</v>
+      </c>
+      <c r="E69">
+        <v>27.7206</v>
+      </c>
+      <c r="F69">
+        <v>29.6006</v>
+      </c>
+      <c r="G69">
+        <v>7.82</v>
+      </c>
+      <c r="H69">
+        <v>42.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>14.5</v>
+      </c>
+      <c r="K69">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L69">
+        <v>13.3</v>
+      </c>
+      <c r="M69">
+        <v>1.4208288</v>
+      </c>
+      <c r="N69">
+        <v>11.8791712</v>
+      </c>
+      <c r="O69">
+        <v>2.9697928</v>
+      </c>
+      <c r="P69">
+        <v>8.9093784</v>
+      </c>
+      <c r="Q69">
+        <v>10.1093784</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3670071357532269</v>
+      </c>
+      <c r="T69">
+        <v>1.706920287523065</v>
+      </c>
+      <c r="U69">
+        <v>0.048</v>
+      </c>
+      <c r="V69">
+        <v>0.25</v>
+      </c>
+      <c r="W69">
+        <v>0.036</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>9.360733678821825</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1448791044838544</v>
+      </c>
+      <c r="C70">
+        <v>19.20605438594979</v>
+      </c>
+      <c r="D70">
+        <v>41.42845438594979</v>
+      </c>
+      <c r="E70">
+        <v>28.1624</v>
+      </c>
+      <c r="F70">
+        <v>30.0424</v>
+      </c>
+      <c r="G70">
+        <v>7.82</v>
+      </c>
+      <c r="H70">
+        <v>42.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>14.5</v>
+      </c>
+      <c r="K70">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L70">
+        <v>13.3</v>
+      </c>
+      <c r="M70">
+        <v>1.4420352</v>
+      </c>
+      <c r="N70">
+        <v>11.8579648</v>
+      </c>
+      <c r="O70">
+        <v>2.9644912</v>
+      </c>
+      <c r="P70">
+        <v>8.8934736</v>
+      </c>
+      <c r="Q70">
+        <v>10.0934736</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3762472015120452</v>
+      </c>
+      <c r="T70">
+        <v>1.754975475797926</v>
+      </c>
+      <c r="U70">
+        <v>0.048</v>
+      </c>
+      <c r="V70">
+        <v>0.25</v>
+      </c>
+      <c r="W70">
+        <v>0.036</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>9.223075830603857</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.144525854169144</v>
+      </c>
+      <c r="C71">
+        <v>18.84260389847444</v>
+      </c>
+      <c r="D71">
+        <v>41.50680389847444</v>
+      </c>
+      <c r="E71">
+        <v>28.6042</v>
+      </c>
+      <c r="F71">
+        <v>30.4842</v>
+      </c>
+      <c r="G71">
+        <v>7.82</v>
+      </c>
+      <c r="H71">
+        <v>42.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>14.5</v>
+      </c>
+      <c r="K71">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L71">
+        <v>13.3</v>
+      </c>
+      <c r="M71">
+        <v>1.4632416</v>
+      </c>
+      <c r="N71">
+        <v>11.8367584</v>
+      </c>
+      <c r="O71">
+        <v>2.9591896</v>
+      </c>
+      <c r="P71">
+        <v>8.877568800000001</v>
+      </c>
+      <c r="Q71">
+        <v>10.0775688</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.386083400545626</v>
+      </c>
+      <c r="T71">
+        <v>1.806130998800197</v>
+      </c>
+      <c r="U71">
+        <v>0.048</v>
+      </c>
+      <c r="V71">
+        <v>0.25</v>
+      </c>
+      <c r="W71">
+        <v>0.036</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>9.089408064942932</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1441726038544336</v>
+      </c>
+      <c r="C72">
+        <v>18.4794503217872</v>
+      </c>
+      <c r="D72">
+        <v>41.58545032178721</v>
+      </c>
+      <c r="E72">
+        <v>29.046</v>
+      </c>
+      <c r="F72">
+        <v>30.926</v>
+      </c>
+      <c r="G72">
+        <v>7.82</v>
+      </c>
+      <c r="H72">
+        <v>42.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>14.5</v>
+      </c>
+      <c r="K72">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L72">
+        <v>13.3</v>
+      </c>
+      <c r="M72">
+        <v>1.484448</v>
+      </c>
+      <c r="N72">
+        <v>11.815552</v>
+      </c>
+      <c r="O72">
+        <v>2.953888</v>
+      </c>
+      <c r="P72">
+        <v>8.861664000000001</v>
+      </c>
+      <c r="Q72">
+        <v>10.061664</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3965753461814455</v>
+      </c>
+      <c r="T72">
+        <v>1.86069689000262</v>
+      </c>
+      <c r="U72">
+        <v>0.048</v>
+      </c>
+      <c r="V72">
+        <v>0.25</v>
+      </c>
+      <c r="W72">
+        <v>0.036</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>8.95955937830089</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1438193535397232</v>
+      </c>
+      <c r="C73">
+        <v>18.11659534683737</v>
+      </c>
+      <c r="D73">
+        <v>41.66439534683737</v>
+      </c>
+      <c r="E73">
+        <v>29.4878</v>
+      </c>
+      <c r="F73">
+        <v>31.3678</v>
+      </c>
+      <c r="G73">
+        <v>7.82</v>
+      </c>
+      <c r="H73">
+        <v>42.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>14.5</v>
+      </c>
+      <c r="K73">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L73">
+        <v>13.3</v>
+      </c>
+      <c r="M73">
+        <v>1.5056544</v>
+      </c>
+      <c r="N73">
+        <v>11.7943456</v>
+      </c>
+      <c r="O73">
+        <v>2.9485864</v>
+      </c>
+      <c r="P73">
+        <v>8.8457592</v>
+      </c>
+      <c r="Q73">
+        <v>10.0457592</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4077908742749076</v>
+      </c>
+      <c r="T73">
+        <v>1.919025946115555</v>
+      </c>
+      <c r="U73">
+        <v>0.048</v>
+      </c>
+      <c r="V73">
+        <v>0.25</v>
+      </c>
+      <c r="W73">
+        <v>0.036</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>8.833368401141723</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1434661032250128</v>
+      </c>
+      <c r="C74">
+        <v>17.75404067743894</v>
+      </c>
+      <c r="D74">
+        <v>41.74364067743894</v>
+      </c>
+      <c r="E74">
+        <v>29.9296</v>
+      </c>
+      <c r="F74">
+        <v>31.8096</v>
+      </c>
+      <c r="G74">
+        <v>7.82</v>
+      </c>
+      <c r="H74">
+        <v>42.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>14.5</v>
+      </c>
+      <c r="K74">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L74">
+        <v>13.3</v>
+      </c>
+      <c r="M74">
+        <v>1.5268608</v>
+      </c>
+      <c r="N74">
+        <v>11.7731392</v>
+      </c>
+      <c r="O74">
+        <v>2.9432848</v>
+      </c>
+      <c r="P74">
+        <v>8.8298544</v>
+      </c>
+      <c r="Q74">
+        <v>10.0298544</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4198075115179029</v>
+      </c>
+      <c r="T74">
+        <v>1.981521363379413</v>
+      </c>
+      <c r="U74">
+        <v>0.048</v>
+      </c>
+      <c r="V74">
+        <v>0.25</v>
+      </c>
+      <c r="W74">
+        <v>0.036</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>8.710682728903645</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1431128529103024</v>
+      </c>
+      <c r="C75">
+        <v>17.3917880303932</v>
+      </c>
+      <c r="D75">
+        <v>41.8231880303932</v>
+      </c>
+      <c r="E75">
+        <v>30.3714</v>
+      </c>
+      <c r="F75">
+        <v>32.2514</v>
+      </c>
+      <c r="G75">
+        <v>7.82</v>
+      </c>
+      <c r="H75">
+        <v>42.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>14.5</v>
+      </c>
+      <c r="K75">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L75">
+        <v>13.3</v>
+      </c>
+      <c r="M75">
+        <v>1.5480672</v>
+      </c>
+      <c r="N75">
+        <v>11.7519328</v>
+      </c>
+      <c r="O75">
+        <v>2.9379832</v>
+      </c>
+      <c r="P75">
+        <v>8.813949600000001</v>
+      </c>
+      <c r="Q75">
+        <v>10.0139496</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.432714270038157</v>
+      </c>
+      <c r="T75">
+        <v>2.048646070810965</v>
+      </c>
+      <c r="U75">
+        <v>0.048</v>
+      </c>
+      <c r="V75">
+        <v>0.25</v>
+      </c>
+      <c r="W75">
+        <v>0.036</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>8.591358307959759</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.142759602595592</v>
+      </c>
+      <c r="C76">
+        <v>17.02983913561263</v>
+      </c>
+      <c r="D76">
+        <v>41.90303913561263</v>
+      </c>
+      <c r="E76">
+        <v>30.8132</v>
+      </c>
+      <c r="F76">
+        <v>32.6932</v>
+      </c>
+      <c r="G76">
+        <v>7.82</v>
+      </c>
+      <c r="H76">
+        <v>42.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>14.5</v>
+      </c>
+      <c r="K76">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L76">
+        <v>13.3</v>
+      </c>
+      <c r="M76">
+        <v>1.5692736</v>
+      </c>
+      <c r="N76">
+        <v>11.7307264</v>
+      </c>
+      <c r="O76">
+        <v>2.9326816</v>
+      </c>
+      <c r="P76">
+        <v>8.798044800000001</v>
+      </c>
+      <c r="Q76">
+        <v>9.998044800000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4466138561368923</v>
+      </c>
+      <c r="T76">
+        <v>2.120934217275714</v>
+      </c>
+      <c r="U76">
+        <v>0.048</v>
+      </c>
+      <c r="V76">
+        <v>0.25</v>
+      </c>
+      <c r="W76">
+        <v>0.036</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>8.475258871365709</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1424063522808816</v>
+      </c>
+      <c r="C77">
+        <v>16.6681957362464</v>
+      </c>
+      <c r="D77">
+        <v>41.9831957362464</v>
+      </c>
+      <c r="E77">
+        <v>31.255</v>
+      </c>
+      <c r="F77">
+        <v>33.135</v>
+      </c>
+      <c r="G77">
+        <v>7.82</v>
+      </c>
+      <c r="H77">
+        <v>42.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>14.5</v>
+      </c>
+      <c r="K77">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L77">
+        <v>13.3</v>
+      </c>
+      <c r="M77">
+        <v>1.59048</v>
+      </c>
+      <c r="N77">
+        <v>11.70952</v>
+      </c>
+      <c r="O77">
+        <v>2.92738</v>
+      </c>
+      <c r="P77">
+        <v>8.782140000000002</v>
+      </c>
+      <c r="Q77">
+        <v>9.982140000000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4616254091235263</v>
+      </c>
+      <c r="T77">
+        <v>2.199005415457642</v>
+      </c>
+      <c r="U77">
+        <v>0.048</v>
+      </c>
+      <c r="V77">
+        <v>0.25</v>
+      </c>
+      <c r="W77">
+        <v>0.036</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>8.362255419747498</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1420531019661712</v>
+      </c>
+      <c r="C78">
+        <v>16.30685958880714</v>
+      </c>
+      <c r="D78">
+        <v>42.06365958880713</v>
+      </c>
+      <c r="E78">
+        <v>31.6968</v>
+      </c>
+      <c r="F78">
+        <v>33.5768</v>
+      </c>
+      <c r="G78">
+        <v>7.82</v>
+      </c>
+      <c r="H78">
+        <v>42.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>14.5</v>
+      </c>
+      <c r="K78">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L78">
+        <v>13.3</v>
+      </c>
+      <c r="M78">
+        <v>1.6116864</v>
+      </c>
+      <c r="N78">
+        <v>11.6883136</v>
+      </c>
+      <c r="O78">
+        <v>2.9220784</v>
+      </c>
+      <c r="P78">
+        <v>8.766235200000001</v>
+      </c>
+      <c r="Q78">
+        <v>9.9662352</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4778879248590467</v>
+      </c>
+      <c r="T78">
+        <v>2.283582546821397</v>
+      </c>
+      <c r="U78">
+        <v>0.048</v>
+      </c>
+      <c r="V78">
+        <v>0.25</v>
+      </c>
+      <c r="W78">
+        <v>0.036</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>8.252225743171874</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1416998516514608</v>
+      </c>
+      <c r="C79">
+        <v>15.94583246329928</v>
+      </c>
+      <c r="D79">
+        <v>42.14443246329927</v>
+      </c>
+      <c r="E79">
+        <v>32.1386</v>
+      </c>
+      <c r="F79">
+        <v>34.0186</v>
+      </c>
+      <c r="G79">
+        <v>7.82</v>
+      </c>
+      <c r="H79">
+        <v>42.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>14.5</v>
+      </c>
+      <c r="K79">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L79">
+        <v>13.3</v>
+      </c>
+      <c r="M79">
+        <v>1.6328928</v>
+      </c>
+      <c r="N79">
+        <v>11.6671072</v>
+      </c>
+      <c r="O79">
+        <v>2.9167768</v>
+      </c>
+      <c r="P79">
+        <v>8.750330399999999</v>
+      </c>
+      <c r="Q79">
+        <v>9.950330399999999</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4955645723976557</v>
+      </c>
+      <c r="T79">
+        <v>2.375514211347219</v>
+      </c>
+      <c r="U79">
+        <v>0.048</v>
+      </c>
+      <c r="V79">
+        <v>0.25</v>
+      </c>
+      <c r="W79">
+        <v>0.036</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>8.145053980273538</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1413466013367504</v>
+      </c>
+      <c r="C80">
+        <v>15.58511614334884</v>
+      </c>
+      <c r="D80">
+        <v>42.22551614334884</v>
+      </c>
+      <c r="E80">
+        <v>32.5804</v>
+      </c>
+      <c r="F80">
+        <v>34.4604</v>
+      </c>
+      <c r="G80">
+        <v>7.82</v>
+      </c>
+      <c r="H80">
+        <v>42.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>14.5</v>
+      </c>
+      <c r="K80">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L80">
+        <v>13.3</v>
+      </c>
+      <c r="M80">
+        <v>1.6540992</v>
+      </c>
+      <c r="N80">
+        <v>11.6459008</v>
+      </c>
+      <c r="O80">
+        <v>2.9114752</v>
+      </c>
+      <c r="P80">
+        <v>8.7344256</v>
+      </c>
+      <c r="Q80">
+        <v>9.934425599999999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.5148481878943199</v>
+      </c>
+      <c r="T80">
+        <v>2.475803299920841</v>
+      </c>
+      <c r="U80">
+        <v>0.048</v>
+      </c>
+      <c r="V80">
+        <v>0.25</v>
+      </c>
+      <c r="W80">
+        <v>0.036</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>8.040630211295671</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.14099335102204</v>
+      </c>
+      <c r="C81">
+        <v>15.22471242633471</v>
+      </c>
+      <c r="D81">
+        <v>42.30691242633471</v>
+      </c>
+      <c r="E81">
+        <v>33.0222</v>
+      </c>
+      <c r="F81">
+        <v>34.9022</v>
+      </c>
+      <c r="G81">
+        <v>7.82</v>
+      </c>
+      <c r="H81">
+        <v>42.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>14.5</v>
+      </c>
+      <c r="K81">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L81">
+        <v>13.3</v>
+      </c>
+      <c r="M81">
+        <v>1.6753056</v>
+      </c>
+      <c r="N81">
+        <v>11.6246944</v>
+      </c>
+      <c r="O81">
+        <v>2.9061736</v>
+      </c>
+      <c r="P81">
+        <v>8.7185208</v>
+      </c>
+      <c r="Q81">
+        <v>9.9185208</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5359683382001905</v>
+      </c>
+      <c r="T81">
+        <v>2.585643730263381</v>
+      </c>
+      <c r="U81">
+        <v>0.048</v>
+      </c>
+      <c r="V81">
+        <v>0.25</v>
+      </c>
+      <c r="W81">
+        <v>0.036</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>7.938850082038764</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1406401007073295</v>
+      </c>
+      <c r="C82">
+        <v>14.86462312352148</v>
+      </c>
+      <c r="D82">
+        <v>42.38862312352148</v>
+      </c>
+      <c r="E82">
+        <v>33.464</v>
+      </c>
+      <c r="F82">
+        <v>35.344</v>
+      </c>
+      <c r="G82">
+        <v>7.82</v>
+      </c>
+      <c r="H82">
+        <v>42.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>14.5</v>
+      </c>
+      <c r="K82">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L82">
+        <v>13.3</v>
+      </c>
+      <c r="M82">
+        <v>1.696512</v>
+      </c>
+      <c r="N82">
+        <v>11.603488</v>
+      </c>
+      <c r="O82">
+        <v>2.900872</v>
+      </c>
+      <c r="P82">
+        <v>8.702616000000001</v>
+      </c>
+      <c r="Q82">
+        <v>9.902616</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5592005035366479</v>
+      </c>
+      <c r="T82">
+        <v>2.706468203640175</v>
+      </c>
+      <c r="U82">
+        <v>0.048</v>
+      </c>
+      <c r="V82">
+        <v>0.25</v>
+      </c>
+      <c r="W82">
+        <v>0.036</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>7.839614456013279</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1402868503926192</v>
+      </c>
+      <c r="C83">
+        <v>14.50485006019372</v>
+      </c>
+      <c r="D83">
+        <v>42.47065006019372</v>
+      </c>
+      <c r="E83">
+        <v>33.9058</v>
+      </c>
+      <c r="F83">
+        <v>35.7858</v>
+      </c>
+      <c r="G83">
+        <v>7.82</v>
+      </c>
+      <c r="H83">
+        <v>42.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>14.5</v>
+      </c>
+      <c r="K83">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L83">
+        <v>13.3</v>
+      </c>
+      <c r="M83">
+        <v>1.7177184</v>
+      </c>
+      <c r="N83">
+        <v>11.5822816</v>
+      </c>
+      <c r="O83">
+        <v>2.8955704</v>
+      </c>
+      <c r="P83">
+        <v>8.6867112</v>
+      </c>
+      <c r="Q83">
+        <v>9.886711199999999</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5848781599611537</v>
+      </c>
+      <c r="T83">
+        <v>2.840011042635579</v>
+      </c>
+      <c r="U83">
+        <v>0.048</v>
+      </c>
+      <c r="V83">
+        <v>0.25</v>
+      </c>
+      <c r="W83">
+        <v>0.036</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>7.742829092358794</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1408561000779088</v>
+      </c>
+      <c r="C84">
+        <v>13.93102263608284</v>
+      </c>
+      <c r="D84">
+        <v>42.33862263608284</v>
+      </c>
+      <c r="E84">
+        <v>34.3476</v>
+      </c>
+      <c r="F84">
+        <v>36.2276</v>
+      </c>
+      <c r="G84">
+        <v>7.82</v>
+      </c>
+      <c r="H84">
+        <v>42.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>14.5</v>
+      </c>
+      <c r="K84">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L84">
+        <v>13.3</v>
+      </c>
+      <c r="M84">
+        <v>1.7932662</v>
+      </c>
+      <c r="N84">
+        <v>11.5067338</v>
+      </c>
+      <c r="O84">
+        <v>2.87668345</v>
+      </c>
+      <c r="P84">
+        <v>8.630050350000001</v>
+      </c>
+      <c r="Q84">
+        <v>9.83005035</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.6134088893217156</v>
+      </c>
+      <c r="T84">
+        <v>2.988391974852694</v>
+      </c>
+      <c r="U84">
+        <v>0.0495</v>
+      </c>
+      <c r="V84">
+        <v>0.25</v>
+      </c>
+      <c r="W84">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>7.416634518623058</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1405140997631983</v>
+      </c>
+      <c r="C85">
+        <v>13.56844495465856</v>
+      </c>
+      <c r="D85">
+        <v>42.41784495465856</v>
+      </c>
+      <c r="E85">
+        <v>34.7894</v>
+      </c>
+      <c r="F85">
+        <v>36.6694</v>
+      </c>
+      <c r="G85">
+        <v>7.82</v>
+      </c>
+      <c r="H85">
+        <v>42.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>14.5</v>
+      </c>
+      <c r="K85">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L85">
+        <v>13.3</v>
+      </c>
+      <c r="M85">
+        <v>1.8151353</v>
+      </c>
+      <c r="N85">
+        <v>11.4848647</v>
+      </c>
+      <c r="O85">
+        <v>2.871216175</v>
+      </c>
+      <c r="P85">
+        <v>8.613648525</v>
+      </c>
+      <c r="Q85">
+        <v>9.813648525</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.6452961750776376</v>
+      </c>
+      <c r="T85">
+        <v>3.154229487330646</v>
+      </c>
+      <c r="U85">
+        <v>0.0495</v>
+      </c>
+      <c r="V85">
+        <v>0.25</v>
+      </c>
+      <c r="W85">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>7.327277476230008</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.140172099448488</v>
+      </c>
+      <c r="C86">
+        <v>13.20616430422447</v>
+      </c>
+      <c r="D86">
+        <v>42.49736430422446</v>
+      </c>
+      <c r="E86">
+        <v>35.23119999999999</v>
+      </c>
+      <c r="F86">
+        <v>37.1112</v>
+      </c>
+      <c r="G86">
+        <v>7.82</v>
+      </c>
+      <c r="H86">
+        <v>42.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>14.5</v>
+      </c>
+      <c r="K86">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L86">
+        <v>13.3</v>
+      </c>
+      <c r="M86">
+        <v>1.8370044</v>
+      </c>
+      <c r="N86">
+        <v>11.4629956</v>
+      </c>
+      <c r="O86">
+        <v>2.8657489</v>
+      </c>
+      <c r="P86">
+        <v>8.597246700000001</v>
+      </c>
+      <c r="Q86">
+        <v>9.797246700000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6811693715530496</v>
+      </c>
+      <c r="T86">
+        <v>3.34079668886834</v>
+      </c>
+      <c r="U86">
+        <v>0.0495</v>
+      </c>
+      <c r="V86">
+        <v>0.25</v>
+      </c>
+      <c r="W86">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>7.240047982465367</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1398300991337776</v>
+      </c>
+      <c r="C87">
+        <v>12.84418235842099</v>
+      </c>
+      <c r="D87">
+        <v>42.57718235842098</v>
+      </c>
+      <c r="E87">
+        <v>35.67299999999999</v>
+      </c>
+      <c r="F87">
+        <v>37.553</v>
+      </c>
+      <c r="G87">
+        <v>7.82</v>
+      </c>
+      <c r="H87">
+        <v>42.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>14.5</v>
+      </c>
+      <c r="K87">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L87">
+        <v>13.3</v>
+      </c>
+      <c r="M87">
+        <v>1.8588735</v>
+      </c>
+      <c r="N87">
+        <v>11.4411265</v>
+      </c>
+      <c r="O87">
+        <v>2.860281625</v>
+      </c>
+      <c r="P87">
+        <v>8.580844875</v>
+      </c>
+      <c r="Q87">
+        <v>9.780844875</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.7218256608918503</v>
+      </c>
+      <c r="T87">
+        <v>3.552239517277729</v>
+      </c>
+      <c r="U87">
+        <v>0.0495</v>
+      </c>
+      <c r="V87">
+        <v>0.25</v>
+      </c>
+      <c r="W87">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>7.154870947377539</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1394880988190672</v>
+      </c>
+      <c r="C88">
+        <v>12.48250080348586</v>
+      </c>
+      <c r="D88">
+        <v>42.65730080348586</v>
+      </c>
+      <c r="E88">
+        <v>36.1148</v>
+      </c>
+      <c r="F88">
+        <v>37.9948</v>
+      </c>
+      <c r="G88">
+        <v>7.82</v>
+      </c>
+      <c r="H88">
+        <v>42.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>14.5</v>
+      </c>
+      <c r="K88">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L88">
+        <v>13.3</v>
+      </c>
+      <c r="M88">
+        <v>1.8807426</v>
+      </c>
+      <c r="N88">
+        <v>11.4192574</v>
+      </c>
+      <c r="O88">
+        <v>2.85481435</v>
+      </c>
+      <c r="P88">
+        <v>8.564443050000001</v>
+      </c>
+      <c r="Q88">
+        <v>9.764443050000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.7682899915647652</v>
+      </c>
+      <c r="T88">
+        <v>3.793888464031316</v>
+      </c>
+      <c r="U88">
+        <v>0.0495</v>
+      </c>
+      <c r="V88">
+        <v>0.25</v>
+      </c>
+      <c r="W88">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>7.071674773570823</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1391460985043567</v>
+      </c>
+      <c r="C89">
+        <v>12.12112133837289</v>
+      </c>
+      <c r="D89">
+        <v>42.73772133837289</v>
+      </c>
+      <c r="E89">
+        <v>36.5566</v>
+      </c>
+      <c r="F89">
+        <v>38.4366</v>
+      </c>
+      <c r="G89">
+        <v>7.82</v>
+      </c>
+      <c r="H89">
+        <v>42.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>14.5</v>
+      </c>
+      <c r="K89">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L89">
+        <v>13.3</v>
+      </c>
+      <c r="M89">
+        <v>1.9026117</v>
+      </c>
+      <c r="N89">
+        <v>11.3973883</v>
+      </c>
+      <c r="O89">
+        <v>2.849347075</v>
+      </c>
+      <c r="P89">
+        <v>8.548041225</v>
+      </c>
+      <c r="Q89">
+        <v>9.748041225</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.8219026808027441</v>
+      </c>
+      <c r="T89">
+        <v>4.072714171823916</v>
+      </c>
+      <c r="U89">
+        <v>0.0495</v>
+      </c>
+      <c r="V89">
+        <v>0.25</v>
+      </c>
+      <c r="W89">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>6.990391155483803</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1388040981896463</v>
+      </c>
+      <c r="C90">
+        <v>11.76004567487198</v>
+      </c>
+      <c r="D90">
+        <v>42.81844567487197</v>
+      </c>
+      <c r="E90">
+        <v>36.9984</v>
+      </c>
+      <c r="F90">
+        <v>38.8784</v>
+      </c>
+      <c r="G90">
+        <v>7.82</v>
+      </c>
+      <c r="H90">
+        <v>42.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>14.5</v>
+      </c>
+      <c r="K90">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L90">
+        <v>13.3</v>
+      </c>
+      <c r="M90">
+        <v>1.9244808</v>
+      </c>
+      <c r="N90">
+        <v>11.3755192</v>
+      </c>
+      <c r="O90">
+        <v>2.8438798</v>
+      </c>
+      <c r="P90">
+        <v>8.531639400000001</v>
+      </c>
+      <c r="Q90">
+        <v>9.731639400000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.8844508182470527</v>
+      </c>
+      <c r="T90">
+        <v>4.398010830915283</v>
+      </c>
+      <c r="U90">
+        <v>0.0495</v>
+      </c>
+      <c r="V90">
+        <v>0.25</v>
+      </c>
+      <c r="W90">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>6.910954892353304</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1384620978749359</v>
+      </c>
+      <c r="C91">
+        <v>11.3992755377307</v>
+      </c>
+      <c r="D91">
+        <v>42.8994755377307</v>
+      </c>
+      <c r="E91">
+        <v>37.4402</v>
+      </c>
+      <c r="F91">
+        <v>39.3202</v>
+      </c>
+      <c r="G91">
+        <v>7.82</v>
+      </c>
+      <c r="H91">
+        <v>42.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>14.5</v>
+      </c>
+      <c r="K91">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L91">
+        <v>13.3</v>
+      </c>
+      <c r="M91">
+        <v>1.9463499</v>
+      </c>
+      <c r="N91">
+        <v>11.3536501</v>
+      </c>
+      <c r="O91">
+        <v>2.838412525</v>
+      </c>
+      <c r="P91">
+        <v>8.515237575</v>
+      </c>
+      <c r="Q91">
+        <v>9.715237575</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.9583713443175994</v>
+      </c>
+      <c r="T91">
+        <v>4.782452337114172</v>
+      </c>
+      <c r="U91">
+        <v>0.0495</v>
+      </c>
+      <c r="V91">
+        <v>0.25</v>
+      </c>
+      <c r="W91">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>6.833303713787537</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1381200975602255</v>
+      </c>
+      <c r="C92">
+        <v>11.03881266477703</v>
+      </c>
+      <c r="D92">
+        <v>42.98081266477703</v>
+      </c>
+      <c r="E92">
+        <v>37.882</v>
+      </c>
+      <c r="F92">
+        <v>39.762</v>
+      </c>
+      <c r="G92">
+        <v>7.82</v>
+      </c>
+      <c r="H92">
+        <v>42.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>14.5</v>
+      </c>
+      <c r="K92">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L92">
+        <v>13.3</v>
+      </c>
+      <c r="M92">
+        <v>1.968219</v>
+      </c>
+      <c r="N92">
+        <v>11.331781</v>
+      </c>
+      <c r="O92">
+        <v>2.83294525</v>
+      </c>
+      <c r="P92">
+        <v>8.498835750000001</v>
+      </c>
+      <c r="Q92">
+        <v>9.698835750000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.047075975602255</v>
+      </c>
+      <c r="T92">
+        <v>5.243782144552839</v>
+      </c>
+      <c r="U92">
+        <v>0.0495</v>
+      </c>
+      <c r="V92">
+        <v>0.25</v>
+      </c>
+      <c r="W92">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>6.757378116967675</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1377780972455151</v>
+      </c>
+      <c r="C93">
+        <v>10.67865880704363</v>
+      </c>
+      <c r="D93">
+        <v>43.06245880704363</v>
+      </c>
+      <c r="E93">
+        <v>38.3238</v>
+      </c>
+      <c r="F93">
+        <v>40.2038</v>
+      </c>
+      <c r="G93">
+        <v>7.82</v>
+      </c>
+      <c r="H93">
+        <v>42.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>14.5</v>
+      </c>
+      <c r="K93">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L93">
+        <v>13.3</v>
+      </c>
+      <c r="M93">
+        <v>1.9900881</v>
+      </c>
+      <c r="N93">
+        <v>11.3099119</v>
+      </c>
+      <c r="O93">
+        <v>2.827477975</v>
+      </c>
+      <c r="P93">
+        <v>8.482433925</v>
+      </c>
+      <c r="Q93">
+        <v>9.682433925</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.15549274717239</v>
+      </c>
+      <c r="T93">
+        <v>5.807629686977876</v>
+      </c>
+      <c r="U93">
+        <v>0.0495</v>
+      </c>
+      <c r="V93">
+        <v>0.25</v>
+      </c>
+      <c r="W93">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>6.683121214583415</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1374360969308047</v>
+      </c>
+      <c r="C94">
+        <v>10.31881572889348</v>
+      </c>
+      <c r="D94">
+        <v>43.14441572889348</v>
+      </c>
+      <c r="E94">
+        <v>38.7656</v>
+      </c>
+      <c r="F94">
+        <v>40.6456</v>
+      </c>
+      <c r="G94">
+        <v>7.82</v>
+      </c>
+      <c r="H94">
+        <v>42.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>14.5</v>
+      </c>
+      <c r="K94">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L94">
+        <v>13.3</v>
+      </c>
+      <c r="M94">
+        <v>2.0119572</v>
+      </c>
+      <c r="N94">
+        <v>11.2880428</v>
+      </c>
+      <c r="O94">
+        <v>2.8220107</v>
+      </c>
+      <c r="P94">
+        <v>8.4660321</v>
+      </c>
+      <c r="Q94">
+        <v>9.666032099999999</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.29101371163506</v>
+      </c>
+      <c r="T94">
+        <v>6.512439115009173</v>
+      </c>
+      <c r="U94">
+        <v>0.0495</v>
+      </c>
+      <c r="V94">
+        <v>0.25</v>
+      </c>
+      <c r="W94">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>6.610478592685768</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1370940966160943</v>
+      </c>
+      <c r="C95">
+        <v>9.959285208147016</v>
+      </c>
+      <c r="D95">
+        <v>43.22668520814702</v>
+      </c>
+      <c r="E95">
+        <v>39.2074</v>
+      </c>
+      <c r="F95">
+        <v>41.0874</v>
+      </c>
+      <c r="G95">
+        <v>7.82</v>
+      </c>
+      <c r="H95">
+        <v>42.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>14.5</v>
+      </c>
+      <c r="K95">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L95">
+        <v>13.3</v>
+      </c>
+      <c r="M95">
+        <v>2.0338263</v>
+      </c>
+      <c r="N95">
+        <v>11.2661737</v>
+      </c>
+      <c r="O95">
+        <v>2.816543425</v>
+      </c>
+      <c r="P95">
+        <v>8.449630275000001</v>
+      </c>
+      <c r="Q95">
+        <v>9.649630275</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.465254951658491</v>
+      </c>
+      <c r="T95">
+        <v>7.418622665335127</v>
+      </c>
+      <c r="U95">
+        <v>0.0495</v>
+      </c>
+      <c r="V95">
+        <v>0.25</v>
+      </c>
+      <c r="W95">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>6.539398177710652</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1367520963013839</v>
+      </c>
+      <c r="C96">
+        <v>9.600069036210641</v>
+      </c>
+      <c r="D96">
+        <v>43.30926903621064</v>
+      </c>
+      <c r="E96">
+        <v>39.6492</v>
+      </c>
+      <c r="F96">
+        <v>41.5292</v>
+      </c>
+      <c r="G96">
+        <v>7.82</v>
+      </c>
+      <c r="H96">
+        <v>42.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>14.5</v>
+      </c>
+      <c r="K96">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L96">
+        <v>13.3</v>
+      </c>
+      <c r="M96">
+        <v>2.0556954</v>
+      </c>
+      <c r="N96">
+        <v>11.2443046</v>
+      </c>
+      <c r="O96">
+        <v>2.81107615</v>
+      </c>
+      <c r="P96">
+        <v>8.43322845</v>
+      </c>
+      <c r="Q96">
+        <v>9.633228449999999</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.697576605023067</v>
+      </c>
+      <c r="T96">
+        <v>8.626867399103064</v>
+      </c>
+      <c r="U96">
+        <v>0.0495</v>
+      </c>
+      <c r="V96">
+        <v>0.25</v>
+      </c>
+      <c r="W96">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>6.469830111990326</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1364100959866735</v>
+      </c>
+      <c r="C97">
+        <v>9.241169018206755</v>
+      </c>
+      <c r="D97">
+        <v>43.39216901820676</v>
+      </c>
+      <c r="E97">
+        <v>40.091</v>
+      </c>
+      <c r="F97">
+        <v>41.971</v>
+      </c>
+      <c r="G97">
+        <v>7.82</v>
+      </c>
+      <c r="H97">
+        <v>42.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>14.5</v>
+      </c>
+      <c r="K97">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L97">
+        <v>13.3</v>
+      </c>
+      <c r="M97">
+        <v>2.0775645</v>
+      </c>
+      <c r="N97">
+        <v>11.2224355</v>
+      </c>
+      <c r="O97">
+        <v>2.805608875</v>
+      </c>
+      <c r="P97">
+        <v>8.416826624999999</v>
+      </c>
+      <c r="Q97">
+        <v>9.616826624999998</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.022826919733473</v>
+      </c>
+      <c r="T97">
+        <v>10.31841002637818</v>
+      </c>
+      <c r="U97">
+        <v>0.0495</v>
+      </c>
+      <c r="V97">
+        <v>0.25</v>
+      </c>
+      <c r="W97">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>6.40172663712727</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1360680956719631</v>
+      </c>
+      <c r="C98">
+        <v>8.882586973105298</v>
+      </c>
+      <c r="D98">
+        <v>43.47538697310529</v>
+      </c>
+      <c r="E98">
+        <v>40.53279999999999</v>
+      </c>
+      <c r="F98">
+        <v>42.4128</v>
+      </c>
+      <c r="G98">
+        <v>7.82</v>
+      </c>
+      <c r="H98">
+        <v>42.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>14.5</v>
+      </c>
+      <c r="K98">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L98">
+        <v>13.3</v>
+      </c>
+      <c r="M98">
+        <v>2.0994336</v>
+      </c>
+      <c r="N98">
+        <v>11.2005664</v>
+      </c>
+      <c r="O98">
+        <v>2.8001416</v>
+      </c>
+      <c r="P98">
+        <v>8.400424800000001</v>
+      </c>
+      <c r="Q98">
+        <v>9.600424800000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.510702391799076</v>
+      </c>
+      <c r="T98">
+        <v>12.85572396729082</v>
+      </c>
+      <c r="U98">
+        <v>0.0495</v>
+      </c>
+      <c r="V98">
+        <v>0.25</v>
+      </c>
+      <c r="W98">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>6.335041984657196</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1357260953572527</v>
+      </c>
+      <c r="C99">
+        <v>8.524324733856808</v>
+      </c>
+      <c r="D99">
+        <v>43.55892473385681</v>
+      </c>
+      <c r="E99">
+        <v>40.9746</v>
+      </c>
+      <c r="F99">
+        <v>42.8546</v>
+      </c>
+      <c r="G99">
+        <v>7.82</v>
+      </c>
+      <c r="H99">
+        <v>42.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>14.5</v>
+      </c>
+      <c r="K99">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L99">
+        <v>13.3</v>
+      </c>
+      <c r="M99">
+        <v>2.1213027</v>
+      </c>
+      <c r="N99">
+        <v>11.1786973</v>
+      </c>
+      <c r="O99">
+        <v>2.794674325</v>
+      </c>
+      <c r="P99">
+        <v>8.384022975000001</v>
+      </c>
+      <c r="Q99">
+        <v>9.584022975</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.323828178575087</v>
+      </c>
+      <c r="T99">
+        <v>17.08458053547859</v>
+      </c>
+      <c r="U99">
+        <v>0.0495</v>
+      </c>
+      <c r="V99">
+        <v>0.25</v>
+      </c>
+      <c r="W99">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>6.269732273475162</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1353840950425423</v>
+      </c>
+      <c r="C100">
+        <v>8.166384147526898</v>
+      </c>
+      <c r="D100">
+        <v>43.6427841475269</v>
+      </c>
+      <c r="E100">
+        <v>41.4164</v>
+      </c>
+      <c r="F100">
+        <v>43.2964</v>
+      </c>
+      <c r="G100">
+        <v>7.82</v>
+      </c>
+      <c r="H100">
+        <v>42.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>14.5</v>
+      </c>
+      <c r="K100">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L100">
+        <v>13.3</v>
+      </c>
+      <c r="M100">
+        <v>2.1431718</v>
+      </c>
+      <c r="N100">
+        <v>11.1568282</v>
+      </c>
+      <c r="O100">
+        <v>2.78920705</v>
+      </c>
+      <c r="P100">
+        <v>8.36762115</v>
+      </c>
+      <c r="Q100">
+        <v>9.567621149999999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.95007975212711</v>
+      </c>
+      <c r="T100">
+        <v>25.54229367185413</v>
+      </c>
+      <c r="U100">
+        <v>0.0495</v>
+      </c>
+      <c r="V100">
+        <v>0.25</v>
+      </c>
+      <c r="W100">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>6.205755413541741</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1360815947278319</v>
+      </c>
+      <c r="C101">
+        <v>7.55389623628357</v>
+      </c>
+      <c r="D101">
+        <v>43.47209623628357</v>
+      </c>
+      <c r="E101">
+        <v>41.8582</v>
+      </c>
+      <c r="F101">
+        <v>43.7382</v>
+      </c>
+      <c r="G101">
+        <v>7.82</v>
+      </c>
+      <c r="H101">
+        <v>42.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>14.5</v>
+      </c>
+      <c r="K101">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L101">
+        <v>13.3</v>
+      </c>
+      <c r="M101">
+        <v>2.22627438</v>
+      </c>
+      <c r="N101">
+        <v>11.07372562</v>
+      </c>
+      <c r="O101">
+        <v>2.768431405</v>
+      </c>
+      <c r="P101">
+        <v>8.305294215</v>
+      </c>
+      <c r="Q101">
+        <v>9.505294214999999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.82883447278318</v>
+      </c>
+      <c r="T101">
+        <v>50.91543308098075</v>
+      </c>
+      <c r="U101">
+        <v>0.0509</v>
+      </c>
+      <c r="V101">
+        <v>0.25</v>
+      </c>
+      <c r="W101">
+        <v>0.038175</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>5.974106390246471</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ghana/ghana_household_products.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_household_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1564329010817382</v>
+        <v>0.1560755688290338</v>
       </c>
       <c r="C2">
-        <v>84.9621897826552</v>
+        <v>84.37989543997925</v>
       </c>
       <c r="D2">
-        <v>81.0421897826552</v>
+        <v>81.30479543997924</v>
       </c>
       <c r="E2">
-        <v>-1.49</v>
+        <v>-0.6451</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.8449</v>
       </c>
       <c r="G2">
         <v>3.92</v>
@@ -1451,28 +1451,28 @@
         <v>13.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04249847</v>
       </c>
       <c r="N2">
-        <v>13.2</v>
+        <v>13.15750153</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.2893753825</v>
       </c>
       <c r="P2">
-        <v>9.899999999999999</v>
+        <v>9.8681261475</v>
       </c>
       <c r="Q2">
-        <v>10.9</v>
+        <v>10.8681261475</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1564329010817382</v>
+        <v>0.1572710291202362</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6817429376593621</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>310.5994168731251</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1560755688290338</v>
+        <v>0.1557182365763294</v>
       </c>
       <c r="C3">
-        <v>84.37989543997925</v>
+        <v>83.79930850226222</v>
       </c>
       <c r="D3">
-        <v>81.30479543997924</v>
+        <v>81.56910850226222</v>
       </c>
       <c r="E3">
-        <v>-0.6451</v>
+        <v>0.1998</v>
       </c>
       <c r="F3">
-        <v>0.8449</v>
+        <v>1.6898</v>
       </c>
       <c r="G3">
         <v>3.92</v>
@@ -1533,28 +1533,28 @@
         <v>13.2</v>
       </c>
       <c r="M3">
-        <v>0.04249847</v>
+        <v>0.08499693999999999</v>
       </c>
       <c r="N3">
-        <v>13.15750153</v>
+        <v>13.11500306</v>
       </c>
       <c r="O3">
-        <v>3.2893753825</v>
+        <v>3.278750765</v>
       </c>
       <c r="P3">
-        <v>9.8681261475</v>
+        <v>9.836252295</v>
       </c>
       <c r="Q3">
-        <v>10.8681261475</v>
+        <v>10.836252295</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1572710291202362</v>
+        <v>0.1581262618125811</v>
       </c>
       <c r="T3">
-        <v>0.6817429376593621</v>
+        <v>0.6869734343423403</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>310.5994168731251</v>
+        <v>155.2997084365626</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1557182365763294</v>
+        <v>0.1553609043236251</v>
       </c>
       <c r="C4">
-        <v>83.79930850226222</v>
+        <v>83.22044567557822</v>
       </c>
       <c r="D4">
-        <v>81.56910850226222</v>
+        <v>81.83514567557822</v>
       </c>
       <c r="E4">
-        <v>0.1998</v>
+        <v>1.0447</v>
       </c>
       <c r="F4">
-        <v>1.6898</v>
+        <v>2.5347</v>
       </c>
       <c r="G4">
         <v>3.92</v>
@@ -1615,28 +1615,28 @@
         <v>13.2</v>
       </c>
       <c r="M4">
-        <v>0.08499693999999999</v>
+        <v>0.12749541</v>
       </c>
       <c r="N4">
-        <v>13.11500306</v>
+        <v>13.07250459</v>
       </c>
       <c r="O4">
-        <v>3.278750765</v>
+        <v>3.2681261475</v>
       </c>
       <c r="P4">
-        <v>9.836252295</v>
+        <v>9.804378442499999</v>
       </c>
       <c r="Q4">
-        <v>10.836252295</v>
+        <v>10.8043784425</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1581262618125811</v>
+        <v>0.1589991281686857</v>
       </c>
       <c r="T4">
-        <v>0.6869734343423403</v>
+        <v>0.6923117763177508</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>155.2997084365626</v>
+        <v>103.5331389577083</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1553609043236251</v>
+        <v>0.1550035720709208</v>
       </c>
       <c r="C5">
-        <v>83.22044567557822</v>
+        <v>82.6433238846614</v>
       </c>
       <c r="D5">
-        <v>81.83514567557822</v>
+        <v>82.10292388466139</v>
       </c>
       <c r="E5">
-        <v>1.0447</v>
+        <v>1.8896</v>
       </c>
       <c r="F5">
-        <v>2.5347</v>
+        <v>3.3796</v>
       </c>
       <c r="G5">
         <v>3.92</v>
@@ -1697,28 +1697,28 @@
         <v>13.2</v>
       </c>
       <c r="M5">
-        <v>0.12749541</v>
+        <v>0.16999388</v>
       </c>
       <c r="N5">
-        <v>13.07250459</v>
+        <v>13.03000612</v>
       </c>
       <c r="O5">
-        <v>3.2681261475</v>
+        <v>3.25750153</v>
       </c>
       <c r="P5">
-        <v>9.804378442499999</v>
+        <v>9.77250459</v>
       </c>
       <c r="Q5">
-        <v>10.8043784425</v>
+        <v>10.77250459</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1589991281686857</v>
+        <v>0.1598901792405425</v>
       </c>
       <c r="T5">
-        <v>0.6923117763177508</v>
+        <v>0.6977613337509825</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>103.5331389577083</v>
+        <v>77.64985421828128</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1550035720709208</v>
+        <v>0.1546462398182164</v>
       </c>
       <c r="C6">
-        <v>82.6433238846614</v>
+        <v>82.06796027649557</v>
       </c>
       <c r="D6">
-        <v>82.10292388466139</v>
+        <v>82.37246027649557</v>
       </c>
       <c r="E6">
-        <v>1.8896</v>
+        <v>2.7345</v>
       </c>
       <c r="F6">
-        <v>3.3796</v>
+        <v>4.2245</v>
       </c>
       <c r="G6">
         <v>3.92</v>
@@ -1779,28 +1779,28 @@
         <v>13.2</v>
       </c>
       <c r="M6">
-        <v>0.16999388</v>
+        <v>0.21249235</v>
       </c>
       <c r="N6">
-        <v>13.03000612</v>
+        <v>12.98750765</v>
       </c>
       <c r="O6">
-        <v>3.25750153</v>
+        <v>3.2468769125</v>
       </c>
       <c r="P6">
-        <v>9.77250459</v>
+        <v>9.7406307375</v>
       </c>
       <c r="Q6">
-        <v>10.77250459</v>
+        <v>10.7406307375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1598901792405425</v>
+        <v>0.1607999892823331</v>
       </c>
       <c r="T6">
-        <v>0.6977613337509825</v>
+        <v>0.7033256187091244</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>77.64985421828128</v>
+        <v>62.11988337462501</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1546462398182164</v>
+        <v>0.1542889075655121</v>
       </c>
       <c r="C7">
-        <v>82.06796027649557</v>
+        <v>81.49437222397395</v>
       </c>
       <c r="D7">
-        <v>82.37246027649557</v>
+        <v>82.64377222397395</v>
       </c>
       <c r="E7">
-        <v>2.7345</v>
+        <v>3.5794</v>
       </c>
       <c r="F7">
-        <v>4.2245</v>
+        <v>5.0694</v>
       </c>
       <c r="G7">
         <v>3.92</v>
@@ -1861,28 +1861,28 @@
         <v>13.2</v>
       </c>
       <c r="M7">
-        <v>0.21249235</v>
+        <v>0.25499082</v>
       </c>
       <c r="N7">
-        <v>12.98750765</v>
+        <v>12.94500918</v>
       </c>
       <c r="O7">
-        <v>3.2468769125</v>
+        <v>3.236252295</v>
       </c>
       <c r="P7">
-        <v>9.7406307375</v>
+        <v>9.708756885</v>
       </c>
       <c r="Q7">
-        <v>10.7406307375</v>
+        <v>10.708756885</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1607999892823331</v>
+        <v>0.1617291569845873</v>
       </c>
       <c r="T7">
-        <v>0.7033256187091244</v>
+        <v>0.7090082927089287</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>62.11988337462501</v>
+        <v>51.76656947885418</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1542889075655121</v>
+        <v>0.1539315753128077</v>
       </c>
       <c r="C8">
-        <v>81.49437222397395</v>
+        <v>80.92257732963202</v>
       </c>
       <c r="D8">
-        <v>82.64377222397395</v>
+        <v>82.91687732963202</v>
       </c>
       <c r="E8">
-        <v>3.5794</v>
+        <v>4.424299999999999</v>
       </c>
       <c r="F8">
-        <v>5.0694</v>
+        <v>5.914299999999999</v>
       </c>
       <c r="G8">
         <v>3.92</v>
@@ -1943,28 +1943,28 @@
         <v>13.2</v>
       </c>
       <c r="M8">
-        <v>0.25499082</v>
+        <v>0.29748929</v>
       </c>
       <c r="N8">
-        <v>12.94500918</v>
+        <v>12.90251071</v>
       </c>
       <c r="O8">
-        <v>3.236252295</v>
+        <v>3.2256276775</v>
       </c>
       <c r="P8">
-        <v>9.708756885</v>
+        <v>9.676883032499999</v>
       </c>
       <c r="Q8">
-        <v>10.708756885</v>
+        <v>10.6768830325</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1617291569845873</v>
+        <v>0.1626783067879653</v>
       </c>
       <c r="T8">
-        <v>0.7090082927089287</v>
+        <v>0.7148131747517397</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>51.76656947885418</v>
+        <v>44.3713452675893</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1539315753128077</v>
+        <v>0.1535742430601034</v>
       </c>
       <c r="C9">
-        <v>80.92257732963203</v>
+        <v>80.35259342945454</v>
       </c>
       <c r="D9">
-        <v>82.91687732963203</v>
+        <v>83.19179342945455</v>
       </c>
       <c r="E9">
-        <v>4.4243</v>
+        <v>5.2692</v>
       </c>
       <c r="F9">
-        <v>5.9143</v>
+        <v>6.7592</v>
       </c>
       <c r="G9">
         <v>3.92</v>
@@ -2025,28 +2025,28 @@
         <v>13.2</v>
       </c>
       <c r="M9">
-        <v>0.29748929</v>
+        <v>0.33998776</v>
       </c>
       <c r="N9">
-        <v>12.90251071</v>
+        <v>12.86001224</v>
       </c>
       <c r="O9">
-        <v>3.2256276775</v>
+        <v>3.21500306</v>
       </c>
       <c r="P9">
-        <v>9.676883032499999</v>
+        <v>9.645009179999999</v>
       </c>
       <c r="Q9">
-        <v>10.6768830325</v>
+        <v>10.64500918</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1626783067879653</v>
+        <v>0.1636480902827211</v>
       </c>
       <c r="T9">
-        <v>0.7148131747517397</v>
+        <v>0.7207442498824378</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>44.3713452675893</v>
+        <v>38.82492710914064</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1535742430601034</v>
+        <v>0.153216910807399</v>
       </c>
       <c r="C10">
-        <v>80.35259342945454</v>
+        <v>79.78443859675843</v>
       </c>
       <c r="D10">
-        <v>83.19179342945455</v>
+        <v>83.46853859675844</v>
       </c>
       <c r="E10">
-        <v>5.2692</v>
+        <v>6.114099999999999</v>
       </c>
       <c r="F10">
-        <v>6.7592</v>
+        <v>7.604099999999999</v>
       </c>
       <c r="G10">
         <v>3.92</v>
@@ -2107,28 +2107,28 @@
         <v>13.2</v>
       </c>
       <c r="M10">
-        <v>0.33998776</v>
+        <v>0.3824862299999999</v>
       </c>
       <c r="N10">
-        <v>12.86001224</v>
+        <v>12.81751377</v>
       </c>
       <c r="O10">
-        <v>3.21500306</v>
+        <v>3.2043784425</v>
       </c>
       <c r="P10">
-        <v>9.645009179999999</v>
+        <v>9.6131353275</v>
       </c>
       <c r="Q10">
-        <v>10.64500918</v>
+        <v>10.6131353275</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1636480902827211</v>
+        <v>0.1646391877004385</v>
       </c>
       <c r="T10">
-        <v>0.7207442498824378</v>
+        <v>0.7268056783127117</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>38.82492710914064</v>
+        <v>34.51104631923612</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.153216910807399</v>
+        <v>0.1528595785546947</v>
       </c>
       <c r="C11">
-        <v>79.78443859675843</v>
+        <v>79.21813114615354</v>
       </c>
       <c r="D11">
-        <v>83.46853859675844</v>
+        <v>83.74713114615354</v>
       </c>
       <c r="E11">
-        <v>6.114099999999999</v>
+        <v>6.958999999999998</v>
       </c>
       <c r="F11">
-        <v>7.604099999999999</v>
+        <v>8.448999999999998</v>
       </c>
       <c r="G11">
         <v>3.92</v>
@@ -2189,28 +2189,28 @@
         <v>13.2</v>
       </c>
       <c r="M11">
-        <v>0.3824862299999999</v>
+        <v>0.4249846999999999</v>
       </c>
       <c r="N11">
-        <v>12.81751377</v>
+        <v>12.7750153</v>
       </c>
       <c r="O11">
-        <v>3.2043784425</v>
+        <v>3.193753825</v>
       </c>
       <c r="P11">
-        <v>9.6131353275</v>
+        <v>9.581261475</v>
       </c>
       <c r="Q11">
-        <v>10.6131353275</v>
+        <v>10.581261475</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1646391877004385</v>
+        <v>0.1656523095052163</v>
       </c>
       <c r="T11">
-        <v>0.7268056783127117</v>
+        <v>0.7330018051525472</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>34.51104631923612</v>
+        <v>31.05994168731252</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1528595785546947</v>
+        <v>0.1525022463019904</v>
       </c>
       <c r="C12">
-        <v>79.21813114615354</v>
+        <v>78.6536896375829</v>
       </c>
       <c r="D12">
-        <v>83.74713114615354</v>
+        <v>84.02758963758289</v>
       </c>
       <c r="E12">
-        <v>6.959</v>
+        <v>7.803899999999999</v>
       </c>
       <c r="F12">
-        <v>8.449</v>
+        <v>9.293899999999999</v>
       </c>
       <c r="G12">
         <v>3.92</v>
@@ -2271,28 +2271,28 @@
         <v>13.2</v>
       </c>
       <c r="M12">
-        <v>0.4249847</v>
+        <v>0.4674831699999999</v>
       </c>
       <c r="N12">
-        <v>12.7750153</v>
+        <v>12.73251683</v>
       </c>
       <c r="O12">
-        <v>3.193753825</v>
+        <v>3.1831292075</v>
       </c>
       <c r="P12">
-        <v>9.581261475</v>
+        <v>9.549387622499999</v>
       </c>
       <c r="Q12">
-        <v>10.581261475</v>
+        <v>10.5493876225</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1656523095052163</v>
+        <v>0.166688198092124</v>
       </c>
       <c r="T12">
-        <v>0.7330018051525472</v>
+        <v>0.7393371707977725</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.05994168731251</v>
+        <v>28.23631062482956</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1525022463019904</v>
+        <v>0.152144914049286</v>
       </c>
       <c r="C13">
-        <v>78.6536896375829</v>
+        <v>78.09113288044452</v>
       </c>
       <c r="D13">
-        <v>84.02758963758289</v>
+        <v>84.30993288044452</v>
       </c>
       <c r="E13">
-        <v>7.803899999999999</v>
+        <v>8.6488</v>
       </c>
       <c r="F13">
-        <v>9.293899999999999</v>
+        <v>10.1388</v>
       </c>
       <c r="G13">
         <v>3.92</v>
@@ -2353,28 +2353,28 @@
         <v>13.2</v>
       </c>
       <c r="M13">
-        <v>0.4674831699999999</v>
+        <v>0.50998164</v>
       </c>
       <c r="N13">
-        <v>12.73251683</v>
+        <v>12.69001836</v>
       </c>
       <c r="O13">
-        <v>3.1831292075</v>
+        <v>3.17250459</v>
       </c>
       <c r="P13">
-        <v>9.549387622499999</v>
+        <v>9.517513770000001</v>
       </c>
       <c r="Q13">
-        <v>10.5493876225</v>
+        <v>10.51751377</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.166688198092124</v>
+        <v>0.1677476296014614</v>
       </c>
       <c r="T13">
-        <v>0.7393371707977725</v>
+        <v>0.7458165220258436</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.23631062482956</v>
+        <v>25.88328473942709</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.152144914049286</v>
+        <v>0.1517875817965816</v>
       </c>
       <c r="C14">
-        <v>78.09113288044452</v>
+        <v>77.53047993779643</v>
       </c>
       <c r="D14">
-        <v>84.30993288044452</v>
+        <v>84.59417993779643</v>
       </c>
       <c r="E14">
-        <v>8.6488</v>
+        <v>9.493699999999999</v>
       </c>
       <c r="F14">
-        <v>10.1388</v>
+        <v>10.9837</v>
       </c>
       <c r="G14">
         <v>3.92</v>
@@ -2435,28 +2435,28 @@
         <v>13.2</v>
       </c>
       <c r="M14">
-        <v>0.50998164</v>
+        <v>0.55248011</v>
       </c>
       <c r="N14">
-        <v>12.69001836</v>
+        <v>12.64751989</v>
       </c>
       <c r="O14">
-        <v>3.17250459</v>
+        <v>3.1618799725</v>
       </c>
       <c r="P14">
-        <v>9.517513770000001</v>
+        <v>9.4856399175</v>
       </c>
       <c r="Q14">
-        <v>10.51751377</v>
+        <v>10.4856399175</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1677476296014614</v>
+        <v>0.1688314158581398</v>
       </c>
       <c r="T14">
-        <v>0.7458165220258436</v>
+        <v>0.7524448238568588</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.88328473942709</v>
+        <v>23.89226283639424</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1517875817965816</v>
+        <v>0.1514302495438773</v>
       </c>
       <c r="C15">
-        <v>77.53047993779643</v>
+        <v>76.97175013064724</v>
       </c>
       <c r="D15">
-        <v>84.59417993779643</v>
+        <v>84.88035013064723</v>
       </c>
       <c r="E15">
-        <v>9.493699999999999</v>
+        <v>10.3386</v>
       </c>
       <c r="F15">
-        <v>10.9837</v>
+        <v>11.8286</v>
       </c>
       <c r="G15">
         <v>3.92</v>
@@ -2517,28 +2517,28 @@
         <v>13.2</v>
       </c>
       <c r="M15">
-        <v>0.55248011</v>
+        <v>0.5949785799999999</v>
       </c>
       <c r="N15">
-        <v>12.64751989</v>
+        <v>12.60502142</v>
       </c>
       <c r="O15">
-        <v>3.1618799725</v>
+        <v>3.151255355</v>
       </c>
       <c r="P15">
-        <v>9.4856399175</v>
+        <v>9.453766065</v>
       </c>
       <c r="Q15">
-        <v>10.4856399175</v>
+        <v>10.453766065</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1688314158581398</v>
+        <v>0.169940406446369</v>
       </c>
       <c r="T15">
-        <v>0.7524448238568588</v>
+        <v>0.7592272722420839</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.89226283639424</v>
+        <v>22.18567263379465</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1514302495438773</v>
+        <v>0.1510729172911729</v>
       </c>
       <c r="C16">
-        <v>76.97175013064724</v>
+        <v>76.41496304233398</v>
       </c>
       <c r="D16">
-        <v>84.88035013064723</v>
+        <v>85.16846304233398</v>
       </c>
       <c r="E16">
-        <v>10.3386</v>
+        <v>11.1835</v>
       </c>
       <c r="F16">
-        <v>11.8286</v>
+        <v>12.6735</v>
       </c>
       <c r="G16">
         <v>3.92</v>
@@ -2599,28 +2599,28 @@
         <v>13.2</v>
       </c>
       <c r="M16">
-        <v>0.5949785799999999</v>
+        <v>0.63747705</v>
       </c>
       <c r="N16">
-        <v>12.60502142</v>
+        <v>12.56252295</v>
       </c>
       <c r="O16">
-        <v>3.151255355</v>
+        <v>3.1406307375</v>
       </c>
       <c r="P16">
-        <v>9.453766065</v>
+        <v>9.4218922125</v>
       </c>
       <c r="Q16">
-        <v>10.453766065</v>
+        <v>10.4218922125</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.169940406446369</v>
+        <v>0.1710754909307917</v>
       </c>
       <c r="T16">
-        <v>0.7592272722420839</v>
+        <v>0.7661693076481376</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.18567263379465</v>
+        <v>20.70662779154167</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1510729172911729</v>
+        <v>0.1507155850384686</v>
       </c>
       <c r="C17">
-        <v>76.41496304233398</v>
+        <v>75.86013852298944</v>
       </c>
       <c r="D17">
-        <v>85.16846304233398</v>
+        <v>85.45853852298944</v>
       </c>
       <c r="E17">
-        <v>11.1835</v>
+        <v>12.0284</v>
       </c>
       <c r="F17">
-        <v>12.6735</v>
+        <v>13.5184</v>
       </c>
       <c r="G17">
         <v>3.92</v>
@@ -2681,28 +2681,28 @@
         <v>13.2</v>
       </c>
       <c r="M17">
-        <v>0.6374770499999999</v>
+        <v>0.6799755199999999</v>
       </c>
       <c r="N17">
-        <v>12.56252295</v>
+        <v>12.52002448</v>
       </c>
       <c r="O17">
-        <v>3.1406307375</v>
+        <v>3.13000612</v>
       </c>
       <c r="P17">
-        <v>9.4218922125</v>
+        <v>9.390018359999999</v>
       </c>
       <c r="Q17">
-        <v>10.4218922125</v>
+        <v>10.39001836</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1710754909307917</v>
+        <v>0.1722376012362722</v>
       </c>
       <c r="T17">
-        <v>0.7661693076481376</v>
+        <v>0.7732766296114784</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.70662779154167</v>
+        <v>19.41246355457032</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1507155850384686</v>
+        <v>0.1503582527857643</v>
       </c>
       <c r="C18">
-        <v>75.86013852298944</v>
+        <v>75.30729669410105</v>
       </c>
       <c r="D18">
-        <v>85.45853852298944</v>
+        <v>85.75059669410105</v>
       </c>
       <c r="E18">
-        <v>12.0284</v>
+        <v>12.8733</v>
       </c>
       <c r="F18">
-        <v>13.5184</v>
+        <v>14.3633</v>
       </c>
       <c r="G18">
         <v>3.92</v>
@@ -2763,28 +2763,28 @@
         <v>13.2</v>
       </c>
       <c r="M18">
-        <v>0.6799755199999999</v>
+        <v>0.72247399</v>
       </c>
       <c r="N18">
-        <v>12.52002448</v>
+        <v>12.47752601</v>
       </c>
       <c r="O18">
-        <v>3.13000612</v>
+        <v>3.1193815025</v>
       </c>
       <c r="P18">
-        <v>9.390018359999999</v>
+        <v>9.3581445075</v>
       </c>
       <c r="Q18">
-        <v>10.39001836</v>
+        <v>10.3581445075</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1722376012362722</v>
+        <v>0.173427714199716</v>
       </c>
       <c r="T18">
-        <v>0.7732766296114784</v>
+        <v>0.7805552123450203</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.41246355457032</v>
+        <v>18.27055393371324</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1503582527857643</v>
+        <v>0.1500009205330599</v>
       </c>
       <c r="C19">
-        <v>75.30729669410105</v>
+        <v>74.75645795316377</v>
       </c>
       <c r="D19">
-        <v>85.75059669410105</v>
+        <v>86.04465795316378</v>
       </c>
       <c r="E19">
-        <v>12.8733</v>
+        <v>13.7182</v>
       </c>
       <c r="F19">
-        <v>14.3633</v>
+        <v>15.2082</v>
       </c>
       <c r="G19">
         <v>3.92</v>
@@ -2845,28 +2845,28 @@
         <v>13.2</v>
       </c>
       <c r="M19">
-        <v>0.72247399</v>
+        <v>0.7649724600000001</v>
       </c>
       <c r="N19">
-        <v>12.47752601</v>
+        <v>12.43502754</v>
       </c>
       <c r="O19">
-        <v>3.1193815025</v>
+        <v>3.108756885</v>
       </c>
       <c r="P19">
-        <v>9.3581445075</v>
+        <v>9.326270655</v>
       </c>
       <c r="Q19">
-        <v>10.3581445075</v>
+        <v>10.326270655</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.173427714199716</v>
+        <v>0.1746468543086097</v>
       </c>
       <c r="T19">
-        <v>0.7805552123450203</v>
+        <v>0.7880113214866972</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.27055393371324</v>
+        <v>17.25552315961806</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.15000092053306</v>
+        <v>0.1496435882803556</v>
       </c>
       <c r="C20">
-        <v>74.75645795316376</v>
+        <v>74.20764297842859</v>
       </c>
       <c r="D20">
-        <v>86.04465795316376</v>
+        <v>86.34074297842859</v>
       </c>
       <c r="E20">
-        <v>13.7182</v>
+        <v>14.5631</v>
       </c>
       <c r="F20">
-        <v>15.2082</v>
+        <v>16.0531</v>
       </c>
       <c r="G20">
         <v>3.92</v>
@@ -2927,28 +2927,28 @@
         <v>13.2</v>
       </c>
       <c r="M20">
-        <v>0.7649724599999999</v>
+        <v>0.80747093</v>
       </c>
       <c r="N20">
-        <v>12.43502754</v>
+        <v>12.39252907</v>
       </c>
       <c r="O20">
-        <v>3.108756885</v>
+        <v>3.0981322675</v>
       </c>
       <c r="P20">
-        <v>9.326270655</v>
+        <v>9.2943968025</v>
       </c>
       <c r="Q20">
-        <v>10.326270655</v>
+        <v>10.2943968025</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1746468543086097</v>
+        <v>0.1758960966424143</v>
       </c>
       <c r="T20">
-        <v>0.7880113214866972</v>
+        <v>0.7956515320886626</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.25552315961806</v>
+        <v>16.34733773016448</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1496435882803556</v>
+        <v>0.1492862560276512</v>
       </c>
       <c r="C21">
-        <v>74.20764297842859</v>
+        <v>73.66087273375</v>
       </c>
       <c r="D21">
-        <v>86.34074297842859</v>
+        <v>86.63887273374999</v>
       </c>
       <c r="E21">
-        <v>14.5631</v>
+        <v>15.408</v>
       </c>
       <c r="F21">
-        <v>16.0531</v>
+        <v>16.898</v>
       </c>
       <c r="G21">
         <v>3.92</v>
@@ -3009,28 +3009,28 @@
         <v>13.2</v>
       </c>
       <c r="M21">
-        <v>0.80747093</v>
+        <v>0.8499694</v>
       </c>
       <c r="N21">
-        <v>12.39252907</v>
+        <v>12.3500306</v>
       </c>
       <c r="O21">
-        <v>3.0981322675</v>
+        <v>3.08750765</v>
       </c>
       <c r="P21">
-        <v>9.2943968025</v>
+        <v>9.262522950000001</v>
       </c>
       <c r="Q21">
-        <v>10.2943968025</v>
+        <v>10.26252295</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1758960966424143</v>
+        <v>0.1771765700345641</v>
       </c>
       <c r="T21">
-        <v>0.7956515320886626</v>
+        <v>0.8034827479556769</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.34733773016448</v>
+        <v>15.52997084365625</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1492862560276512</v>
+        <v>0.1489289237749469</v>
       </c>
       <c r="C22">
-        <v>73.66087273375</v>
+        <v>73.11616847353368</v>
       </c>
       <c r="D22">
-        <v>86.63887273374999</v>
+        <v>86.93906847353368</v>
       </c>
       <c r="E22">
-        <v>15.408</v>
+        <v>16.2529</v>
       </c>
       <c r="F22">
-        <v>16.898</v>
+        <v>17.7429</v>
       </c>
       <c r="G22">
         <v>3.92</v>
@@ -3091,28 +3091,28 @@
         <v>13.2</v>
       </c>
       <c r="M22">
-        <v>0.8499694</v>
+        <v>0.8924678700000001</v>
       </c>
       <c r="N22">
-        <v>12.3500306</v>
+        <v>12.30753213</v>
       </c>
       <c r="O22">
-        <v>3.08750765</v>
+        <v>3.0768830325</v>
       </c>
       <c r="P22">
-        <v>9.262522950000001</v>
+        <v>9.230649097499999</v>
       </c>
       <c r="Q22">
-        <v>10.26252295</v>
+        <v>10.2306490975</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1771765700345641</v>
+        <v>0.1784894604746163</v>
       </c>
       <c r="T22">
-        <v>0.8034827479556769</v>
+        <v>0.8115122224522359</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.52997084365625</v>
+        <v>14.79044842252976</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1489289237749469</v>
+        <v>0.1485715915222426</v>
       </c>
       <c r="C23">
-        <v>73.11616847353369</v>
+        <v>72.57355174778795</v>
       </c>
       <c r="D23">
-        <v>86.93906847353368</v>
+        <v>87.24135174778795</v>
       </c>
       <c r="E23">
-        <v>16.2529</v>
+        <v>17.0978</v>
       </c>
       <c r="F23">
-        <v>17.7429</v>
+        <v>18.5878</v>
       </c>
       <c r="G23">
         <v>3.92</v>
@@ -3173,28 +3173,28 @@
         <v>13.2</v>
       </c>
       <c r="M23">
-        <v>0.8924678699999999</v>
+        <v>0.9349663399999999</v>
       </c>
       <c r="N23">
-        <v>12.30753213</v>
+        <v>12.26503366</v>
       </c>
       <c r="O23">
-        <v>3.0768830325</v>
+        <v>3.066258415</v>
       </c>
       <c r="P23">
-        <v>9.230649097499999</v>
+        <v>9.198775245</v>
       </c>
       <c r="Q23">
-        <v>10.2306490975</v>
+        <v>10.198775245</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1784894604746163</v>
+        <v>0.1798360147721058</v>
       </c>
       <c r="T23">
-        <v>0.8115122224522359</v>
+        <v>0.8197475809102451</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.79044842252977</v>
+        <v>14.11815531241478</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1485715915222426</v>
+        <v>0.1482142592695382</v>
       </c>
       <c r="C24">
-        <v>72.57355174778795</v>
+        <v>72.03304440728044</v>
       </c>
       <c r="D24">
-        <v>87.24135174778795</v>
+        <v>87.54574440728044</v>
       </c>
       <c r="E24">
-        <v>17.0978</v>
+        <v>17.9427</v>
       </c>
       <c r="F24">
-        <v>18.5878</v>
+        <v>19.4327</v>
       </c>
       <c r="G24">
         <v>3.92</v>
@@ -3255,28 +3255,28 @@
         <v>13.2</v>
       </c>
       <c r="M24">
-        <v>0.9349663399999999</v>
+        <v>0.97746481</v>
       </c>
       <c r="N24">
-        <v>12.26503366</v>
+        <v>12.22253519</v>
       </c>
       <c r="O24">
-        <v>3.066258415</v>
+        <v>3.0556337975</v>
       </c>
       <c r="P24">
-        <v>9.198775245</v>
+        <v>9.166901392499998</v>
       </c>
       <c r="Q24">
-        <v>10.198775245</v>
+        <v>10.1669013925</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1798360147721058</v>
+        <v>0.1812175445058938</v>
       </c>
       <c r="T24">
-        <v>0.8197475809102451</v>
+        <v>0.8281968447827482</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.11815531241478</v>
+        <v>13.50432247274457</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1482142592695382</v>
+        <v>0.1478569270168339</v>
       </c>
       <c r="C25">
-        <v>72.03304440728044</v>
+        <v>71.49466860880352</v>
       </c>
       <c r="D25">
-        <v>87.54574440728044</v>
+        <v>87.85226860880351</v>
       </c>
       <c r="E25">
-        <v>17.9427</v>
+        <v>18.7876</v>
       </c>
       <c r="F25">
-        <v>19.4327</v>
+        <v>20.2776</v>
       </c>
       <c r="G25">
         <v>3.92</v>
@@ -3337,28 +3337,28 @@
         <v>13.2</v>
       </c>
       <c r="M25">
-        <v>0.97746481</v>
+        <v>1.01996328</v>
       </c>
       <c r="N25">
-        <v>12.22253519</v>
+        <v>12.18003672</v>
       </c>
       <c r="O25">
-        <v>3.0556337975</v>
+        <v>3.04500918</v>
       </c>
       <c r="P25">
-        <v>9.166901392499998</v>
+        <v>9.135027539999999</v>
       </c>
       <c r="Q25">
-        <v>10.1669013925</v>
+        <v>10.13502754</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1812175445058938</v>
+        <v>0.1826354302853077</v>
       </c>
       <c r="T25">
-        <v>0.8281968447827482</v>
+        <v>0.8368684577045277</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.50432247274457</v>
+        <v>12.94164236971354</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1478569270168339</v>
+        <v>0.1477808447641295</v>
       </c>
       <c r="C26">
-        <v>71.49466860880352</v>
+        <v>70.71531031436993</v>
       </c>
       <c r="D26">
-        <v>87.85226860880351</v>
+        <v>87.91781031436993</v>
       </c>
       <c r="E26">
-        <v>18.7876</v>
+        <v>19.6325</v>
       </c>
       <c r="F26">
-        <v>20.2776</v>
+        <v>21.1225</v>
       </c>
       <c r="G26">
         <v>3.92</v>
@@ -3419,45 +3419,45 @@
         <v>13.2</v>
       </c>
       <c r="M26">
-        <v>1.01996328</v>
+        <v>1.0941455</v>
       </c>
       <c r="N26">
-        <v>12.18003672</v>
+        <v>12.1058545</v>
       </c>
       <c r="O26">
-        <v>3.04500918</v>
+        <v>3.026463625</v>
       </c>
       <c r="P26">
-        <v>9.135027539999999</v>
+        <v>9.079390875</v>
       </c>
       <c r="Q26">
-        <v>10.13502754</v>
+        <v>10.079390875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1826354302853077</v>
+        <v>0.1840911263521727</v>
       </c>
       <c r="T26">
-        <v>0.8368684577045277</v>
+        <v>0.8457713136375545</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>12.94164236971354</v>
+        <v>12.0642090105932</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1477808447641295</v>
+        <v>0.1474347625114252</v>
       </c>
       <c r="C27">
-        <v>70.71531031436993</v>
+        <v>70.16978420077037</v>
       </c>
       <c r="D27">
-        <v>87.91781031436993</v>
+        <v>88.21718420077036</v>
       </c>
       <c r="E27">
-        <v>19.6325</v>
+        <v>20.4774</v>
       </c>
       <c r="F27">
-        <v>21.1225</v>
+        <v>21.9674</v>
       </c>
       <c r="G27">
         <v>3.92</v>
@@ -3501,28 +3501,28 @@
         <v>13.2</v>
       </c>
       <c r="M27">
-        <v>1.0941455</v>
+        <v>1.13791132</v>
       </c>
       <c r="N27">
-        <v>12.1058545</v>
+        <v>12.06208868</v>
       </c>
       <c r="O27">
-        <v>3.026463625</v>
+        <v>3.01552217</v>
       </c>
       <c r="P27">
-        <v>9.079390875</v>
+        <v>9.046566509999998</v>
       </c>
       <c r="Q27">
-        <v>10.079390875</v>
+        <v>10.04656651</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1840911263521727</v>
+        <v>0.18558616555598</v>
       </c>
       <c r="T27">
-        <v>0.8457713136375545</v>
+        <v>0.8549147872985011</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.0642090105932</v>
+        <v>11.60020097172423</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1474347625114252</v>
+        <v>0.1470886802587208</v>
       </c>
       <c r="C28">
-        <v>70.16978420077037</v>
+        <v>69.62630388318158</v>
       </c>
       <c r="D28">
-        <v>88.21718420077036</v>
+        <v>88.51860388318158</v>
       </c>
       <c r="E28">
-        <v>20.4774</v>
+        <v>21.3223</v>
       </c>
       <c r="F28">
-        <v>21.9674</v>
+        <v>22.8123</v>
       </c>
       <c r="G28">
         <v>3.92</v>
@@ -3583,28 +3583,28 @@
         <v>13.2</v>
       </c>
       <c r="M28">
-        <v>1.13791132</v>
+        <v>1.18167714</v>
       </c>
       <c r="N28">
-        <v>12.06208868</v>
+        <v>12.01832286</v>
       </c>
       <c r="O28">
-        <v>3.01552217</v>
+        <v>3.004580715</v>
       </c>
       <c r="P28">
-        <v>9.046566509999998</v>
+        <v>9.013742145</v>
       </c>
       <c r="Q28">
-        <v>10.04656651</v>
+        <v>10.013742145</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.18558616555598</v>
+        <v>0.1871221647379737</v>
       </c>
       <c r="T28">
-        <v>0.8549147872985011</v>
+        <v>0.8643087670871449</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.60020097172423</v>
+        <v>11.17056389869741</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1470886802587208</v>
+        <v>0.1467425980060165</v>
       </c>
       <c r="C29">
-        <v>69.62630388318158</v>
+        <v>69.08489040367226</v>
       </c>
       <c r="D29">
-        <v>88.51860388318158</v>
+        <v>88.82209040367226</v>
       </c>
       <c r="E29">
-        <v>21.3223</v>
+        <v>22.1672</v>
       </c>
       <c r="F29">
-        <v>22.8123</v>
+        <v>23.6572</v>
       </c>
       <c r="G29">
         <v>3.92</v>
@@ -3665,28 +3665,28 @@
         <v>13.2</v>
       </c>
       <c r="M29">
-        <v>1.18167714</v>
+        <v>1.22544296</v>
       </c>
       <c r="N29">
-        <v>12.01832286</v>
+        <v>11.97455704</v>
       </c>
       <c r="O29">
-        <v>3.004580715</v>
+        <v>2.99363926</v>
       </c>
       <c r="P29">
-        <v>9.013742145</v>
+        <v>8.980917779999999</v>
       </c>
       <c r="Q29">
-        <v>10.013742145</v>
+        <v>9.980917779999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1871221647379737</v>
+        <v>0.1887008305639118</v>
       </c>
       <c r="T29">
-        <v>0.8643087670871449</v>
+        <v>0.8739636907588064</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.17056389869741</v>
+        <v>10.77161518802964</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1467425980060165</v>
+        <v>0.1463965157533121</v>
       </c>
       <c r="C30">
-        <v>69.08489040367226</v>
+        <v>68.5455650938752</v>
       </c>
       <c r="D30">
-        <v>88.82209040367226</v>
+        <v>89.12766509387519</v>
       </c>
       <c r="E30">
-        <v>22.1672</v>
+        <v>23.0121</v>
       </c>
       <c r="F30">
-        <v>23.6572</v>
+        <v>24.5021</v>
       </c>
       <c r="G30">
         <v>3.92</v>
@@ -3747,28 +3747,28 @@
         <v>13.2</v>
       </c>
       <c r="M30">
-        <v>1.22544296</v>
+        <v>1.26920878</v>
       </c>
       <c r="N30">
-        <v>11.97455704</v>
+        <v>11.93079122</v>
       </c>
       <c r="O30">
-        <v>2.99363926</v>
+        <v>2.982697805</v>
       </c>
       <c r="P30">
-        <v>8.980917779999999</v>
+        <v>8.948093414999999</v>
       </c>
       <c r="Q30">
-        <v>9.980917779999999</v>
+        <v>9.948093414999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1887008305639118</v>
+        <v>0.1903239658497354</v>
       </c>
       <c r="T30">
-        <v>0.8739636907588064</v>
+        <v>0.8838905841113598</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.77161518802964</v>
+        <v>10.40018018154586</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1463965157533121</v>
+        <v>0.1460504335006078</v>
       </c>
       <c r="C31">
-        <v>68.5455650938752</v>
+        <v>68.00834957998548</v>
       </c>
       <c r="D31">
-        <v>89.12766509387519</v>
+        <v>89.43534957998547</v>
       </c>
       <c r="E31">
-        <v>23.0121</v>
+        <v>23.857</v>
       </c>
       <c r="F31">
-        <v>24.5021</v>
+        <v>25.347</v>
       </c>
       <c r="G31">
         <v>3.92</v>
@@ -3829,28 +3829,28 @@
         <v>13.2</v>
       </c>
       <c r="M31">
-        <v>1.26920878</v>
+        <v>1.3129746</v>
       </c>
       <c r="N31">
-        <v>11.93079122</v>
+        <v>11.8870254</v>
       </c>
       <c r="O31">
-        <v>2.982697805</v>
+        <v>2.97175635</v>
       </c>
       <c r="P31">
-        <v>8.948093414999999</v>
+        <v>8.915269049999999</v>
       </c>
       <c r="Q31">
-        <v>9.948093414999999</v>
+        <v>9.915269049999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1903239658497354</v>
+        <v>0.1919934764294397</v>
       </c>
       <c r="T31">
-        <v>0.8838905841113598</v>
+        <v>0.8941011029882719</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.40018018154586</v>
+        <v>10.05350750882767</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1460504335006078</v>
+        <v>0.1460996012479034</v>
       </c>
       <c r="C32">
-        <v>68.00834957998548</v>
+        <v>67.11960758447665</v>
       </c>
       <c r="D32">
-        <v>89.43534957998547</v>
+        <v>89.39150758447664</v>
       </c>
       <c r="E32">
-        <v>23.857</v>
+        <v>24.7019</v>
       </c>
       <c r="F32">
-        <v>25.347</v>
+        <v>26.1919</v>
       </c>
       <c r="G32">
         <v>3.92</v>
@@ -3911,45 +3911,45 @@
         <v>13.2</v>
       </c>
       <c r="M32">
-        <v>1.3129746</v>
+        <v>1.40126665</v>
       </c>
       <c r="N32">
-        <v>11.8870254</v>
+        <v>11.79873335</v>
       </c>
       <c r="O32">
-        <v>2.97175635</v>
+        <v>2.9496833375</v>
       </c>
       <c r="P32">
-        <v>8.915269049999999</v>
+        <v>8.849050012499999</v>
       </c>
       <c r="Q32">
-        <v>9.915269049999999</v>
+        <v>9.849050012499999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1919934764294397</v>
+        <v>0.1937113786201499</v>
       </c>
       <c r="T32">
-        <v>0.8941011029882719</v>
+        <v>0.9046075789340801</v>
       </c>
       <c r="U32">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>10.05350750882767</v>
+        <v>9.420048639564783</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1460996012479034</v>
+        <v>0.1457662689951991</v>
       </c>
       <c r="C33">
-        <v>67.11960758447665</v>
+        <v>66.57277885286825</v>
       </c>
       <c r="D33">
-        <v>89.39150758447664</v>
+        <v>89.68957885286825</v>
       </c>
       <c r="E33">
-        <v>24.7019</v>
+        <v>25.5468</v>
       </c>
       <c r="F33">
-        <v>26.1919</v>
+        <v>27.0368</v>
       </c>
       <c r="G33">
         <v>3.92</v>
@@ -3993,28 +3993,28 @@
         <v>13.2</v>
       </c>
       <c r="M33">
-        <v>1.40126665</v>
+        <v>1.4464688</v>
       </c>
       <c r="N33">
-        <v>11.79873335</v>
+        <v>11.7535312</v>
       </c>
       <c r="O33">
-        <v>2.9496833375</v>
+        <v>2.9383828</v>
       </c>
       <c r="P33">
-        <v>8.849050012499999</v>
+        <v>8.8151484</v>
       </c>
       <c r="Q33">
-        <v>9.849050012499999</v>
+        <v>9.8151484</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1937113786201499</v>
+        <v>0.195479807345881</v>
       </c>
       <c r="T33">
-        <v>0.9046075789340801</v>
+        <v>0.9154230688782944</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.420048639564783</v>
+        <v>9.125672119578383</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1457662689951991</v>
+        <v>0.1454329367424947</v>
       </c>
       <c r="C34">
-        <v>66.57277885286825</v>
+        <v>66.0279445775231</v>
       </c>
       <c r="D34">
-        <v>89.68957885286825</v>
+        <v>89.98964457752309</v>
       </c>
       <c r="E34">
-        <v>25.5468</v>
+        <v>26.3917</v>
       </c>
       <c r="F34">
-        <v>27.0368</v>
+        <v>27.8817</v>
       </c>
       <c r="G34">
         <v>3.92</v>
@@ -4075,28 +4075,28 @@
         <v>13.2</v>
       </c>
       <c r="M34">
-        <v>1.4464688</v>
+        <v>1.49167095</v>
       </c>
       <c r="N34">
-        <v>11.7535312</v>
+        <v>11.70832905</v>
       </c>
       <c r="O34">
-        <v>2.9383828</v>
+        <v>2.9270822625</v>
       </c>
       <c r="P34">
-        <v>8.8151484</v>
+        <v>8.781246787499999</v>
       </c>
       <c r="Q34">
-        <v>9.8151484</v>
+        <v>9.781246787499999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.195479807345881</v>
+        <v>0.1973010249887981</v>
       </c>
       <c r="T34">
-        <v>0.9154230688782944</v>
+        <v>0.9265614092686046</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.125672119578383</v>
+        <v>8.849136600803281</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1454329367424947</v>
+        <v>0.1450996044897904</v>
       </c>
       <c r="C35">
-        <v>66.0279445775231</v>
+        <v>65.48512484361493</v>
       </c>
       <c r="D35">
-        <v>89.98964457752309</v>
+        <v>90.29172484361493</v>
       </c>
       <c r="E35">
-        <v>26.3917</v>
+        <v>27.2366</v>
       </c>
       <c r="F35">
-        <v>27.8817</v>
+        <v>28.7266</v>
       </c>
       <c r="G35">
         <v>3.92</v>
@@ -4157,28 +4157,28 @@
         <v>13.2</v>
       </c>
       <c r="M35">
-        <v>1.49167095</v>
+        <v>1.5368731</v>
       </c>
       <c r="N35">
-        <v>11.70832905</v>
+        <v>11.6631269</v>
       </c>
       <c r="O35">
-        <v>2.9270822625</v>
+        <v>2.915781725</v>
       </c>
       <c r="P35">
-        <v>8.781246787499999</v>
+        <v>8.747345175</v>
       </c>
       <c r="Q35">
-        <v>9.781246787499999</v>
+        <v>9.747345175</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1973010249887981</v>
+        <v>0.199177431045137</v>
       </c>
       <c r="T35">
-        <v>0.9265614092686046</v>
+        <v>0.9380372751252879</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.849136600803281</v>
+        <v>8.588867877250243</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1450996044897904</v>
+        <v>0.144766272237086</v>
       </c>
       <c r="C36">
-        <v>65.48512484361493</v>
+        <v>64.94434000691605</v>
       </c>
       <c r="D36">
-        <v>90.29172484361493</v>
+        <v>90.59584000691605</v>
       </c>
       <c r="E36">
-        <v>27.2366</v>
+        <v>28.0815</v>
       </c>
       <c r="F36">
-        <v>28.7266</v>
+        <v>29.5715</v>
       </c>
       <c r="G36">
         <v>3.92</v>
@@ -4239,28 +4239,28 @@
         <v>13.2</v>
       </c>
       <c r="M36">
-        <v>1.5368731</v>
+        <v>1.58207525</v>
       </c>
       <c r="N36">
-        <v>11.6631269</v>
+        <v>11.61792475</v>
       </c>
       <c r="O36">
-        <v>2.915781725</v>
+        <v>2.9044811875</v>
       </c>
       <c r="P36">
-        <v>8.747345175</v>
+        <v>8.7134435625</v>
       </c>
       <c r="Q36">
-        <v>9.747345175</v>
+        <v>9.7134435625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.199177431045137</v>
+        <v>0.2011115726724401</v>
       </c>
       <c r="T36">
-        <v>0.9380372751252879</v>
+        <v>0.9498662445467921</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.588867877250243</v>
+        <v>8.343471652185951</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.144766272237086</v>
+        <v>0.1444329399843817</v>
       </c>
       <c r="C37">
-        <v>64.94434000691605</v>
+        <v>64.40561069836991</v>
       </c>
       <c r="D37">
-        <v>90.59584000691605</v>
+        <v>90.90201069836991</v>
       </c>
       <c r="E37">
-        <v>28.0815</v>
+        <v>28.9264</v>
       </c>
       <c r="F37">
-        <v>29.5715</v>
+        <v>30.4164</v>
       </c>
       <c r="G37">
         <v>3.92</v>
@@ -4321,28 +4321,28 @@
         <v>13.2</v>
       </c>
       <c r="M37">
-        <v>1.58207525</v>
+        <v>1.6272774</v>
       </c>
       <c r="N37">
-        <v>11.61792475</v>
+        <v>11.5727226</v>
       </c>
       <c r="O37">
-        <v>2.9044811875</v>
+        <v>2.89318065</v>
       </c>
       <c r="P37">
-        <v>8.7134435625</v>
+        <v>8.679541949999999</v>
       </c>
       <c r="Q37">
-        <v>9.7134435625</v>
+        <v>9.679541949999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2011115726724401</v>
+        <v>0.2031061562255964</v>
       </c>
       <c r="T37">
-        <v>0.9498662445467921</v>
+        <v>0.9620648692627183</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.343471652185951</v>
+        <v>8.111708550736338</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1444329399843817</v>
+        <v>0.1440996077316774</v>
       </c>
       <c r="C38">
-        <v>64.40561069836991</v>
+        <v>63.86895782875677</v>
       </c>
       <c r="D38">
-        <v>90.90201069836991</v>
+        <v>91.21025782875677</v>
       </c>
       <c r="E38">
-        <v>28.9264</v>
+        <v>29.7713</v>
       </c>
       <c r="F38">
-        <v>30.4164</v>
+        <v>31.2613</v>
       </c>
       <c r="G38">
         <v>3.92</v>
@@ -4403,28 +4403,28 @@
         <v>13.2</v>
       </c>
       <c r="M38">
-        <v>1.6272774</v>
+        <v>1.67247955</v>
       </c>
       <c r="N38">
-        <v>11.5727226</v>
+        <v>11.52752045</v>
       </c>
       <c r="O38">
-        <v>2.89318065</v>
+        <v>2.8818801125</v>
       </c>
       <c r="P38">
-        <v>8.679541949999999</v>
+        <v>8.6456403375</v>
       </c>
       <c r="Q38">
-        <v>9.679541949999999</v>
+        <v>9.6456403375</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2031061562255964</v>
+        <v>0.2051640598915514</v>
       </c>
       <c r="T38">
-        <v>0.9620648692627183</v>
+        <v>0.9746507519061343</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.111708550736342</v>
+        <v>7.892473184500223</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1440996077316774</v>
+        <v>0.143766275478973</v>
       </c>
       <c r="C39">
-        <v>63.86895782875677</v>
+        <v>63.33440259345417</v>
       </c>
       <c r="D39">
-        <v>91.21025782875677</v>
+        <v>91.52060259345417</v>
       </c>
       <c r="E39">
-        <v>29.7713</v>
+        <v>30.6162</v>
       </c>
       <c r="F39">
-        <v>31.2613</v>
+        <v>32.1062</v>
       </c>
       <c r="G39">
         <v>3.92</v>
@@ -4485,28 +4485,28 @@
         <v>13.2</v>
       </c>
       <c r="M39">
-        <v>1.67247955</v>
+        <v>1.7176817</v>
       </c>
       <c r="N39">
-        <v>11.52752045</v>
+        <v>11.4823183</v>
       </c>
       <c r="O39">
-        <v>2.8818801125</v>
+        <v>2.870579575</v>
       </c>
       <c r="P39">
-        <v>8.6456403375</v>
+        <v>8.611738724999999</v>
       </c>
       <c r="Q39">
-        <v>9.6456403375</v>
+        <v>9.611738724999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2051640598915514</v>
+        <v>0.2072883475467307</v>
       </c>
       <c r="T39">
-        <v>0.9746507519061343</v>
+        <v>0.9876426307638541</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.892473184500223</v>
+        <v>7.684776521750217</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.143766275478973</v>
+        <v>0.1436669432262687</v>
       </c>
       <c r="C40">
-        <v>63.33440259345417</v>
+        <v>62.58239348515646</v>
       </c>
       <c r="D40">
-        <v>91.52060259345417</v>
+        <v>91.61349348515645</v>
       </c>
       <c r="E40">
-        <v>30.6162</v>
+        <v>31.4611</v>
       </c>
       <c r="F40">
-        <v>32.1062</v>
+        <v>32.9511</v>
       </c>
       <c r="G40">
         <v>3.92</v>
@@ -4567,45 +4567,45 @@
         <v>13.2</v>
       </c>
       <c r="M40">
-        <v>1.7176817</v>
+        <v>1.78924473</v>
       </c>
       <c r="N40">
-        <v>11.4823183</v>
+        <v>11.41075527</v>
       </c>
       <c r="O40">
-        <v>2.870579575</v>
+        <v>2.8526888175</v>
       </c>
       <c r="P40">
-        <v>8.611738724999999</v>
+        <v>8.5580664525</v>
       </c>
       <c r="Q40">
-        <v>9.611738724999999</v>
+        <v>9.5580664525</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2072883475467307</v>
+        <v>0.2094822839774897</v>
       </c>
       <c r="T40">
-        <v>0.9876426307638541</v>
+        <v>1.001060472862811</v>
       </c>
       <c r="U40">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y40">
-        <v>7.684776521750217</v>
+        <v>7.377414491532414</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1436669432262687</v>
+        <v>0.1433396109735643</v>
       </c>
       <c r="C41">
-        <v>62.58239348515646</v>
+        <v>62.04493833654856</v>
       </c>
       <c r="D41">
-        <v>91.61349348515645</v>
+        <v>91.92093833654856</v>
       </c>
       <c r="E41">
-        <v>31.4611</v>
+        <v>32.306</v>
       </c>
       <c r="F41">
-        <v>32.9511</v>
+        <v>33.796</v>
       </c>
       <c r="G41">
         <v>3.92</v>
@@ -4649,28 +4649,28 @@
         <v>13.2</v>
       </c>
       <c r="M41">
-        <v>1.78924473</v>
+        <v>1.8351228</v>
       </c>
       <c r="N41">
-        <v>11.41075527</v>
+        <v>11.3648772</v>
       </c>
       <c r="O41">
-        <v>2.8526888175</v>
+        <v>2.8412193</v>
       </c>
       <c r="P41">
-        <v>8.5580664525</v>
+        <v>8.5236579</v>
       </c>
       <c r="Q41">
-        <v>9.5580664525</v>
+        <v>9.5236579</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2094822839774897</v>
+        <v>0.2117493516226072</v>
       </c>
       <c r="T41">
-        <v>1.001060472862811</v>
+        <v>1.014925576365066</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.377414491532414</v>
+        <v>7.192979129244103</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1433396109735643</v>
+        <v>0.14301227872086</v>
       </c>
       <c r="C42">
-        <v>62.04493833654856</v>
+        <v>61.50955363865147</v>
       </c>
       <c r="D42">
-        <v>91.92093833654856</v>
+        <v>92.23045363865147</v>
       </c>
       <c r="E42">
-        <v>32.306</v>
+        <v>33.1509</v>
       </c>
       <c r="F42">
-        <v>33.796</v>
+        <v>34.6409</v>
       </c>
       <c r="G42">
         <v>3.92</v>
@@ -4731,28 +4731,28 @@
         <v>13.2</v>
       </c>
       <c r="M42">
-        <v>1.8351228</v>
+        <v>1.88100087</v>
       </c>
       <c r="N42">
-        <v>11.3648772</v>
+        <v>11.31899913</v>
       </c>
       <c r="O42">
-        <v>2.8412193</v>
+        <v>2.8297497825</v>
       </c>
       <c r="P42">
-        <v>8.5236579</v>
+        <v>8.489249347499999</v>
       </c>
       <c r="Q42">
-        <v>9.5236579</v>
+        <v>9.489249347499999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2117493516226072</v>
+        <v>0.2140932690184068</v>
       </c>
       <c r="T42">
-        <v>1.014925576365066</v>
+        <v>1.029260683375872</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.192979129244103</v>
+        <v>7.017540613896686</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.14301227872086</v>
+        <v>0.1426849464681556</v>
       </c>
       <c r="C43">
-        <v>61.50955363865147</v>
+        <v>60.97626037693264</v>
       </c>
       <c r="D43">
-        <v>92.23045363865147</v>
+        <v>92.54206037693264</v>
       </c>
       <c r="E43">
-        <v>33.1509</v>
+        <v>33.9958</v>
       </c>
       <c r="F43">
-        <v>34.6409</v>
+        <v>35.4858</v>
       </c>
       <c r="G43">
         <v>3.92</v>
@@ -4813,28 +4813,28 @@
         <v>13.2</v>
       </c>
       <c r="M43">
-        <v>1.88100087</v>
+        <v>1.92687894</v>
       </c>
       <c r="N43">
-        <v>11.31899913</v>
+        <v>11.27312106</v>
       </c>
       <c r="O43">
-        <v>2.8297497825</v>
+        <v>2.818280265</v>
       </c>
       <c r="P43">
-        <v>8.489249347499999</v>
+        <v>8.454840794999999</v>
       </c>
       <c r="Q43">
-        <v>9.489249347499999</v>
+        <v>9.454840794999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2140932690184068</v>
+        <v>0.2165180111519925</v>
       </c>
       <c r="T43">
-        <v>1.029260683375872</v>
+        <v>1.044090104421533</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.017540613896686</v>
+        <v>6.850456313565811</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1426849464681557</v>
+        <v>0.1423576142154513</v>
       </c>
       <c r="C44">
-        <v>60.9762603769326</v>
+        <v>60.44507982142395</v>
       </c>
       <c r="D44">
-        <v>92.5420603769326</v>
+        <v>92.85577982142395</v>
       </c>
       <c r="E44">
-        <v>33.9958</v>
+        <v>34.8407</v>
       </c>
       <c r="F44">
-        <v>35.4858</v>
+        <v>36.3307</v>
       </c>
       <c r="G44">
         <v>3.92</v>
@@ -4895,28 +4895,28 @@
         <v>13.2</v>
       </c>
       <c r="M44">
-        <v>1.92687894</v>
+        <v>1.97275701</v>
       </c>
       <c r="N44">
-        <v>11.27312106</v>
+        <v>11.22724299</v>
       </c>
       <c r="O44">
-        <v>2.818280265</v>
+        <v>2.8068107475</v>
       </c>
       <c r="P44">
-        <v>8.454840794999999</v>
+        <v>8.420432242499999</v>
       </c>
       <c r="Q44">
-        <v>9.454840794999999</v>
+        <v>9.420432242499999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2165180111519925</v>
+        <v>0.2190278319569321</v>
       </c>
       <c r="T44">
-        <v>1.044090104421533</v>
+        <v>1.0594398560302</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.850456313565812</v>
+        <v>6.691143376041025</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1423576142154513</v>
+        <v>0.142030281962747</v>
       </c>
       <c r="C45">
-        <v>60.44507982142395</v>
+        <v>59.91603353156203</v>
       </c>
       <c r="D45">
-        <v>92.85577982142395</v>
+        <v>93.17163353156202</v>
       </c>
       <c r="E45">
-        <v>34.8407</v>
+        <v>35.68559999999999</v>
       </c>
       <c r="F45">
-        <v>36.3307</v>
+        <v>37.1756</v>
       </c>
       <c r="G45">
         <v>3.92</v>
@@ -4977,28 +4977,28 @@
         <v>13.2</v>
       </c>
       <c r="M45">
-        <v>1.97275701</v>
+        <v>2.01863508</v>
       </c>
       <c r="N45">
-        <v>11.22724299</v>
+        <v>11.18136492</v>
       </c>
       <c r="O45">
-        <v>2.8068107475</v>
+        <v>2.79534123</v>
       </c>
       <c r="P45">
-        <v>8.420432242499999</v>
+        <v>8.38602369</v>
       </c>
       <c r="Q45">
-        <v>9.420432242499999</v>
+        <v>9.38602369</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2190278319569321</v>
+        <v>0.221627289219191</v>
       </c>
       <c r="T45">
-        <v>1.0594398560302</v>
+        <v>1.075337813053462</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.691143376041025</v>
+        <v>6.539071935676458</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.142030281962747</v>
+        <v>0.1417029497100426</v>
       </c>
       <c r="C46">
-        <v>59.91603353156203</v>
+        <v>59.38914336112663</v>
       </c>
       <c r="D46">
-        <v>93.17163353156202</v>
+        <v>93.48964336112662</v>
       </c>
       <c r="E46">
-        <v>35.68559999999999</v>
+        <v>36.5305</v>
       </c>
       <c r="F46">
-        <v>37.1756</v>
+        <v>38.0205</v>
       </c>
       <c r="G46">
         <v>3.92</v>
@@ -5059,28 +5059,28 @@
         <v>13.2</v>
       </c>
       <c r="M46">
-        <v>2.01863508</v>
+        <v>2.06451315</v>
       </c>
       <c r="N46">
-        <v>11.18136492</v>
+        <v>11.13548685</v>
       </c>
       <c r="O46">
-        <v>2.79534123</v>
+        <v>2.7838717125</v>
       </c>
       <c r="P46">
-        <v>8.38602369</v>
+        <v>8.3516151375</v>
       </c>
       <c r="Q46">
-        <v>9.38602369</v>
+        <v>9.3516151375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.221627289219191</v>
+        <v>0.2243212722000775</v>
       </c>
       <c r="T46">
-        <v>1.075337813053462</v>
+        <v>1.091813877604843</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.539071935676458</v>
+        <v>6.393759225994758</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1417029497100426</v>
+        <v>0.1413756174573383</v>
       </c>
       <c r="C47">
-        <v>59.38914336112663</v>
+        <v>58.86443146328123</v>
       </c>
       <c r="D47">
-        <v>93.48964336112662</v>
+        <v>93.80983146328123</v>
       </c>
       <c r="E47">
-        <v>36.5305</v>
+        <v>37.3754</v>
       </c>
       <c r="F47">
-        <v>38.0205</v>
+        <v>38.8654</v>
       </c>
       <c r="G47">
         <v>3.92</v>
@@ -5141,28 +5141,28 @@
         <v>13.2</v>
       </c>
       <c r="M47">
-        <v>2.06451315</v>
+        <v>2.11039122</v>
       </c>
       <c r="N47">
-        <v>11.13548685</v>
+        <v>11.08960878</v>
       </c>
       <c r="O47">
-        <v>2.7838717125</v>
+        <v>2.772402195</v>
       </c>
       <c r="P47">
-        <v>8.3516151375</v>
+        <v>8.317206584999999</v>
       </c>
       <c r="Q47">
-        <v>9.3516151375</v>
+        <v>9.317206584999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2243212722000775</v>
+        <v>0.2271150323284042</v>
       </c>
       <c r="T47">
-        <v>1.091813877604843</v>
+        <v>1.108900166769238</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.393759225994758</v>
+        <v>6.254764460212263</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1413756174573383</v>
+        <v>0.1410482852046339</v>
       </c>
       <c r="C48">
-        <v>58.86443146328123</v>
+        <v>58.34192029571766</v>
       </c>
       <c r="D48">
-        <v>93.80983146328123</v>
+        <v>94.13222029571766</v>
       </c>
       <c r="E48">
-        <v>37.3754</v>
+        <v>38.22029999999999</v>
       </c>
       <c r="F48">
-        <v>38.8654</v>
+        <v>39.7103</v>
       </c>
       <c r="G48">
         <v>3.92</v>
@@ -5223,28 +5223,28 @@
         <v>13.2</v>
       </c>
       <c r="M48">
-        <v>2.11039122</v>
+        <v>2.15626929</v>
       </c>
       <c r="N48">
-        <v>11.08960878</v>
+        <v>11.04373071</v>
       </c>
       <c r="O48">
-        <v>2.772402195</v>
+        <v>2.7609326775</v>
       </c>
       <c r="P48">
-        <v>8.317206584999999</v>
+        <v>8.282798032499999</v>
       </c>
       <c r="Q48">
-        <v>9.317206584999999</v>
+        <v>9.282798032499999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2271150323284042</v>
+        <v>0.2300142173672338</v>
       </c>
       <c r="T48">
-        <v>1.108900166769238</v>
+        <v>1.126631221562478</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.254764460212263</v>
+        <v>6.121684365314129</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1410482852046339</v>
+        <v>0.1410809529519296</v>
       </c>
       <c r="C49">
-        <v>58.34192029571766</v>
+        <v>57.46474639952194</v>
       </c>
       <c r="D49">
-        <v>94.13222029571766</v>
+        <v>94.09994639952194</v>
       </c>
       <c r="E49">
-        <v>38.22029999999999</v>
+        <v>39.0652</v>
       </c>
       <c r="F49">
-        <v>39.7103</v>
+        <v>40.5552</v>
       </c>
       <c r="G49">
         <v>3.92</v>
@@ -5305,45 +5305,45 @@
         <v>13.2</v>
       </c>
       <c r="M49">
-        <v>2.15626929</v>
+        <v>2.24270256</v>
       </c>
       <c r="N49">
-        <v>11.04373071</v>
+        <v>10.95729744</v>
       </c>
       <c r="O49">
-        <v>2.7609326775</v>
+        <v>2.73932436</v>
       </c>
       <c r="P49">
-        <v>8.282798032499999</v>
+        <v>8.21797308</v>
       </c>
       <c r="Q49">
-        <v>9.282798032499999</v>
+        <v>9.21797308</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2300142173672338</v>
+        <v>0.2330249095229415</v>
       </c>
       <c r="T49">
-        <v>1.126631221562478</v>
+        <v>1.145044240001612</v>
       </c>
       <c r="U49">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>6.121684365314129</v>
+        <v>5.88575597826936</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1410809529519296</v>
+        <v>0.1407611206992252</v>
       </c>
       <c r="C50">
-        <v>57.46474639952194</v>
+        <v>56.93677818818145</v>
       </c>
       <c r="D50">
-        <v>94.09994639952194</v>
+        <v>94.41687818818144</v>
       </c>
       <c r="E50">
-        <v>39.0652</v>
+        <v>39.91009999999999</v>
       </c>
       <c r="F50">
-        <v>40.5552</v>
+        <v>41.40009999999999</v>
       </c>
       <c r="G50">
         <v>3.92</v>
@@ -5387,28 +5387,28 @@
         <v>13.2</v>
       </c>
       <c r="M50">
-        <v>2.24270256</v>
+        <v>2.28942553</v>
       </c>
       <c r="N50">
-        <v>10.95729744</v>
+        <v>10.91057447</v>
       </c>
       <c r="O50">
-        <v>2.73932436</v>
+        <v>2.7276436175</v>
       </c>
       <c r="P50">
-        <v>8.21797308</v>
+        <v>8.1829308525</v>
       </c>
       <c r="Q50">
-        <v>9.21797308</v>
+        <v>9.1829308525</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2330249095229415</v>
+        <v>0.2361536680376965</v>
       </c>
       <c r="T50">
-        <v>1.145044240001612</v>
+        <v>1.164179337595222</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.88575597826936</v>
+        <v>5.765638509325089</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1407611206992252</v>
+        <v>0.1404412884465209</v>
       </c>
       <c r="C51">
-        <v>56.93677818818145</v>
+        <v>56.41095206534346</v>
       </c>
       <c r="D51">
-        <v>94.41687818818144</v>
+        <v>94.73595206534345</v>
       </c>
       <c r="E51">
-        <v>39.91009999999999</v>
+        <v>40.755</v>
       </c>
       <c r="F51">
-        <v>41.40009999999999</v>
+        <v>42.245</v>
       </c>
       <c r="G51">
         <v>3.92</v>
@@ -5469,28 +5469,28 @@
         <v>13.2</v>
       </c>
       <c r="M51">
-        <v>2.28942553</v>
+        <v>2.3361485</v>
       </c>
       <c r="N51">
-        <v>10.91057447</v>
+        <v>10.8638515</v>
       </c>
       <c r="O51">
-        <v>2.7276436175</v>
+        <v>2.715962875</v>
       </c>
       <c r="P51">
-        <v>8.1829308525</v>
+        <v>8.147888625</v>
       </c>
       <c r="Q51">
-        <v>9.1829308525</v>
+        <v>9.147888625</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2361536680376965</v>
+        <v>0.2394075768930418</v>
       </c>
       <c r="T51">
-        <v>1.164179337595222</v>
+        <v>1.184079839092576</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.765638509325089</v>
+        <v>5.650325739138586</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1404412884465209</v>
+        <v>0.1401214561938166</v>
       </c>
       <c r="C52">
-        <v>56.41095206534346</v>
+        <v>55.88728982166992</v>
       </c>
       <c r="D52">
-        <v>94.73595206534345</v>
+        <v>95.05718982166992</v>
       </c>
       <c r="E52">
-        <v>40.755</v>
+        <v>41.5999</v>
       </c>
       <c r="F52">
-        <v>42.245</v>
+        <v>43.0899</v>
       </c>
       <c r="G52">
         <v>3.92</v>
@@ -5551,28 +5551,28 @@
         <v>13.2</v>
       </c>
       <c r="M52">
-        <v>2.3361485</v>
+        <v>2.38287147</v>
       </c>
       <c r="N52">
-        <v>10.8638515</v>
+        <v>10.81712853</v>
       </c>
       <c r="O52">
-        <v>2.715962875</v>
+        <v>2.7042821325</v>
       </c>
       <c r="P52">
-        <v>8.147888625</v>
+        <v>8.1128463975</v>
       </c>
       <c r="Q52">
-        <v>9.147888625</v>
+        <v>9.1128463975</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2394075768930418</v>
+        <v>0.2427942983547276</v>
       </c>
       <c r="T52">
-        <v>1.184079839092576</v>
+        <v>1.20479260595717</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.650325739138586</v>
+        <v>5.539535038371163</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1401214561938166</v>
+        <v>0.1398016239411122</v>
       </c>
       <c r="C53">
-        <v>55.88728982166992</v>
+        <v>55.36581354438623</v>
       </c>
       <c r="D53">
-        <v>95.05718982166992</v>
+        <v>95.38061354438622</v>
       </c>
       <c r="E53">
-        <v>41.5999</v>
+        <v>42.44479999999999</v>
       </c>
       <c r="F53">
-        <v>43.0899</v>
+        <v>43.9348</v>
       </c>
       <c r="G53">
         <v>3.92</v>
@@ -5633,28 +5633,28 @@
         <v>13.2</v>
       </c>
       <c r="M53">
-        <v>2.38287147</v>
+        <v>2.42959444</v>
       </c>
       <c r="N53">
-        <v>10.81712853</v>
+        <v>10.77040556</v>
       </c>
       <c r="O53">
-        <v>2.7042821325</v>
+        <v>2.69260139</v>
       </c>
       <c r="P53">
-        <v>8.1128463975</v>
+        <v>8.07780417</v>
       </c>
       <c r="Q53">
-        <v>9.1128463975</v>
+        <v>9.07780417</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2427942983547276</v>
+        <v>0.2463221332106504</v>
       </c>
       <c r="T53">
-        <v>1.20479260595717</v>
+        <v>1.226368404774454</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.539535038371163</v>
+        <v>5.433005518402488</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1398016239411122</v>
+        <v>0.1394817916884078</v>
       </c>
       <c r="C54">
-        <v>55.36581354438623</v>
+        <v>54.84654562234315</v>
       </c>
       <c r="D54">
-        <v>95.38061354438622</v>
+        <v>95.70624562234315</v>
       </c>
       <c r="E54">
-        <v>42.44479999999999</v>
+        <v>43.2897</v>
       </c>
       <c r="F54">
-        <v>43.9348</v>
+        <v>44.7797</v>
       </c>
       <c r="G54">
         <v>3.92</v>
@@ -5715,28 +5715,28 @@
         <v>13.2</v>
       </c>
       <c r="M54">
-        <v>2.42959444</v>
+        <v>2.47631741</v>
       </c>
       <c r="N54">
-        <v>10.77040556</v>
+        <v>10.72368259</v>
       </c>
       <c r="O54">
-        <v>2.69260139</v>
+        <v>2.6809206475</v>
       </c>
       <c r="P54">
-        <v>8.07780417</v>
+        <v>8.0427619425</v>
       </c>
       <c r="Q54">
-        <v>9.07780417</v>
+        <v>9.0427619425</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2463221332106504</v>
+        <v>0.2500000886987401</v>
       </c>
       <c r="T54">
-        <v>1.226368404774454</v>
+        <v>1.248862322690347</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.433005518402488</v>
+        <v>5.330495980319421</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1394817916884078</v>
+        <v>0.1391619594357035</v>
       </c>
       <c r="C55">
-        <v>54.84654562234315</v>
+        <v>54.32950875118365</v>
       </c>
       <c r="D55">
-        <v>95.70624562234315</v>
+        <v>96.03410875118365</v>
       </c>
       <c r="E55">
-        <v>43.2897</v>
+        <v>44.1346</v>
       </c>
       <c r="F55">
-        <v>44.7797</v>
+        <v>45.6246</v>
       </c>
       <c r="G55">
         <v>3.92</v>
@@ -5797,28 +5797,28 @@
         <v>13.2</v>
       </c>
       <c r="M55">
-        <v>2.47631741</v>
+        <v>2.52304038</v>
       </c>
       <c r="N55">
-        <v>10.72368259</v>
+        <v>10.67695962</v>
       </c>
       <c r="O55">
-        <v>2.6809206475</v>
+        <v>2.669239905</v>
       </c>
       <c r="P55">
-        <v>8.0427619425</v>
+        <v>8.007719714999999</v>
       </c>
       <c r="Q55">
-        <v>9.0427619425</v>
+        <v>9.007719714999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2500000886987401</v>
+        <v>0.2538379552950076</v>
       </c>
       <c r="T55">
-        <v>1.248862322690347</v>
+        <v>1.272334237037365</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.330495980319421</v>
+        <v>5.231783091794986</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1391619594357035</v>
+        <v>0.1388421271829992</v>
       </c>
       <c r="C56">
-        <v>54.32950875118365</v>
+        <v>53.81472593861563</v>
       </c>
       <c r="D56">
-        <v>96.03410875118365</v>
+        <v>96.36422593861563</v>
       </c>
       <c r="E56">
-        <v>44.1346</v>
+        <v>44.9795</v>
       </c>
       <c r="F56">
-        <v>45.6246</v>
+        <v>46.4695</v>
       </c>
       <c r="G56">
         <v>3.92</v>
@@ -5879,28 +5879,28 @@
         <v>13.2</v>
       </c>
       <c r="M56">
-        <v>2.52304038</v>
+        <v>2.56976335</v>
       </c>
       <c r="N56">
-        <v>10.67695962</v>
+        <v>10.63023665</v>
       </c>
       <c r="O56">
-        <v>2.669239905</v>
+        <v>2.6575591625</v>
       </c>
       <c r="P56">
-        <v>8.007719714999999</v>
+        <v>7.972677487499999</v>
       </c>
       <c r="Q56">
-        <v>9.007719714999999</v>
+        <v>8.972677487499999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2538379552950076</v>
+        <v>0.2578463937399982</v>
       </c>
       <c r="T56">
-        <v>1.272334237037365</v>
+        <v>1.296849347577584</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.231783091794986</v>
+        <v>5.13665976285326</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1388421271829992</v>
+        <v>0.1385222949302948</v>
       </c>
       <c r="C57">
-        <v>53.81472593861563</v>
+        <v>53.30222050979435</v>
       </c>
       <c r="D57">
-        <v>96.36422593861563</v>
+        <v>96.69662050979434</v>
       </c>
       <c r="E57">
-        <v>44.9795</v>
+        <v>45.8244</v>
       </c>
       <c r="F57">
-        <v>46.4695</v>
+        <v>47.3144</v>
       </c>
       <c r="G57">
         <v>3.92</v>
@@ -5961,28 +5961,28 @@
         <v>13.2</v>
       </c>
       <c r="M57">
-        <v>2.56976335</v>
+        <v>2.61648632</v>
       </c>
       <c r="N57">
-        <v>10.63023665</v>
+        <v>10.58351368</v>
       </c>
       <c r="O57">
-        <v>2.6575591625</v>
+        <v>2.64587842</v>
       </c>
       <c r="P57">
-        <v>7.972677487499999</v>
+        <v>7.93763526</v>
       </c>
       <c r="Q57">
-        <v>8.972677487499999</v>
+        <v>8.93763526</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2578463937399982</v>
+        <v>0.2620370339324882</v>
       </c>
       <c r="T57">
-        <v>1.296849347577584</v>
+        <v>1.322478781324176</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.13665976285326</v>
+        <v>5.044933695659452</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1385222949302948</v>
+        <v>0.1382024626775905</v>
       </c>
       <c r="C58">
-        <v>53.30222050979435</v>
+        <v>52.79201611281582</v>
       </c>
       <c r="D58">
-        <v>96.69662050979434</v>
+        <v>97.03131611281582</v>
       </c>
       <c r="E58">
-        <v>45.8244</v>
+        <v>46.6693</v>
       </c>
       <c r="F58">
-        <v>47.3144</v>
+        <v>48.1593</v>
       </c>
       <c r="G58">
         <v>3.92</v>
@@ -6043,28 +6043,28 @@
         <v>13.2</v>
       </c>
       <c r="M58">
-        <v>2.61648632</v>
+        <v>2.66320929</v>
       </c>
       <c r="N58">
-        <v>10.58351368</v>
+        <v>10.53679071</v>
       </c>
       <c r="O58">
-        <v>2.64587842</v>
+        <v>2.6341976775</v>
       </c>
       <c r="P58">
-        <v>7.93763526</v>
+        <v>7.902593032499999</v>
       </c>
       <c r="Q58">
-        <v>8.93763526</v>
+        <v>8.902593032499999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2620370339324882</v>
+        <v>0.2664225876223034</v>
       </c>
       <c r="T58">
-        <v>1.322478781324176</v>
+        <v>1.349300281756657</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.044933695659452</v>
+        <v>4.956426086963671</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1382024626775905</v>
+        <v>0.1378826304248861</v>
       </c>
       <c r="C59">
-        <v>52.79201611281582</v>
+        <v>52.28413672432564</v>
       </c>
       <c r="D59">
-        <v>97.03131611281582</v>
+        <v>97.36833672432564</v>
       </c>
       <c r="E59">
-        <v>46.6693</v>
+        <v>47.5142</v>
       </c>
       <c r="F59">
-        <v>48.1593</v>
+        <v>49.0042</v>
       </c>
       <c r="G59">
         <v>3.92</v>
@@ -6125,28 +6125,28 @@
         <v>13.2</v>
       </c>
       <c r="M59">
-        <v>2.66320929</v>
+        <v>2.70993226</v>
       </c>
       <c r="N59">
-        <v>10.53679071</v>
+        <v>10.49006774</v>
       </c>
       <c r="O59">
-        <v>2.6341976775</v>
+        <v>2.622516935</v>
       </c>
       <c r="P59">
-        <v>7.902593032499999</v>
+        <v>7.867550804999999</v>
       </c>
       <c r="Q59">
-        <v>8.902593032499999</v>
+        <v>8.867550804999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2664225876223034</v>
+        <v>0.2710169772021098</v>
       </c>
       <c r="T59">
-        <v>1.349300281756657</v>
+        <v>1.377398996495446</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.956426086963671</v>
+        <v>4.870970464774643</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1378826304248861</v>
+        <v>0.1375627981721818</v>
       </c>
       <c r="C60">
-        <v>52.28413672432566</v>
+        <v>51.77860665524454</v>
       </c>
       <c r="D60">
-        <v>97.36833672432564</v>
+        <v>97.70770665524454</v>
       </c>
       <c r="E60">
-        <v>47.51419999999999</v>
+        <v>48.35909999999999</v>
       </c>
       <c r="F60">
-        <v>49.00419999999999</v>
+        <v>49.84909999999999</v>
       </c>
       <c r="G60">
         <v>3.92</v>
@@ -6207,28 +6207,28 @@
         <v>13.2</v>
       </c>
       <c r="M60">
-        <v>2.70993226</v>
+        <v>2.75665523</v>
       </c>
       <c r="N60">
-        <v>10.49006774</v>
+        <v>10.44334477</v>
       </c>
       <c r="O60">
-        <v>2.622516935</v>
+        <v>2.6108361925</v>
       </c>
       <c r="P60">
-        <v>7.867550805</v>
+        <v>7.8325085775</v>
       </c>
       <c r="Q60">
-        <v>8.867550805</v>
+        <v>8.832508577500001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2710169772021098</v>
+        <v>0.2758354833467848</v>
       </c>
       <c r="T60">
-        <v>1.377398996495446</v>
+        <v>1.406868380245883</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.870970464774644</v>
+        <v>4.788411643337785</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1375627981721818</v>
+        <v>0.1372429659194774</v>
       </c>
       <c r="C61">
-        <v>51.77860665524454</v>
+        <v>51.27545055661404</v>
       </c>
       <c r="D61">
-        <v>97.70770665524454</v>
+        <v>98.04945055661403</v>
       </c>
       <c r="E61">
-        <v>48.35909999999999</v>
+        <v>49.20399999999999</v>
       </c>
       <c r="F61">
-        <v>49.84909999999999</v>
+        <v>50.694</v>
       </c>
       <c r="G61">
         <v>3.92</v>
@@ -6289,28 +6289,28 @@
         <v>13.2</v>
       </c>
       <c r="M61">
-        <v>2.75665523</v>
+        <v>2.8033782</v>
       </c>
       <c r="N61">
-        <v>10.44334477</v>
+        <v>10.3966218</v>
       </c>
       <c r="O61">
-        <v>2.6108361925</v>
+        <v>2.59915545</v>
       </c>
       <c r="P61">
-        <v>7.8325085775</v>
+        <v>7.797466349999999</v>
       </c>
       <c r="Q61">
-        <v>8.832508577500001</v>
+        <v>8.797466349999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2758354833467848</v>
+        <v>0.2808949147986936</v>
       </c>
       <c r="T61">
-        <v>1.406868380245883</v>
+        <v>1.437811233183843</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.788411643337785</v>
+        <v>4.708604782615488</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1372429659194774</v>
+        <v>0.1369231336667731</v>
       </c>
       <c r="C62">
-        <v>51.27545055661404</v>
+        <v>50.77469342556564</v>
       </c>
       <c r="D62">
-        <v>98.04945055661403</v>
+        <v>98.39359342556564</v>
       </c>
       <c r="E62">
-        <v>49.20399999999999</v>
+        <v>50.0489</v>
       </c>
       <c r="F62">
-        <v>50.694</v>
+        <v>51.5389</v>
       </c>
       <c r="G62">
         <v>3.92</v>
@@ -6371,28 +6371,28 @@
         <v>13.2</v>
       </c>
       <c r="M62">
-        <v>2.8033782</v>
+        <v>2.85010117</v>
       </c>
       <c r="N62">
-        <v>10.3966218</v>
+        <v>10.34989883</v>
       </c>
       <c r="O62">
-        <v>2.59915545</v>
+        <v>2.5874747075</v>
       </c>
       <c r="P62">
-        <v>7.797466349999999</v>
+        <v>7.762424122499999</v>
       </c>
       <c r="Q62">
-        <v>8.797466349999999</v>
+        <v>8.762424122499999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2808949147986936</v>
+        <v>0.2862138042737771</v>
       </c>
       <c r="T62">
-        <v>1.437811233183843</v>
+        <v>1.47034089909298</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.708604782615488</v>
+        <v>4.63141454027753</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1369231336667731</v>
+        <v>0.1366033014140687</v>
       </c>
       <c r="C63">
-        <v>50.77469342556564</v>
+        <v>50.2763606114158</v>
       </c>
       <c r="D63">
-        <v>98.39359342556564</v>
+        <v>98.74016061141579</v>
       </c>
       <c r="E63">
-        <v>50.0489</v>
+        <v>50.89379999999999</v>
       </c>
       <c r="F63">
-        <v>51.5389</v>
+        <v>52.38379999999999</v>
       </c>
       <c r="G63">
         <v>3.92</v>
@@ -6453,28 +6453,28 @@
         <v>13.2</v>
       </c>
       <c r="M63">
-        <v>2.85010117</v>
+        <v>2.89682414</v>
       </c>
       <c r="N63">
-        <v>10.34989883</v>
+        <v>10.30317586</v>
       </c>
       <c r="O63">
-        <v>2.5874747075</v>
+        <v>2.575793965</v>
       </c>
       <c r="P63">
-        <v>7.762424122499999</v>
+        <v>7.727381895</v>
       </c>
       <c r="Q63">
-        <v>8.762424122499999</v>
+        <v>8.727381895000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2862138042737771</v>
+        <v>0.2918126353001809</v>
       </c>
       <c r="T63">
-        <v>1.47034089909298</v>
+        <v>1.504582652681544</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.63141454027753</v>
+        <v>4.556714305756925</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1366033014140687</v>
+        <v>0.1374647191613644</v>
       </c>
       <c r="C64">
-        <v>50.2763606114158</v>
+        <v>48.50355151509523</v>
       </c>
       <c r="D64">
-        <v>98.74016061141579</v>
+        <v>97.81225151509523</v>
       </c>
       <c r="E64">
-        <v>50.89379999999999</v>
+        <v>51.73869999999999</v>
       </c>
       <c r="F64">
-        <v>52.38379999999999</v>
+        <v>53.2287</v>
       </c>
       <c r="G64">
         <v>3.92</v>
@@ -6535,45 +6535,45 @@
         <v>13.2</v>
       </c>
       <c r="M64">
-        <v>2.89682414</v>
+        <v>3.07661886</v>
       </c>
       <c r="N64">
-        <v>10.30317586</v>
+        <v>10.12338114</v>
       </c>
       <c r="O64">
-        <v>2.575793965</v>
+        <v>2.530845285</v>
       </c>
       <c r="P64">
-        <v>7.727381895</v>
+        <v>7.592535855</v>
       </c>
       <c r="Q64">
-        <v>8.727381895000001</v>
+        <v>8.592535855</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2918126353001809</v>
+        <v>0.2977141058415254</v>
       </c>
       <c r="T64">
-        <v>1.504582652681544</v>
+        <v>1.540675311869491</v>
       </c>
       <c r="U64">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.556714305756925</v>
+        <v>4.290424196385509</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1374647191613644</v>
+        <v>0.13716363690866</v>
       </c>
       <c r="C65">
-        <v>48.50355151509523</v>
+        <v>47.98098471049651</v>
       </c>
       <c r="D65">
-        <v>97.81225151509523</v>
+        <v>98.13458471049651</v>
       </c>
       <c r="E65">
-        <v>51.73869999999999</v>
+        <v>52.5836</v>
       </c>
       <c r="F65">
-        <v>53.2287</v>
+        <v>54.0736</v>
       </c>
       <c r="G65">
         <v>3.92</v>
@@ -6617,28 +6617,28 @@
         <v>13.2</v>
       </c>
       <c r="M65">
-        <v>3.07661886</v>
+        <v>3.12545408</v>
       </c>
       <c r="N65">
-        <v>10.12338114</v>
+        <v>10.07454592</v>
       </c>
       <c r="O65">
-        <v>2.530845285</v>
+        <v>2.51863648</v>
       </c>
       <c r="P65">
-        <v>7.592535855</v>
+        <v>7.555909439999999</v>
       </c>
       <c r="Q65">
-        <v>8.592535855</v>
+        <v>8.555909439999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2977141058415254</v>
+        <v>0.303943435857389</v>
       </c>
       <c r="T65">
-        <v>1.540675311869491</v>
+        <v>1.578773118790102</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.290424196385509</v>
+        <v>4.223386318316985</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.13716363690866</v>
+        <v>0.1368625546559557</v>
       </c>
       <c r="C66">
-        <v>47.98098471049651</v>
+        <v>47.46054938145233</v>
       </c>
       <c r="D66">
-        <v>98.13458471049651</v>
+        <v>98.45904938145233</v>
       </c>
       <c r="E66">
-        <v>52.5836</v>
+        <v>53.4285</v>
       </c>
       <c r="F66">
-        <v>54.0736</v>
+        <v>54.9185</v>
       </c>
       <c r="G66">
         <v>3.92</v>
@@ -6699,28 +6699,28 @@
         <v>13.2</v>
       </c>
       <c r="M66">
-        <v>3.12545408</v>
+        <v>3.1742893</v>
       </c>
       <c r="N66">
-        <v>10.07454592</v>
+        <v>10.0257107</v>
       </c>
       <c r="O66">
-        <v>2.51863648</v>
+        <v>2.506427675</v>
       </c>
       <c r="P66">
-        <v>7.555909439999999</v>
+        <v>7.519283025</v>
       </c>
       <c r="Q66">
-        <v>8.555909439999999</v>
+        <v>8.519283025</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.303943435857389</v>
+        <v>0.3105287275884449</v>
       </c>
       <c r="T66">
-        <v>1.578773118790102</v>
+        <v>1.619047943249033</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.223386318316985</v>
+        <v>4.158411144189031</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1368625546559557</v>
+        <v>0.1365614724032514</v>
       </c>
       <c r="C67">
-        <v>47.46054938145233</v>
+        <v>46.94226674013935</v>
       </c>
       <c r="D67">
-        <v>98.45904938145233</v>
+        <v>98.78566674013935</v>
       </c>
       <c r="E67">
-        <v>53.4285</v>
+        <v>54.2734</v>
       </c>
       <c r="F67">
-        <v>54.9185</v>
+        <v>55.7634</v>
       </c>
       <c r="G67">
         <v>3.92</v>
@@ -6781,28 +6781,28 @@
         <v>13.2</v>
       </c>
       <c r="M67">
-        <v>3.1742893</v>
+        <v>3.22312452</v>
       </c>
       <c r="N67">
-        <v>10.0257107</v>
+        <v>9.976875479999999</v>
       </c>
       <c r="O67">
-        <v>2.506427675</v>
+        <v>2.49421887</v>
       </c>
       <c r="P67">
-        <v>7.519283025</v>
+        <v>7.482656609999999</v>
       </c>
       <c r="Q67">
-        <v>8.519283025</v>
+        <v>8.482656609999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3105287275884449</v>
+        <v>0.3175013894213276</v>
       </c>
       <c r="T67">
-        <v>1.619047943249033</v>
+        <v>1.661691875029078</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.158411144189031</v>
+        <v>4.095404914731621</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1365614724032514</v>
+        <v>0.136260390150547</v>
       </c>
       <c r="C68">
-        <v>46.94226674013935</v>
+        <v>46.42615828113894</v>
       </c>
       <c r="D68">
-        <v>98.78566674013935</v>
+        <v>99.11445828113894</v>
       </c>
       <c r="E68">
-        <v>54.2734</v>
+        <v>55.1183</v>
       </c>
       <c r="F68">
-        <v>55.7634</v>
+        <v>56.6083</v>
       </c>
       <c r="G68">
         <v>3.92</v>
@@ -6863,28 +6863,28 @@
         <v>13.2</v>
       </c>
       <c r="M68">
-        <v>3.22312452</v>
+        <v>3.27195974</v>
       </c>
       <c r="N68">
-        <v>9.976875479999999</v>
+        <v>9.92804026</v>
       </c>
       <c r="O68">
-        <v>2.49421887</v>
+        <v>2.482010065</v>
       </c>
       <c r="P68">
-        <v>7.482656609999999</v>
+        <v>7.446030195</v>
       </c>
       <c r="Q68">
-        <v>8.482656609999999</v>
+        <v>8.446030194999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3175013894213276</v>
+        <v>0.3248966368198395</v>
       </c>
       <c r="T68">
-        <v>1.661691875029078</v>
+        <v>1.706920287523065</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.095404914731621</v>
+        <v>4.03427946824309</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.136260390150547</v>
+        <v>0.1377443078978427</v>
       </c>
       <c r="C69">
-        <v>46.42615828113894</v>
+        <v>43.98161924942865</v>
       </c>
       <c r="D69">
-        <v>99.11445828113894</v>
+        <v>97.51481924942865</v>
       </c>
       <c r="E69">
-        <v>55.1183</v>
+        <v>55.9632</v>
       </c>
       <c r="F69">
-        <v>56.6083</v>
+        <v>57.4532</v>
       </c>
       <c r="G69">
         <v>3.92</v>
@@ -6945,45 +6945,45 @@
         <v>13.2</v>
       </c>
       <c r="M69">
-        <v>3.27195974</v>
+        <v>3.52188116</v>
       </c>
       <c r="N69">
-        <v>9.92804026</v>
+        <v>9.67811884</v>
       </c>
       <c r="O69">
-        <v>2.482010065</v>
+        <v>2.41952971</v>
       </c>
       <c r="P69">
-        <v>7.446030195</v>
+        <v>7.25858913</v>
       </c>
       <c r="Q69">
-        <v>8.446030194999999</v>
+        <v>8.258589130000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3248966368198395</v>
+        <v>0.3327540871807584</v>
       </c>
       <c r="T69">
-        <v>1.706920287523065</v>
+        <v>1.754975475797926</v>
       </c>
       <c r="U69">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>4.03427946824309</v>
+        <v>3.747996993742969</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1377443078978427</v>
+        <v>0.1374694756451383</v>
       </c>
       <c r="C70">
-        <v>43.98161924942865</v>
+        <v>43.42907629912016</v>
       </c>
       <c r="D70">
-        <v>97.51481924942865</v>
+        <v>97.80717629912016</v>
       </c>
       <c r="E70">
-        <v>55.9632</v>
+        <v>56.8081</v>
       </c>
       <c r="F70">
-        <v>57.4532</v>
+        <v>58.2981</v>
       </c>
       <c r="G70">
         <v>3.92</v>
@@ -7027,28 +7027,28 @@
         <v>13.2</v>
       </c>
       <c r="M70">
-        <v>3.52188116</v>
+        <v>3.57367353</v>
       </c>
       <c r="N70">
-        <v>9.67811884</v>
+        <v>9.626326469999999</v>
       </c>
       <c r="O70">
-        <v>2.41952971</v>
+        <v>2.4065816175</v>
       </c>
       <c r="P70">
-        <v>7.25858913</v>
+        <v>7.219744852499999</v>
       </c>
       <c r="Q70">
-        <v>8.258589130000001</v>
+        <v>8.2197448525</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3327540871807584</v>
+        <v>0.3411184698230269</v>
       </c>
       <c r="T70">
-        <v>1.754975475797926</v>
+        <v>1.806130998800197</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.747996993742969</v>
+        <v>3.693678196732201</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1374694756451383</v>
+        <v>0.137194643392434</v>
       </c>
       <c r="C71">
-        <v>43.42907629912016</v>
+        <v>42.8782916388728</v>
       </c>
       <c r="D71">
-        <v>97.80717629912016</v>
+        <v>98.10129163887279</v>
       </c>
       <c r="E71">
-        <v>56.8081</v>
+        <v>57.653</v>
       </c>
       <c r="F71">
-        <v>58.2981</v>
+        <v>59.143</v>
       </c>
       <c r="G71">
         <v>3.92</v>
@@ -7109,28 +7109,28 @@
         <v>13.2</v>
       </c>
       <c r="M71">
-        <v>3.57367353</v>
+        <v>3.6254659</v>
       </c>
       <c r="N71">
-        <v>9.626326469999999</v>
+        <v>9.574534099999999</v>
       </c>
       <c r="O71">
-        <v>2.4065816175</v>
+        <v>2.393633525</v>
       </c>
       <c r="P71">
-        <v>7.219744852499999</v>
+        <v>7.180900574999999</v>
       </c>
       <c r="Q71">
-        <v>8.2197448525</v>
+        <v>8.180900574999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3411184698230269</v>
+        <v>0.35004047797478</v>
       </c>
       <c r="T71">
-        <v>1.806130998800197</v>
+        <v>1.86069689000262</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.693678196732201</v>
+        <v>3.640911365350312</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.137194643392434</v>
+        <v>0.1369198111397296</v>
       </c>
       <c r="C72">
-        <v>42.8782916388728</v>
+        <v>42.32928117855779</v>
       </c>
       <c r="D72">
-        <v>98.10129163887279</v>
+        <v>98.39718117855779</v>
       </c>
       <c r="E72">
-        <v>57.653</v>
+        <v>58.4979</v>
       </c>
       <c r="F72">
-        <v>59.143</v>
+        <v>59.9879</v>
       </c>
       <c r="G72">
         <v>3.92</v>
@@ -7191,28 +7191,28 @@
         <v>13.2</v>
       </c>
       <c r="M72">
-        <v>3.6254659</v>
+        <v>3.67725827</v>
       </c>
       <c r="N72">
-        <v>9.574534099999999</v>
+        <v>9.52274173</v>
       </c>
       <c r="O72">
-        <v>2.393633525</v>
+        <v>2.3806854325</v>
       </c>
       <c r="P72">
-        <v>7.180900574999999</v>
+        <v>7.1420562975</v>
       </c>
       <c r="Q72">
-        <v>8.180900574999999</v>
+        <v>8.1420562975</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.35004047797478</v>
+        <v>0.3595777970335505</v>
       </c>
       <c r="T72">
-        <v>1.86069689000262</v>
+        <v>1.919025946115555</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.640911365350312</v>
+        <v>3.589630923584815</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1369198111397296</v>
+        <v>0.1366449788870253</v>
       </c>
       <c r="C73">
-        <v>42.32928117855779</v>
+        <v>41.78206102057406</v>
       </c>
       <c r="D73">
-        <v>98.39718117855779</v>
+        <v>98.69486102057405</v>
       </c>
       <c r="E73">
-        <v>58.49789999999999</v>
+        <v>59.34279999999999</v>
       </c>
       <c r="F73">
-        <v>59.9879</v>
+        <v>60.83279999999999</v>
       </c>
       <c r="G73">
         <v>3.92</v>
@@ -7273,28 +7273,28 @@
         <v>13.2</v>
       </c>
       <c r="M73">
-        <v>3.67725827</v>
+        <v>3.72905064</v>
       </c>
       <c r="N73">
-        <v>9.52274173</v>
+        <v>9.470949359999999</v>
       </c>
       <c r="O73">
-        <v>2.3806854325</v>
+        <v>2.36773734</v>
       </c>
       <c r="P73">
-        <v>7.1420562975</v>
+        <v>7.103212019999999</v>
       </c>
       <c r="Q73">
-        <v>8.1420562975</v>
+        <v>8.103212019999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3595777970335504</v>
+        <v>0.3697963531679474</v>
       </c>
       <c r="T73">
-        <v>1.919025946115555</v>
+        <v>1.981521363379413</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.589630923584815</v>
+        <v>3.539774938535026</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1366449788870253</v>
+        <v>0.1379031466343209</v>
       </c>
       <c r="C74">
-        <v>41.78206102057406</v>
+        <v>39.5889476804487</v>
       </c>
       <c r="D74">
-        <v>98.69486102057405</v>
+        <v>97.3466476804487</v>
       </c>
       <c r="E74">
-        <v>59.34279999999999</v>
+        <v>60.18769999999999</v>
       </c>
       <c r="F74">
-        <v>60.83279999999999</v>
+        <v>61.67769999999999</v>
       </c>
       <c r="G74">
         <v>3.92</v>
@@ -7355,45 +7355,45 @@
         <v>13.2</v>
       </c>
       <c r="M74">
-        <v>3.72905064</v>
+        <v>3.95354057</v>
       </c>
       <c r="N74">
-        <v>9.470949359999999</v>
+        <v>9.24645943</v>
       </c>
       <c r="O74">
-        <v>2.36773734</v>
+        <v>2.3116148575</v>
       </c>
       <c r="P74">
-        <v>7.103212019999999</v>
+        <v>6.934844572499999</v>
       </c>
       <c r="Q74">
-        <v>8.103212019999999</v>
+        <v>7.934844572499999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3697963531679474</v>
+        <v>0.3807718393863738</v>
       </c>
       <c r="T74">
-        <v>1.981521363379413</v>
+        <v>2.048646070810965</v>
       </c>
       <c r="U74">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>3.539774938535026</v>
+        <v>3.338779447506719</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1379031466343209</v>
+        <v>0.1376493143816166</v>
       </c>
       <c r="C75">
-        <v>39.5889476804487</v>
+        <v>39.01307221307917</v>
       </c>
       <c r="D75">
-        <v>97.3466476804487</v>
+        <v>97.61567221307916</v>
       </c>
       <c r="E75">
-        <v>60.18769999999999</v>
+        <v>61.0326</v>
       </c>
       <c r="F75">
-        <v>61.67769999999999</v>
+        <v>62.5226</v>
       </c>
       <c r="G75">
         <v>3.92</v>
@@ -7437,28 +7437,28 @@
         <v>13.2</v>
       </c>
       <c r="M75">
-        <v>3.95354057</v>
+        <v>4.00769866</v>
       </c>
       <c r="N75">
-        <v>9.24645943</v>
+        <v>9.19230134</v>
       </c>
       <c r="O75">
-        <v>2.3116148575</v>
+        <v>2.298075335</v>
       </c>
       <c r="P75">
-        <v>6.934844572499999</v>
+        <v>6.894226005</v>
       </c>
       <c r="Q75">
-        <v>7.934844572499999</v>
+        <v>7.894226005</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3807718393863738</v>
+        <v>0.3925915937754484</v>
       </c>
       <c r="T75">
-        <v>2.048646070810965</v>
+        <v>2.120934217275714</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.338779447506719</v>
+        <v>3.293660806324196</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1376493143816166</v>
+        <v>0.1373954821289123</v>
       </c>
       <c r="C76">
-        <v>39.01307221307917</v>
+        <v>38.43868780403619</v>
       </c>
       <c r="D76">
-        <v>97.61567221307916</v>
+        <v>97.88618780403618</v>
       </c>
       <c r="E76">
-        <v>61.0326</v>
+        <v>61.87749999999999</v>
       </c>
       <c r="F76">
-        <v>62.5226</v>
+        <v>63.36749999999999</v>
       </c>
       <c r="G76">
         <v>3.92</v>
@@ -7519,28 +7519,28 @@
         <v>13.2</v>
       </c>
       <c r="M76">
-        <v>4.00769866</v>
+        <v>4.06185675</v>
       </c>
       <c r="N76">
-        <v>9.19230134</v>
+        <v>9.138143249999999</v>
       </c>
       <c r="O76">
-        <v>2.298075335</v>
+        <v>2.2845358125</v>
       </c>
       <c r="P76">
-        <v>6.894226005</v>
+        <v>6.853607437499999</v>
       </c>
       <c r="Q76">
-        <v>7.894226005</v>
+        <v>7.853607437499999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3925915937754484</v>
+        <v>0.405356928515649</v>
       </c>
       <c r="T76">
-        <v>2.120934217275714</v>
+        <v>2.199005415457642</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.293660806324196</v>
+        <v>3.24974532890654</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1373954821289123</v>
+        <v>0.1371416498762079</v>
       </c>
       <c r="C77">
-        <v>38.43868780403619</v>
+        <v>37.86580688396973</v>
       </c>
       <c r="D77">
-        <v>97.88618780403618</v>
+        <v>98.15820688396973</v>
       </c>
       <c r="E77">
-        <v>61.87749999999999</v>
+        <v>62.7224</v>
       </c>
       <c r="F77">
-        <v>63.36749999999999</v>
+        <v>64.2124</v>
       </c>
       <c r="G77">
         <v>3.92</v>
@@ -7601,28 +7601,28 @@
         <v>13.2</v>
       </c>
       <c r="M77">
-        <v>4.06185675</v>
+        <v>4.11601484</v>
       </c>
       <c r="N77">
-        <v>9.138143249999999</v>
+        <v>9.083985159999999</v>
       </c>
       <c r="O77">
-        <v>2.2845358125</v>
+        <v>2.27099629</v>
       </c>
       <c r="P77">
-        <v>6.853607437499999</v>
+        <v>6.81298887</v>
       </c>
       <c r="Q77">
-        <v>7.853607437499999</v>
+        <v>7.81298887</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.405356928515649</v>
+        <v>0.4191860411508663</v>
       </c>
       <c r="T77">
-        <v>2.199005415457642</v>
+        <v>2.283582546821397</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.24974532890654</v>
+        <v>3.206985521947243</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1371416498762079</v>
+        <v>0.1368878176235036</v>
       </c>
       <c r="C78">
-        <v>37.86580688396973</v>
+        <v>37.29444202209064</v>
       </c>
       <c r="D78">
-        <v>98.15820688396973</v>
+        <v>98.43174202209063</v>
       </c>
       <c r="E78">
-        <v>62.7224</v>
+        <v>63.5673</v>
       </c>
       <c r="F78">
-        <v>64.2124</v>
+        <v>65.0573</v>
       </c>
       <c r="G78">
         <v>3.92</v>
@@ -7683,28 +7683,28 @@
         <v>13.2</v>
       </c>
       <c r="M78">
-        <v>4.11601484</v>
+        <v>4.170172930000001</v>
       </c>
       <c r="N78">
-        <v>9.083985159999999</v>
+        <v>9.02982707</v>
       </c>
       <c r="O78">
-        <v>2.27099629</v>
+        <v>2.2574567675</v>
       </c>
       <c r="P78">
-        <v>6.81298887</v>
+        <v>6.7723703025</v>
       </c>
       <c r="Q78">
-        <v>7.81298887</v>
+        <v>7.7723703025</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4191860411508663</v>
+        <v>0.4342176853195807</v>
       </c>
       <c r="T78">
-        <v>2.283582546821397</v>
+        <v>2.375514211347219</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.206985521947243</v>
+        <v>3.165336359324552</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1368878176235036</v>
+        <v>0.1366339853707992</v>
       </c>
       <c r="C79">
-        <v>37.29444202209064</v>
+        <v>36.72460592810657</v>
       </c>
       <c r="D79">
-        <v>98.43174202209063</v>
+        <v>98.70680592810656</v>
       </c>
       <c r="E79">
-        <v>63.5673</v>
+        <v>64.4122</v>
       </c>
       <c r="F79">
-        <v>65.0573</v>
+        <v>65.90219999999999</v>
       </c>
       <c r="G79">
         <v>3.92</v>
@@ -7765,28 +7765,28 @@
         <v>13.2</v>
       </c>
       <c r="M79">
-        <v>4.170172930000001</v>
+        <v>4.22433102</v>
       </c>
       <c r="N79">
-        <v>9.02982707</v>
+        <v>8.975668979999998</v>
       </c>
       <c r="O79">
-        <v>2.2574567675</v>
+        <v>2.243917245</v>
       </c>
       <c r="P79">
-        <v>6.7723703025</v>
+        <v>6.731751734999999</v>
       </c>
       <c r="Q79">
-        <v>7.7723703025</v>
+        <v>7.731751734999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4342176853195807</v>
+        <v>0.4506158425945418</v>
       </c>
       <c r="T79">
-        <v>2.375514211347219</v>
+        <v>2.475803299920841</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.165336359324552</v>
+        <v>3.124755123948596</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1366339853707992</v>
+        <v>0.1363801531180949</v>
       </c>
       <c r="C80">
-        <v>36.72460592810657</v>
+        <v>36.15631145419032</v>
       </c>
       <c r="D80">
-        <v>98.70680592810656</v>
+        <v>98.98341145419032</v>
       </c>
       <c r="E80">
-        <v>64.4122</v>
+        <v>65.25710000000001</v>
       </c>
       <c r="F80">
-        <v>65.90219999999999</v>
+        <v>66.7471</v>
       </c>
       <c r="G80">
         <v>3.92</v>
@@ -7847,28 +7847,28 @@
         <v>13.2</v>
       </c>
       <c r="M80">
-        <v>4.22433102</v>
+        <v>4.278489110000001</v>
       </c>
       <c r="N80">
-        <v>8.975668979999998</v>
+        <v>8.921510889999999</v>
       </c>
       <c r="O80">
-        <v>2.243917245</v>
+        <v>2.2303777225</v>
       </c>
       <c r="P80">
-        <v>6.731751734999999</v>
+        <v>6.691133167499999</v>
       </c>
       <c r="Q80">
-        <v>7.731751734999999</v>
+        <v>7.691133167499999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4506158425945418</v>
+        <v>0.4685757291337851</v>
       </c>
       <c r="T80">
-        <v>2.475803299920841</v>
+        <v>2.585643730263381</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.124755123948596</v>
+        <v>3.085201261620132</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1363801531180949</v>
+        <v>0.1361263208653905</v>
       </c>
       <c r="C81">
-        <v>36.15631145419032</v>
+        <v>35.58957159698218</v>
       </c>
       <c r="D81">
-        <v>98.98341145419032</v>
+        <v>99.26157159698218</v>
       </c>
       <c r="E81">
-        <v>65.25710000000001</v>
+        <v>66.102</v>
       </c>
       <c r="F81">
-        <v>66.7471</v>
+        <v>67.592</v>
       </c>
       <c r="G81">
         <v>3.92</v>
@@ -7929,28 +7929,28 @@
         <v>13.2</v>
       </c>
       <c r="M81">
-        <v>4.278489110000001</v>
+        <v>4.3326472</v>
       </c>
       <c r="N81">
-        <v>8.921510889999999</v>
+        <v>8.867352799999999</v>
       </c>
       <c r="O81">
-        <v>2.2303777225</v>
+        <v>2.2168382</v>
       </c>
       <c r="P81">
-        <v>6.691133167499999</v>
+        <v>6.650514599999999</v>
       </c>
       <c r="Q81">
-        <v>7.691133167499999</v>
+        <v>7.650514599999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4685757291337851</v>
+        <v>0.4883316043269527</v>
       </c>
       <c r="T81">
-        <v>2.585643730263381</v>
+        <v>2.706468203640175</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.085201261620132</v>
+        <v>3.046636245849881</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1361263208653905</v>
+        <v>0.1358724886126862</v>
       </c>
       <c r="C82">
-        <v>35.58957159698218</v>
+        <v>35.02439949962488</v>
       </c>
       <c r="D82">
-        <v>99.26157159698218</v>
+        <v>99.54129949962487</v>
       </c>
       <c r="E82">
-        <v>66.102</v>
+        <v>66.9469</v>
       </c>
       <c r="F82">
-        <v>67.592</v>
+        <v>68.43689999999999</v>
       </c>
       <c r="G82">
         <v>3.92</v>
@@ -8011,28 +8011,28 @@
         <v>13.2</v>
       </c>
       <c r="M82">
-        <v>4.3326472</v>
+        <v>4.38680529</v>
       </c>
       <c r="N82">
-        <v>8.867352799999999</v>
+        <v>8.813194709999999</v>
       </c>
       <c r="O82">
-        <v>2.2168382</v>
+        <v>2.2032986775</v>
       </c>
       <c r="P82">
-        <v>6.650514599999999</v>
+        <v>6.6098960325</v>
       </c>
       <c r="Q82">
-        <v>7.650514599999999</v>
+        <v>7.6098960325</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4883316043269527</v>
+        <v>0.5101670453299273</v>
       </c>
       <c r="T82">
-        <v>2.706468203640175</v>
+        <v>2.840011042635579</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.046636245849881</v>
+        <v>3.009023452691241</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1358724886126862</v>
+        <v>0.1404156563599818</v>
       </c>
       <c r="C83">
-        <v>35.02439949962488</v>
+        <v>29.39981674088573</v>
       </c>
       <c r="D83">
-        <v>99.54129949962487</v>
+        <v>94.76161674088573</v>
       </c>
       <c r="E83">
-        <v>66.9469</v>
+        <v>67.79180000000001</v>
       </c>
       <c r="F83">
-        <v>68.43689999999999</v>
+        <v>69.2818</v>
       </c>
       <c r="G83">
         <v>3.92</v>
@@ -8093,45 +8093,45 @@
         <v>13.2</v>
       </c>
       <c r="M83">
-        <v>4.38680529</v>
+        <v>4.981361420000001</v>
       </c>
       <c r="N83">
-        <v>8.813194709999999</v>
+        <v>8.218638579999999</v>
       </c>
       <c r="O83">
-        <v>2.2032986775</v>
+        <v>2.054659645</v>
       </c>
       <c r="P83">
-        <v>6.6098960325</v>
+        <v>6.163978934999999</v>
       </c>
       <c r="Q83">
-        <v>7.6098960325</v>
+        <v>7.163978934999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5101670453299273</v>
+        <v>0.5344286464443436</v>
       </c>
       <c r="T83">
-        <v>2.840011042635579</v>
+        <v>2.988391974852694</v>
       </c>
       <c r="U83">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V83">
         <v>0.25</v>
       </c>
       <c r="W83">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y83">
-        <v>3.009023452691241</v>
+        <v>2.649877992591029</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1404156563599818</v>
+        <v>0.1402203241072775</v>
       </c>
       <c r="C84">
-        <v>29.39981674088573</v>
+        <v>28.75095504347483</v>
       </c>
       <c r="D84">
-        <v>94.76161674088573</v>
+        <v>94.95765504347483</v>
       </c>
       <c r="E84">
-        <v>67.79180000000001</v>
+        <v>68.6367</v>
       </c>
       <c r="F84">
-        <v>69.2818</v>
+        <v>70.1267</v>
       </c>
       <c r="G84">
         <v>3.92</v>
@@ -8175,28 +8175,28 @@
         <v>13.2</v>
       </c>
       <c r="M84">
-        <v>4.981361420000001</v>
+        <v>5.04210973</v>
       </c>
       <c r="N84">
-        <v>8.218638579999999</v>
+        <v>8.157890269999999</v>
       </c>
       <c r="O84">
-        <v>2.054659645</v>
+        <v>2.0394725675</v>
       </c>
       <c r="P84">
-        <v>6.163978934999999</v>
+        <v>6.118417702499999</v>
       </c>
       <c r="Q84">
-        <v>7.163978934999999</v>
+        <v>7.118417702499999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5344286464443436</v>
+        <v>0.5615445535722207</v>
       </c>
       <c r="T84">
-        <v>2.988391974852694</v>
+        <v>3.154229487330646</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.649877992591029</v>
+        <v>2.617951751716439</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1402203241072775</v>
+        <v>0.1400249918545731</v>
       </c>
       <c r="C85">
-        <v>28.75095504347483</v>
+        <v>28.10290613686405</v>
       </c>
       <c r="D85">
-        <v>94.95765504347483</v>
+        <v>95.15450613686406</v>
       </c>
       <c r="E85">
-        <v>68.6367</v>
+        <v>69.48160000000001</v>
       </c>
       <c r="F85">
-        <v>70.1267</v>
+        <v>70.97160000000001</v>
       </c>
       <c r="G85">
         <v>3.92</v>
@@ -8257,28 +8257,28 @@
         <v>13.2</v>
       </c>
       <c r="M85">
-        <v>5.04210973</v>
+        <v>5.102858040000001</v>
       </c>
       <c r="N85">
-        <v>8.157890269999999</v>
+        <v>8.097141959999998</v>
       </c>
       <c r="O85">
-        <v>2.0394725675</v>
+        <v>2.02428549</v>
       </c>
       <c r="P85">
-        <v>6.118417702499999</v>
+        <v>6.072856469999999</v>
       </c>
       <c r="Q85">
-        <v>7.118417702499999</v>
+        <v>7.072856469999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5615445535722207</v>
+        <v>0.5920499490910823</v>
       </c>
       <c r="T85">
-        <v>3.154229487330646</v>
+        <v>3.340796688868342</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.617951751716439</v>
+        <v>2.5867856594341</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1400249918545731</v>
+        <v>0.1398296596018688</v>
       </c>
       <c r="C86">
-        <v>28.10290613686406</v>
+        <v>27.45567508639955</v>
       </c>
       <c r="D86">
-        <v>95.15450613686406</v>
+        <v>95.35217508639954</v>
       </c>
       <c r="E86">
-        <v>69.4816</v>
+        <v>70.3265</v>
       </c>
       <c r="F86">
-        <v>70.9716</v>
+        <v>71.81649999999999</v>
       </c>
       <c r="G86">
         <v>3.92</v>
@@ -8339,28 +8339,28 @@
         <v>13.2</v>
       </c>
       <c r="M86">
-        <v>5.10285804</v>
+        <v>5.163606349999999</v>
       </c>
       <c r="N86">
-        <v>8.097141959999998</v>
+        <v>8.036393650000001</v>
       </c>
       <c r="O86">
-        <v>2.02428549</v>
+        <v>2.0090984125</v>
       </c>
       <c r="P86">
-        <v>6.072856469999999</v>
+        <v>6.027295237500001</v>
       </c>
       <c r="Q86">
-        <v>7.072856469999999</v>
+        <v>7.027295237500001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.592049949091082</v>
+        <v>0.6266227306791252</v>
       </c>
       <c r="T86">
-        <v>3.34079668886834</v>
+        <v>3.552239517277729</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.5867856594341</v>
+        <v>2.55635288697017</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1398296596018688</v>
+        <v>0.1396343273491644</v>
       </c>
       <c r="C87">
-        <v>27.45567508639955</v>
+        <v>26.80926699960504</v>
       </c>
       <c r="D87">
-        <v>95.35217508639954</v>
+        <v>95.55066699960504</v>
       </c>
       <c r="E87">
-        <v>70.3265</v>
+        <v>71.17140000000001</v>
       </c>
       <c r="F87">
-        <v>71.81649999999999</v>
+        <v>72.6614</v>
       </c>
       <c r="G87">
         <v>3.92</v>
@@ -8421,28 +8421,28 @@
         <v>13.2</v>
       </c>
       <c r="M87">
-        <v>5.163606349999999</v>
+        <v>5.22435466</v>
       </c>
       <c r="N87">
-        <v>8.036393650000001</v>
+        <v>7.975645339999999</v>
       </c>
       <c r="O87">
-        <v>2.0090984125</v>
+        <v>1.993911335</v>
       </c>
       <c r="P87">
-        <v>6.027295237500001</v>
+        <v>5.981734004999999</v>
       </c>
       <c r="Q87">
-        <v>7.027295237500001</v>
+        <v>6.981734004999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6266227306791252</v>
+        <v>0.6661344810654602</v>
       </c>
       <c r="T87">
-        <v>3.552239517277729</v>
+        <v>3.793888464031316</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.55635288697017</v>
+        <v>2.526627853400749</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1396343273491644</v>
+        <v>0.1419837450964601</v>
       </c>
       <c r="C88">
-        <v>26.80926699960504</v>
+        <v>23.63041303898855</v>
       </c>
       <c r="D88">
-        <v>95.55066699960504</v>
+        <v>93.21671303898854</v>
       </c>
       <c r="E88">
-        <v>71.17140000000001</v>
+        <v>72.0163</v>
       </c>
       <c r="F88">
-        <v>72.6614</v>
+        <v>73.5063</v>
       </c>
       <c r="G88">
         <v>3.92</v>
@@ -8503,45 +8503,45 @@
         <v>13.2</v>
       </c>
       <c r="M88">
-        <v>5.22435466</v>
+        <v>5.57177754</v>
       </c>
       <c r="N88">
-        <v>7.975645339999999</v>
+        <v>7.628222459999999</v>
       </c>
       <c r="O88">
-        <v>1.993911335</v>
+        <v>1.907055615</v>
       </c>
       <c r="P88">
-        <v>5.981734004999999</v>
+        <v>5.721166844999999</v>
       </c>
       <c r="Q88">
-        <v>6.981734004999999</v>
+        <v>6.721166844999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6661344810654602</v>
+        <v>0.7117249622804622</v>
       </c>
       <c r="T88">
-        <v>3.793888464031316</v>
+        <v>4.072714171823916</v>
       </c>
       <c r="U88">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V88">
         <v>0.25</v>
       </c>
       <c r="W88">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y88">
-        <v>2.526627853400749</v>
+        <v>2.369082380844659</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1419837450964601</v>
+        <v>0.1418176628437557</v>
       </c>
       <c r="C89">
-        <v>23.63041303898855</v>
+        <v>22.94675047419258</v>
       </c>
       <c r="D89">
-        <v>93.21671303898854</v>
+        <v>93.37795047419257</v>
       </c>
       <c r="E89">
-        <v>72.0163</v>
+        <v>72.8612</v>
       </c>
       <c r="F89">
-        <v>73.5063</v>
+        <v>74.35119999999999</v>
       </c>
       <c r="G89">
         <v>3.92</v>
@@ -8585,28 +8585,28 @@
         <v>13.2</v>
       </c>
       <c r="M89">
-        <v>5.57177754</v>
+        <v>5.63582096</v>
       </c>
       <c r="N89">
-        <v>7.628222459999999</v>
+        <v>7.564179039999999</v>
       </c>
       <c r="O89">
-        <v>1.907055615</v>
+        <v>1.89104476</v>
       </c>
       <c r="P89">
-        <v>5.721166844999999</v>
+        <v>5.673134279999999</v>
       </c>
       <c r="Q89">
-        <v>6.721166844999999</v>
+        <v>6.673134279999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7117249622804622</v>
+        <v>0.7649138570312979</v>
       </c>
       <c r="T89">
-        <v>4.072714171823916</v>
+        <v>4.398010830915283</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.369082380844659</v>
+        <v>2.342160990153243</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1418176628437557</v>
+        <v>0.1416515805910514</v>
       </c>
       <c r="C90">
-        <v>22.94675047419258</v>
+        <v>22.26364666234136</v>
       </c>
       <c r="D90">
-        <v>93.37795047419257</v>
+        <v>93.53974666234136</v>
       </c>
       <c r="E90">
-        <v>72.8612</v>
+        <v>73.70610000000001</v>
       </c>
       <c r="F90">
-        <v>74.35119999999999</v>
+        <v>75.1961</v>
       </c>
       <c r="G90">
         <v>3.92</v>
@@ -8667,28 +8667,28 @@
         <v>13.2</v>
       </c>
       <c r="M90">
-        <v>5.63582096</v>
+        <v>5.69986438</v>
       </c>
       <c r="N90">
-        <v>7.564179039999999</v>
+        <v>7.500135619999999</v>
       </c>
       <c r="O90">
-        <v>1.89104476</v>
+        <v>1.875033905</v>
       </c>
       <c r="P90">
-        <v>5.673134279999999</v>
+        <v>5.625101715</v>
       </c>
       <c r="Q90">
-        <v>6.673134279999999</v>
+        <v>6.625101715</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7649138570312979</v>
+        <v>0.8277734599186491</v>
       </c>
       <c r="T90">
-        <v>4.398010830915283</v>
+        <v>4.782452337114172</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.342160990153243</v>
+        <v>2.315844574533544</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1416515805910514</v>
+        <v>0.1414854983383471</v>
       </c>
       <c r="C91">
-        <v>22.26364666234136</v>
+        <v>21.58110451293375</v>
       </c>
       <c r="D91">
-        <v>93.53974666234136</v>
+        <v>93.70210451293374</v>
       </c>
       <c r="E91">
-        <v>73.70610000000001</v>
+        <v>74.551</v>
       </c>
       <c r="F91">
-        <v>75.1961</v>
+        <v>76.041</v>
       </c>
       <c r="G91">
         <v>3.92</v>
@@ -8749,28 +8749,28 @@
         <v>13.2</v>
       </c>
       <c r="M91">
-        <v>5.69986438</v>
+        <v>5.7639078</v>
       </c>
       <c r="N91">
-        <v>7.500135619999999</v>
+        <v>7.436092199999999</v>
       </c>
       <c r="O91">
-        <v>1.875033905</v>
+        <v>1.85902305</v>
       </c>
       <c r="P91">
-        <v>5.625101715</v>
+        <v>5.57706915</v>
       </c>
       <c r="Q91">
-        <v>6.625101715</v>
+        <v>6.57706915</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8277734599186491</v>
+        <v>0.9032049833834708</v>
       </c>
       <c r="T91">
-        <v>4.782452337114172</v>
+        <v>5.243782144552839</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.315844574533544</v>
+        <v>2.290112968149837</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1414854983383471</v>
+        <v>0.1413194160856427</v>
       </c>
       <c r="C92">
-        <v>21.58110451293375</v>
+        <v>20.89912695570384</v>
       </c>
       <c r="D92">
-        <v>93.70210451293374</v>
+        <v>93.86502695570383</v>
       </c>
       <c r="E92">
-        <v>74.551</v>
+        <v>75.3959</v>
       </c>
       <c r="F92">
-        <v>76.041</v>
+        <v>76.88589999999999</v>
       </c>
       <c r="G92">
         <v>3.92</v>
@@ -8831,28 +8831,28 @@
         <v>13.2</v>
       </c>
       <c r="M92">
-        <v>5.7639078</v>
+        <v>5.82795122</v>
       </c>
       <c r="N92">
-        <v>7.436092199999999</v>
+        <v>7.372048779999999</v>
       </c>
       <c r="O92">
-        <v>1.85902305</v>
+        <v>1.843012195</v>
       </c>
       <c r="P92">
-        <v>5.57706915</v>
+        <v>5.529036584999999</v>
       </c>
       <c r="Q92">
-        <v>6.57706915</v>
+        <v>6.529036584999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9032049833834708</v>
+        <v>0.9953990676182526</v>
       </c>
       <c r="T92">
-        <v>5.243782144552839</v>
+        <v>5.807629686977876</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.290112968149837</v>
+        <v>2.264946891576762</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1413194160856427</v>
+        <v>0.1411533338329384</v>
       </c>
       <c r="C93">
-        <v>20.89912695570384</v>
+        <v>20.21771694079727</v>
       </c>
       <c r="D93">
-        <v>93.86502695570383</v>
+        <v>94.02851694079727</v>
       </c>
       <c r="E93">
-        <v>75.3959</v>
+        <v>76.24080000000001</v>
       </c>
       <c r="F93">
-        <v>76.88589999999999</v>
+        <v>77.7308</v>
       </c>
       <c r="G93">
         <v>3.92</v>
@@ -8913,28 +8913,28 @@
         <v>13.2</v>
       </c>
       <c r="M93">
-        <v>5.82795122</v>
+        <v>5.891994640000001</v>
       </c>
       <c r="N93">
-        <v>7.372048779999999</v>
+        <v>7.308005359999998</v>
       </c>
       <c r="O93">
-        <v>1.843012195</v>
+        <v>1.82700134</v>
       </c>
       <c r="P93">
-        <v>5.529036584999999</v>
+        <v>5.481004019999999</v>
       </c>
       <c r="Q93">
-        <v>6.529036584999999</v>
+        <v>6.481004019999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9953990676182526</v>
+        <v>1.11064167291173</v>
       </c>
       <c r="T93">
-        <v>5.807629686977876</v>
+        <v>6.512439115009173</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.264946891576762</v>
+        <v>2.24032790362484</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1411533338329384</v>
+        <v>0.140987251580234</v>
       </c>
       <c r="C94">
-        <v>20.21771694079727</v>
+        <v>19.5368774389493</v>
       </c>
       <c r="D94">
-        <v>94.02851694079727</v>
+        <v>94.1925774389493</v>
       </c>
       <c r="E94">
-        <v>76.24080000000001</v>
+        <v>77.0857</v>
       </c>
       <c r="F94">
-        <v>77.7308</v>
+        <v>78.5757</v>
       </c>
       <c r="G94">
         <v>3.92</v>
@@ -8995,28 +8995,28 @@
         <v>13.2</v>
       </c>
       <c r="M94">
-        <v>5.891994640000001</v>
+        <v>5.95603806</v>
       </c>
       <c r="N94">
-        <v>7.308005359999998</v>
+        <v>7.243961939999999</v>
       </c>
       <c r="O94">
-        <v>1.82700134</v>
+        <v>1.810990485</v>
       </c>
       <c r="P94">
-        <v>5.481004019999999</v>
+        <v>5.432971455</v>
       </c>
       <c r="Q94">
-        <v>6.481004019999999</v>
+        <v>6.432971455</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.11064167291173</v>
+        <v>1.258810736860487</v>
       </c>
       <c r="T94">
-        <v>6.512439115009173</v>
+        <v>7.418622665335127</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.24032790362484</v>
+        <v>2.216238356274036</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.140987251580234</v>
+        <v>0.1408211693275297</v>
       </c>
       <c r="C95">
-        <v>19.5368774389493</v>
+        <v>18.85661144166471</v>
       </c>
       <c r="D95">
-        <v>94.1925774389493</v>
+        <v>94.3572114416647</v>
       </c>
       <c r="E95">
-        <v>77.0857</v>
+        <v>77.9306</v>
       </c>
       <c r="F95">
-        <v>78.5757</v>
+        <v>79.42059999999999</v>
       </c>
       <c r="G95">
         <v>3.92</v>
@@ -9077,28 +9077,28 @@
         <v>13.2</v>
       </c>
       <c r="M95">
-        <v>5.95603806</v>
+        <v>6.02008148</v>
       </c>
       <c r="N95">
-        <v>7.243961939999999</v>
+        <v>7.179918519999999</v>
       </c>
       <c r="O95">
-        <v>1.810990485</v>
+        <v>1.79497963</v>
       </c>
       <c r="P95">
-        <v>5.432971455</v>
+        <v>5.384938889999999</v>
       </c>
       <c r="Q95">
-        <v>6.432971455</v>
+        <v>6.384938889999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.258810736860487</v>
+        <v>1.456369488792163</v>
       </c>
       <c r="T95">
-        <v>7.418622665335127</v>
+        <v>8.626867399103064</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.216238356274036</v>
+        <v>2.192661352483887</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1408211693275297</v>
+        <v>0.1406550870748254</v>
       </c>
       <c r="C96">
-        <v>18.85661144166471</v>
+        <v>18.17692196139961</v>
       </c>
       <c r="D96">
-        <v>94.3572114416647</v>
+        <v>94.52242196139962</v>
       </c>
       <c r="E96">
-        <v>77.9306</v>
+        <v>78.77550000000001</v>
       </c>
       <c r="F96">
-        <v>79.42059999999999</v>
+        <v>80.2655</v>
       </c>
       <c r="G96">
         <v>3.92</v>
@@ -9159,28 +9159,28 @@
         <v>13.2</v>
       </c>
       <c r="M96">
-        <v>6.02008148</v>
+        <v>6.084124900000001</v>
       </c>
       <c r="N96">
-        <v>7.179918519999999</v>
+        <v>7.115875099999998</v>
       </c>
       <c r="O96">
-        <v>1.79497963</v>
+        <v>1.778968775</v>
       </c>
       <c r="P96">
-        <v>5.384938889999999</v>
+        <v>5.336906324999999</v>
       </c>
       <c r="Q96">
-        <v>6.384938889999999</v>
+        <v>6.336906324999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.456369488792163</v>
+        <v>1.732951741496509</v>
       </c>
       <c r="T96">
-        <v>8.626867399103064</v>
+        <v>10.31841002637818</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.192661352483887</v>
+        <v>2.169580706668267</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1406550870748254</v>
+        <v>0.140489004822121</v>
       </c>
       <c r="C97">
-        <v>18.17692196139961</v>
+        <v>17.4978120317453</v>
       </c>
       <c r="D97">
-        <v>94.52242196139962</v>
+        <v>94.68821203174529</v>
       </c>
       <c r="E97">
-        <v>78.77550000000001</v>
+        <v>79.6204</v>
       </c>
       <c r="F97">
-        <v>80.2655</v>
+        <v>81.1104</v>
       </c>
       <c r="G97">
         <v>3.92</v>
@@ -9241,28 +9241,28 @@
         <v>13.2</v>
       </c>
       <c r="M97">
-        <v>6.084124900000001</v>
+        <v>6.148168320000001</v>
       </c>
       <c r="N97">
-        <v>7.115875099999998</v>
+        <v>7.051831679999998</v>
       </c>
       <c r="O97">
-        <v>1.778968775</v>
+        <v>1.76295792</v>
       </c>
       <c r="P97">
-        <v>5.336906324999999</v>
+        <v>5.288873759999999</v>
       </c>
       <c r="Q97">
-        <v>6.336906324999999</v>
+        <v>6.288873759999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.732951741496509</v>
+        <v>2.147825120553029</v>
       </c>
       <c r="T97">
-        <v>10.31841002637818</v>
+        <v>12.85572396729085</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.169580706668267</v>
+        <v>2.146980907640472</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.140489004822121</v>
+        <v>0.1403229225694166</v>
       </c>
       <c r="C98">
-        <v>17.49781203174527</v>
+        <v>16.81928470761373</v>
       </c>
       <c r="D98">
-        <v>94.68821203174527</v>
+        <v>94.85458470761372</v>
       </c>
       <c r="E98">
-        <v>79.6204</v>
+        <v>80.4653</v>
       </c>
       <c r="F98">
-        <v>81.1104</v>
+        <v>81.95529999999999</v>
       </c>
       <c r="G98">
         <v>3.92</v>
@@ -9323,28 +9323,28 @@
         <v>13.2</v>
       </c>
       <c r="M98">
-        <v>6.148168320000001</v>
+        <v>6.21221174</v>
       </c>
       <c r="N98">
-        <v>7.051831679999998</v>
+        <v>6.987788259999999</v>
       </c>
       <c r="O98">
-        <v>1.76295792</v>
+        <v>1.746947065</v>
       </c>
       <c r="P98">
-        <v>5.288873759999999</v>
+        <v>5.240841195</v>
       </c>
       <c r="Q98">
-        <v>6.288873759999999</v>
+        <v>6.240841195</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.147825120553023</v>
+        <v>2.839280752313885</v>
       </c>
       <c r="T98">
-        <v>12.85572396729082</v>
+        <v>17.08458053547859</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.146980907640472</v>
+        <v>2.124847083850365</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1403229225694166</v>
+        <v>0.1401568403167123</v>
       </c>
       <c r="C99">
-        <v>16.81928470761373</v>
+        <v>16.1413430654254</v>
       </c>
       <c r="D99">
-        <v>94.85458470761372</v>
+        <v>95.02154306542539</v>
       </c>
       <c r="E99">
-        <v>80.4653</v>
+        <v>81.31019999999999</v>
       </c>
       <c r="F99">
-        <v>81.95529999999999</v>
+        <v>82.80019999999999</v>
       </c>
       <c r="G99">
         <v>3.92</v>
@@ -9405,28 +9405,28 @@
         <v>13.2</v>
       </c>
       <c r="M99">
-        <v>6.21221174</v>
+        <v>6.27625516</v>
       </c>
       <c r="N99">
-        <v>6.987788259999999</v>
+        <v>6.923744839999999</v>
       </c>
       <c r="O99">
-        <v>1.746947065</v>
+        <v>1.73093621</v>
       </c>
       <c r="P99">
-        <v>5.240841195</v>
+        <v>5.19280863</v>
       </c>
       <c r="Q99">
-        <v>6.240841195</v>
+        <v>6.19280863</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.839280752313885</v>
+        <v>4.222192015835612</v>
       </c>
       <c r="T99">
-        <v>17.08458053547859</v>
+        <v>25.54229367185413</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.124847083850365</v>
+        <v>2.103164970749851</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1401568403167123</v>
+        <v>0.139990758064008</v>
       </c>
       <c r="C100">
-        <v>16.1413430654254</v>
+        <v>15.46399020329875</v>
       </c>
       <c r="D100">
-        <v>95.02154306542539</v>
+        <v>95.18909020329875</v>
       </c>
       <c r="E100">
-        <v>81.31019999999999</v>
+        <v>82.1551</v>
       </c>
       <c r="F100">
-        <v>82.80019999999999</v>
+        <v>83.6451</v>
       </c>
       <c r="G100">
         <v>3.92</v>
@@ -9487,28 +9487,28 @@
         <v>13.2</v>
       </c>
       <c r="M100">
-        <v>6.27625516</v>
+        <v>6.340298580000001</v>
       </c>
       <c r="N100">
-        <v>6.923744839999999</v>
+        <v>6.859701419999999</v>
       </c>
       <c r="O100">
-        <v>1.73093621</v>
+        <v>1.714925355</v>
       </c>
       <c r="P100">
-        <v>5.19280863</v>
+        <v>5.144776064999999</v>
       </c>
       <c r="Q100">
-        <v>6.19280863</v>
+        <v>6.144776064999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.222192015835612</v>
+        <v>8.370925806400789</v>
       </c>
       <c r="T100">
-        <v>25.54229367185413</v>
+        <v>50.91543308098075</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.103164970749851</v>
+        <v>2.081920880136216</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.139990758064008</v>
-      </c>
-      <c r="C101">
-        <v>15.46399020329875</v>
-      </c>
-      <c r="D101">
-        <v>95.18909020329875</v>
-      </c>
-      <c r="E101">
-        <v>82.1551</v>
-      </c>
-      <c r="F101">
-        <v>83.6451</v>
-      </c>
-      <c r="G101">
-        <v>3.92</v>
-      </c>
-      <c r="H101">
-        <v>83</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>14.2</v>
-      </c>
-      <c r="K101">
-        <v>1</v>
-      </c>
-      <c r="L101">
-        <v>13.2</v>
-      </c>
-      <c r="M101">
-        <v>6.340298580000001</v>
-      </c>
-      <c r="N101">
-        <v>6.859701419999999</v>
-      </c>
-      <c r="O101">
-        <v>1.714925355</v>
-      </c>
-      <c r="P101">
-        <v>5.144776064999999</v>
-      </c>
-      <c r="Q101">
-        <v>6.144776064999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.370925806400789</v>
-      </c>
-      <c r="T101">
-        <v>50.91543308098075</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.05685</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.081920880136216</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
